--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,6 +807,8361 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122578749</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>671</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>707570</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6374984</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122578807</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>783</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>707678</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6374990</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122578774</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>783</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>707528</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6375154</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122578823</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>783</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>707605</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6374970</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Granplantering äldre, enstaka tall.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122578751</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>707569</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6374979</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122578821</v>
+      </c>
+      <c r="B8" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>671</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>707605</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6374970</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Granplantering äldre, enstaka tall.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122578781</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>783</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>707621</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6375108</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Glest spridd.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122578812</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>671</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>707646</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6374967</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122578762</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>671</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>707548</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6375014</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122578780</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>783</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>707626</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6375120</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122578741</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>783</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>707609</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6375033</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spridd, riklig. Strensamling, grav?</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122578796</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>783</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>707725</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6374976</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122578775</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>783</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>707564</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6375169</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal med enstaka tall.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122578769</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>783</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>707513</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6375053</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>3 ex.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122578771</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>707490</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6375090</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I långsträckt stensamlig, grav?</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122578811</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>707652</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6374986</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122578810</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>783</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>707652</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6374986</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122578757</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>707557</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6375009</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122578747</v>
+      </c>
+      <c r="B21" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>671</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>707590</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6375036</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122578783</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>783</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>707633</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6375094</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Glest spridd.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122578817</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>783</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>707624</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6374996</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spridd, ganska rikligt.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122578814</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>707638</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6374988</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122578752</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>783</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>707569</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6374979</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122578744</v>
+      </c>
+      <c r="B26" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>671</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>707626</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6375071</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Stensamling, grav? Nära.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122578797</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>707725</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6374976</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122578756</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>783</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>707541</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6374993</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122578740</v>
+      </c>
+      <c r="B29" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>671</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>707609</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6375033</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Spridd, riklig. Strensamling, grav?</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122578764</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>783</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>707538</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6375024</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122578770</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>783</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>707506</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6375077</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122578755</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>707541</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6374993</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122578802</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>707697</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6374969</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122578825</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>783</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>707611</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6374954</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Grandunge.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122578804</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>783</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>707697</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6374980</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122578773</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>783</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>707489</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6375140</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122578748</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>783</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>707590</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6375036</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122578750</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98246</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>707569</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6374979</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122578808</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>707678</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6374990</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122578766</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>783</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>707548</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6375091</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122578765</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>783</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>707532</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6375035</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spridd glest mot O-N.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122578772</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>783</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>707506</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6375110</v>
+      </c>
+      <c r="S42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122578816</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>783</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>707638</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6374988</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spridd, ganska rikligt.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122578763</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>783</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>707548</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6375014</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122578819</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>783</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>707605</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6374982</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Granplantering äldre, enstaka tall.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122578813</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>783</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>707646</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6374967</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122578754</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>783</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>707554</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6374978</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122578760</v>
+      </c>
+      <c r="B48" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>671</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>707547</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6375010</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122578824</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>783</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>707606</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6374961</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Grandunge.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122578742</v>
+      </c>
+      <c r="B50" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>671</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>707638</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6375036</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122578806</v>
+      </c>
+      <c r="B51" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>671</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>707678</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6374990</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122578758</v>
+      </c>
+      <c r="B52" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>671</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>707557</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6375009</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122578805</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>707697</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6374980</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122578746</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>783</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>707626</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6375071</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Stensamling, grav? Nära.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122578753</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>707554</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6374978</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122578777</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>783</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>707591</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6375187</v>
+      </c>
+      <c r="S56" t="n">
+        <v>6</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>30 m S åker i N.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>122578809</v>
+      </c>
+      <c r="B57" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>671</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>707652</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6374986</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122578786</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>707652</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6375083</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122578782</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>707621</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6375108</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122578778</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>783</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>707599</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6375165</v>
+      </c>
+      <c r="S60" t="n">
+        <v>6</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Barrblandskog mot åker i N.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122578779</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>783</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>707597</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6375142</v>
+      </c>
+      <c r="S61" t="n">
+        <v>6</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Enstaka strå.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal med enstaka tall.</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>122578776</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>783</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>707584</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6375172</v>
+      </c>
+      <c r="S62" t="n">
+        <v>7</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal med enstaka tall.</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>122578803</v>
+      </c>
+      <c r="B63" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>671</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>707697</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6374980</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>122578795</v>
+      </c>
+      <c r="B64" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>671</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>707725</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6374976</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>122578784</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>783</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>707648</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6375072</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Glest spridd, men saknas mot O-NO..</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>122578785</v>
+      </c>
+      <c r="B66" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>671</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>707648</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6375072</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Glest spridd, men saknas mot O-NO..</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>122578818</v>
+      </c>
+      <c r="B67" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>671</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>707605</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6374982</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Granplantering äldre, enstaka tall.</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122578759</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>783</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>707557</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6375009</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>122578767</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98246</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>707513</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6375053</v>
+      </c>
+      <c r="S69" t="n">
+        <v>7</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal.</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122578815</v>
+      </c>
+      <c r="B70" t="n">
+        <v>105422</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>671</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>707638</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6374988</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Spridd, ganska rikligt.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>122578743</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99752</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>783</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>707638</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6375036</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt söderut.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578749</v>
+        <v>122578754</v>
       </c>
       <c r="B3" t="n">
-        <v>105422</v>
+        <v>99765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,21 +826,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707570</v>
+        <v>707554</v>
       </c>
       <c r="R3" t="n">
-        <v>6374984</v>
+        <v>6374978</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578807</v>
+        <v>122578753</v>
       </c>
       <c r="B4" t="n">
-        <v>99752</v>
+        <v>98215</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,28 +948,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -981,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707678</v>
+        <v>707554</v>
       </c>
       <c r="R4" t="n">
-        <v>6374990</v>
+        <v>6374978</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1021,7 +1030,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1062,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578774</v>
+        <v>122578811</v>
       </c>
       <c r="B5" t="n">
-        <v>99752</v>
+        <v>98215</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,35 +1074,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1107,13 +1116,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707528</v>
+        <v>707652</v>
       </c>
       <c r="R5" t="n">
-        <v>6375154</v>
+        <v>6374986</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1156,7 +1165,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1174,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578823</v>
+        <v>122578810</v>
       </c>
       <c r="B6" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,16 +1216,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707605</v>
+        <v>707652</v>
       </c>
       <c r="R6" t="n">
-        <v>6374970</v>
+        <v>6374986</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578751</v>
+        <v>122578750</v>
       </c>
       <c r="B7" t="n">
-        <v>98202</v>
+        <v>98259</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,26 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1426,10 +1426,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578821</v>
+        <v>122578751</v>
       </c>
       <c r="B8" t="n">
-        <v>105422</v>
+        <v>98215</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,40 +1438,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707605</v>
+        <v>707569</v>
       </c>
       <c r="R8" t="n">
-        <v>6374970</v>
+        <v>6374979</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578781</v>
+        <v>122578784</v>
       </c>
       <c r="B9" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707621</v>
+        <v>707648</v>
       </c>
       <c r="R9" t="n">
-        <v>6375108</v>
+        <v>6375072</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,10 +1669,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578812</v>
+        <v>122578795</v>
       </c>
       <c r="B10" t="n">
-        <v>105422</v>
+        <v>105435</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707646</v>
+        <v>707725</v>
       </c>
       <c r="R10" t="n">
-        <v>6374967</v>
+        <v>6374976</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,10 +1786,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578762</v>
+        <v>122578773</v>
       </c>
       <c r="B11" t="n">
-        <v>105422</v>
+        <v>99765</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1802,36 +1802,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707548</v>
+        <v>707489</v>
       </c>
       <c r="R11" t="n">
-        <v>6375014</v>
+        <v>6375140</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1878,11 +1878,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1894,7 +1889,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1912,10 +1907,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578780</v>
+        <v>122578821</v>
       </c>
       <c r="B12" t="n">
-        <v>99752</v>
+        <v>105435</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1928,27 +1923,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1957,13 +1961,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707626</v>
+        <v>707605</v>
       </c>
       <c r="R12" t="n">
-        <v>6375120</v>
+        <v>6374970</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1997,7 +2001,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2011,7 +2015,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2029,10 +2033,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578741</v>
+        <v>122578759</v>
       </c>
       <c r="B13" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2062,20 +2066,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707609</v>
+        <v>707557</v>
       </c>
       <c r="R13" t="n">
-        <v>6375033</v>
+        <v>6375009</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2109,7 +2127,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2141,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578796</v>
+        <v>122578797</v>
       </c>
       <c r="B14" t="n">
-        <v>99752</v>
+        <v>98215</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2153,28 +2171,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2222,11 +2249,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2258,10 +2280,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578775</v>
+        <v>122578774</v>
       </c>
       <c r="B15" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2293,7 +2315,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2312,13 +2334,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707564</v>
+        <v>707528</v>
       </c>
       <c r="R15" t="n">
-        <v>6375169</v>
+        <v>6375154</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2361,7 +2383,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2379,10 +2401,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578769</v>
+        <v>122578749</v>
       </c>
       <c r="B16" t="n">
-        <v>99752</v>
+        <v>105435</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2395,36 +2417,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2433,13 +2455,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707513</v>
+        <v>707570</v>
       </c>
       <c r="R16" t="n">
-        <v>6375053</v>
+        <v>6374984</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2473,7 +2495,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2487,7 +2509,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2505,10 +2527,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578771</v>
+        <v>122578744</v>
       </c>
       <c r="B17" t="n">
-        <v>98202</v>
+        <v>105435</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2517,30 +2539,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2550,7 +2572,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2559,13 +2581,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707490</v>
+        <v>707626</v>
       </c>
       <c r="R17" t="n">
-        <v>6375090</v>
+        <v>6375071</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2599,7 +2621,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2613,7 +2635,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2631,10 +2653,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578811</v>
+        <v>122578802</v>
       </c>
       <c r="B18" t="n">
-        <v>98202</v>
+        <v>98215</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2666,7 +2688,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2685,10 +2707,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707652</v>
+        <v>707697</v>
       </c>
       <c r="R18" t="n">
-        <v>6374986</v>
+        <v>6374969</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2752,10 +2774,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578810</v>
+        <v>122578742</v>
       </c>
       <c r="B19" t="n">
-        <v>99752</v>
+        <v>105435</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2768,42 +2790,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707652</v>
+        <v>707638</v>
       </c>
       <c r="R19" t="n">
-        <v>6374986</v>
+        <v>6375036</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2837,7 +2854,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2869,10 +2886,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578757</v>
+        <v>122578758</v>
       </c>
       <c r="B20" t="n">
-        <v>98202</v>
+        <v>105435</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2881,40 +2898,40 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2995,10 +3012,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578747</v>
+        <v>122578813</v>
       </c>
       <c r="B21" t="n">
-        <v>105422</v>
+        <v>99765</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3011,34 +3028,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707590</v>
+        <v>707646</v>
       </c>
       <c r="R21" t="n">
-        <v>6375036</v>
+        <v>6374967</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3075,7 +3097,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3107,10 +3129,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578783</v>
+        <v>122578819</v>
       </c>
       <c r="B22" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3140,7 +3162,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3152,13 +3183,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707633</v>
+        <v>707605</v>
       </c>
       <c r="R22" t="n">
-        <v>6375094</v>
+        <v>6374982</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3192,7 +3223,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3206,7 +3237,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3224,10 +3255,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578817</v>
+        <v>122578741</v>
       </c>
       <c r="B23" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3257,34 +3288,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707624</v>
+        <v>707609</v>
       </c>
       <c r="R23" t="n">
-        <v>6374996</v>
+        <v>6375033</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3318,7 +3335,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3350,10 +3367,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578814</v>
+        <v>122578776</v>
       </c>
       <c r="B24" t="n">
-        <v>98202</v>
+        <v>99765</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3362,35 +3379,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3404,13 +3421,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707638</v>
+        <v>707584</v>
       </c>
       <c r="R24" t="n">
-        <v>6374988</v>
+        <v>6375172</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3453,7 +3470,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3471,10 +3488,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578752</v>
+        <v>122578779</v>
       </c>
       <c r="B25" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3504,16 +3521,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3525,13 +3533,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707569</v>
+        <v>707597</v>
       </c>
       <c r="R25" t="n">
-        <v>6374979</v>
+        <v>6375142</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3565,7 +3573,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Enstaka strå.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3579,7 +3587,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3597,10 +3605,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578744</v>
+        <v>122578775</v>
       </c>
       <c r="B26" t="n">
-        <v>105422</v>
+        <v>99765</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3613,26 +3621,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3642,7 +3650,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3651,10 +3659,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707626</v>
+        <v>707564</v>
       </c>
       <c r="R26" t="n">
-        <v>6375071</v>
+        <v>6375169</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3689,11 +3697,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Stensamling, grav? Nära.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3705,7 +3708,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3723,10 +3726,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578797</v>
+        <v>122578777</v>
       </c>
       <c r="B27" t="n">
-        <v>98202</v>
+        <v>99765</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3735,25 +3738,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3763,7 +3766,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3777,13 +3780,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707725</v>
+        <v>707591</v>
       </c>
       <c r="R27" t="n">
-        <v>6374976</v>
+        <v>6375187</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3815,6 +3818,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>30 m S åker i N.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3826,7 +3834,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3844,10 +3852,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578756</v>
+        <v>122578815</v>
       </c>
       <c r="B28" t="n">
-        <v>99752</v>
+        <v>105435</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3860,36 +3868,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3898,13 +3897,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707541</v>
+        <v>707638</v>
       </c>
       <c r="R28" t="n">
-        <v>6374993</v>
+        <v>6374988</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3938,7 +3937,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3970,10 +3969,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578740</v>
+        <v>122578803</v>
       </c>
       <c r="B29" t="n">
-        <v>105422</v>
+        <v>105435</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4004,19 +4003,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707609</v>
+        <v>707697</v>
       </c>
       <c r="R29" t="n">
-        <v>6375033</v>
+        <v>6374980</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4050,7 +4054,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4082,10 +4086,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578764</v>
+        <v>122578769</v>
       </c>
       <c r="B30" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4117,7 +4121,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4136,13 +4140,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707538</v>
+        <v>707513</v>
       </c>
       <c r="R30" t="n">
-        <v>6375024</v>
+        <v>6375053</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4176,7 +4180,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4190,7 +4194,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4208,10 +4212,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578770</v>
+        <v>122578760</v>
       </c>
       <c r="B31" t="n">
-        <v>99752</v>
+        <v>105435</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4224,36 +4228,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4262,13 +4266,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707506</v>
+        <v>707547</v>
       </c>
       <c r="R31" t="n">
-        <v>6375077</v>
+        <v>6375010</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4302,7 +4306,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4316,7 +4320,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4334,10 +4338,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578755</v>
+        <v>122578782</v>
       </c>
       <c r="B32" t="n">
-        <v>98202</v>
+        <v>98215</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4369,7 +4373,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4388,13 +4392,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707541</v>
+        <v>707621</v>
       </c>
       <c r="R32" t="n">
-        <v>6374993</v>
+        <v>6375108</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4424,11 +4428,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4460,10 +4459,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578802</v>
+        <v>122578762</v>
       </c>
       <c r="B33" t="n">
-        <v>98202</v>
+        <v>105435</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4472,40 +4471,40 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4514,13 +4513,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707697</v>
+        <v>707548</v>
       </c>
       <c r="R33" t="n">
-        <v>6374969</v>
+        <v>6375014</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4550,6 +4549,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4581,10 +4585,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578825</v>
+        <v>122578814</v>
       </c>
       <c r="B34" t="n">
-        <v>99752</v>
+        <v>98215</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4593,35 +4597,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4635,10 +4639,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707611</v>
+        <v>707638</v>
       </c>
       <c r="R34" t="n">
-        <v>6374954</v>
+        <v>6374988</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4684,7 +4688,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4702,10 +4706,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578804</v>
+        <v>122578817</v>
       </c>
       <c r="B35" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4735,7 +4739,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4747,10 +4760,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707697</v>
+        <v>707624</v>
       </c>
       <c r="R35" t="n">
-        <v>6374980</v>
+        <v>6374996</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4787,7 +4800,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4819,10 +4832,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578773</v>
+        <v>122578812</v>
       </c>
       <c r="B36" t="n">
-        <v>99752</v>
+        <v>105435</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4835,36 +4848,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4873,13 +4877,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707489</v>
+        <v>707646</v>
       </c>
       <c r="R36" t="n">
-        <v>6375140</v>
+        <v>6374967</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4911,6 +4915,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4922,7 +4931,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4940,10 +4949,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578748</v>
+        <v>122578765</v>
       </c>
       <c r="B37" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4974,19 +4983,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707590</v>
+        <v>707532</v>
       </c>
       <c r="R37" t="n">
-        <v>6375036</v>
+        <v>6375035</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5020,7 +5034,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5052,10 +5066,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578750</v>
+        <v>122578763</v>
       </c>
       <c r="B38" t="n">
-        <v>98246</v>
+        <v>99765</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5064,35 +5078,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5106,10 +5120,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707569</v>
+        <v>707548</v>
       </c>
       <c r="R38" t="n">
-        <v>6374979</v>
+        <v>6375014</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -5178,10 +5192,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578808</v>
+        <v>122578809</v>
       </c>
       <c r="B39" t="n">
-        <v>98202</v>
+        <v>105435</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5190,40 +5204,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5232,10 +5237,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707678</v>
+        <v>707652</v>
       </c>
       <c r="R39" t="n">
-        <v>6374990</v>
+        <v>6374986</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5268,6 +5273,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5299,10 +5309,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578766</v>
+        <v>122578778</v>
       </c>
       <c r="B40" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5334,12 +5344,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5353,13 +5363,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707548</v>
+        <v>707599</v>
       </c>
       <c r="R40" t="n">
-        <v>6375091</v>
+        <v>6375165</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5393,7 +5403,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5407,7 +5417,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5425,10 +5435,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578765</v>
+        <v>122578770</v>
       </c>
       <c r="B41" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5458,7 +5468,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5470,13 +5489,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707532</v>
+        <v>707506</v>
       </c>
       <c r="R41" t="n">
-        <v>6375035</v>
+        <v>6375077</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5510,7 +5529,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5524,7 +5543,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5542,10 +5561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578772</v>
+        <v>122578823</v>
       </c>
       <c r="B42" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5577,7 +5596,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5596,13 +5615,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707506</v>
+        <v>707605</v>
       </c>
       <c r="R42" t="n">
-        <v>6375110</v>
+        <v>6374970</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5636,7 +5655,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5650,7 +5669,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5668,10 +5687,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578816</v>
+        <v>122578804</v>
       </c>
       <c r="B43" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5713,10 +5732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707638</v>
+        <v>707697</v>
       </c>
       <c r="R43" t="n">
-        <v>6374988</v>
+        <v>6374980</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5753,7 +5772,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5785,10 +5804,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578763</v>
+        <v>122578764</v>
       </c>
       <c r="B44" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5820,7 +5839,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5839,13 +5858,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707548</v>
+        <v>707538</v>
       </c>
       <c r="R44" t="n">
-        <v>6375014</v>
+        <v>6375024</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5911,10 +5930,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578819</v>
+        <v>122578772</v>
       </c>
       <c r="B45" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5946,7 +5965,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5965,13 +5984,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707605</v>
+        <v>707506</v>
       </c>
       <c r="R45" t="n">
-        <v>6374982</v>
+        <v>6375110</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6005,7 +6024,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6019,7 +6038,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6037,10 +6056,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578813</v>
+        <v>122578805</v>
       </c>
       <c r="B46" t="n">
-        <v>99752</v>
+        <v>98215</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6049,28 +6068,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6082,10 +6110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707646</v>
+        <v>707697</v>
       </c>
       <c r="R46" t="n">
-        <v>6374967</v>
+        <v>6374980</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6118,11 +6146,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6154,10 +6177,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578754</v>
+        <v>122578756</v>
       </c>
       <c r="B47" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6189,7 +6212,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6208,13 +6231,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707554</v>
+        <v>707541</v>
       </c>
       <c r="R47" t="n">
-        <v>6374978</v>
+        <v>6374993</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6280,10 +6303,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578760</v>
+        <v>122578825</v>
       </c>
       <c r="B48" t="n">
-        <v>105422</v>
+        <v>99765</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6296,36 +6319,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6334,10 +6357,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707547</v>
+        <v>707611</v>
       </c>
       <c r="R48" t="n">
-        <v>6375010</v>
+        <v>6374954</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6372,11 +6395,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6388,7 +6406,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6406,10 +6424,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578824</v>
+        <v>122578746</v>
       </c>
       <c r="B49" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6439,34 +6457,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707606</v>
+        <v>707626</v>
       </c>
       <c r="R49" t="n">
-        <v>6374961</v>
+        <v>6375071</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6498,6 +6502,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Stensamling, grav? Nära.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6509,7 +6518,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6527,10 +6536,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578742</v>
+        <v>122578785</v>
       </c>
       <c r="B50" t="n">
-        <v>105422</v>
+        <v>105435</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6561,19 +6570,24 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707638</v>
+        <v>707648</v>
       </c>
       <c r="R50" t="n">
-        <v>6375036</v>
+        <v>6375072</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6607,7 +6621,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6639,10 +6653,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578806</v>
+        <v>122578786</v>
       </c>
       <c r="B51" t="n">
-        <v>105422</v>
+        <v>98215</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6651,31 +6665,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6684,10 +6707,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707678</v>
+        <v>707652</v>
       </c>
       <c r="R51" t="n">
-        <v>6374990</v>
+        <v>6375083</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6724,7 +6747,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6756,10 +6779,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578758</v>
+        <v>122578747</v>
       </c>
       <c r="B52" t="n">
-        <v>105422</v>
+        <v>105435</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6789,34 +6812,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707557</v>
+        <v>707590</v>
       </c>
       <c r="R52" t="n">
-        <v>6375009</v>
+        <v>6375036</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6850,7 +6859,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6882,10 +6891,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578805</v>
+        <v>122578783</v>
       </c>
       <c r="B53" t="n">
-        <v>98202</v>
+        <v>99765</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6894,37 +6903,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6936,13 +6936,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707697</v>
+        <v>707633</v>
       </c>
       <c r="R53" t="n">
-        <v>6374980</v>
+        <v>6375094</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6972,6 +6972,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7003,10 +7008,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578746</v>
+        <v>122578755</v>
       </c>
       <c r="B54" t="n">
-        <v>99752</v>
+        <v>98215</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7015,41 +7020,55 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707626</v>
+        <v>707541</v>
       </c>
       <c r="R54" t="n">
-        <v>6375071</v>
+        <v>6374993</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7083,7 +7102,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7115,10 +7134,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578753</v>
+        <v>122578781</v>
       </c>
       <c r="B55" t="n">
-        <v>98202</v>
+        <v>99765</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7127,37 +7146,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7169,10 +7179,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707554</v>
+        <v>707621</v>
       </c>
       <c r="R55" t="n">
-        <v>6374978</v>
+        <v>6375108</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7209,7 +7219,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7241,10 +7251,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578777</v>
+        <v>122578780</v>
       </c>
       <c r="B56" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7274,16 +7284,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7295,13 +7296,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707591</v>
+        <v>707626</v>
       </c>
       <c r="R56" t="n">
-        <v>6375187</v>
+        <v>6375120</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7335,7 +7336,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>30 m S åker i N.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7349,7 +7350,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7367,10 +7368,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578809</v>
+        <v>122578806</v>
       </c>
       <c r="B57" t="n">
-        <v>105422</v>
+        <v>105435</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7412,10 +7413,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707652</v>
+        <v>707678</v>
       </c>
       <c r="R57" t="n">
-        <v>6374986</v>
+        <v>6374990</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7484,10 +7485,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578786</v>
+        <v>122578743</v>
       </c>
       <c r="B58" t="n">
-        <v>98202</v>
+        <v>99765</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7496,55 +7497,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707652</v>
+        <v>707638</v>
       </c>
       <c r="R58" t="n">
-        <v>6375083</v>
+        <v>6375036</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7578,7 +7565,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7610,10 +7597,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578782</v>
+        <v>122578818</v>
       </c>
       <c r="B59" t="n">
-        <v>98202</v>
+        <v>105435</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7622,40 +7609,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7664,10 +7651,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707621</v>
+        <v>707605</v>
       </c>
       <c r="R59" t="n">
-        <v>6375108</v>
+        <v>6374982</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7702,6 +7689,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7713,7 +7705,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7731,10 +7723,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578778</v>
+        <v>122578748</v>
       </c>
       <c r="B60" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7764,34 +7756,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707599</v>
+        <v>707590</v>
       </c>
       <c r="R60" t="n">
-        <v>6375165</v>
+        <v>6375036</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7825,7 +7803,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Barrblandskog mot åker i N.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7839,7 +7817,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7857,10 +7835,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578779</v>
+        <v>122578807</v>
       </c>
       <c r="B61" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7902,13 +7880,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707597</v>
+        <v>707678</v>
       </c>
       <c r="R61" t="n">
-        <v>6375142</v>
+        <v>6374990</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7942,7 +7920,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,7 +7934,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7974,10 +7952,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578776</v>
+        <v>122578824</v>
       </c>
       <c r="B62" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8009,7 +7987,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8028,13 +8006,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707584</v>
+        <v>707606</v>
       </c>
       <c r="R62" t="n">
-        <v>6375172</v>
+        <v>6374961</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8077,7 +8055,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8095,10 +8073,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578803</v>
+        <v>122578816</v>
       </c>
       <c r="B63" t="n">
-        <v>105422</v>
+        <v>99765</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8111,27 +8089,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8140,10 +8118,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707697</v>
+        <v>707638</v>
       </c>
       <c r="R63" t="n">
-        <v>6374980</v>
+        <v>6374988</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8180,7 +8158,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8212,10 +8190,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578795</v>
+        <v>122578752</v>
       </c>
       <c r="B64" t="n">
-        <v>105422</v>
+        <v>99765</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8228,27 +8206,36 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8257,13 +8244,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707725</v>
+        <v>707569</v>
       </c>
       <c r="R64" t="n">
-        <v>6374976</v>
+        <v>6374979</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8297,7 +8284,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8329,10 +8316,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578784</v>
+        <v>122578796</v>
       </c>
       <c r="B65" t="n">
-        <v>99752</v>
+        <v>99765</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8374,10 +8361,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707648</v>
+        <v>707725</v>
       </c>
       <c r="R65" t="n">
-        <v>6375072</v>
+        <v>6374976</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8414,7 +8401,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8446,10 +8433,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578785</v>
+        <v>122578740</v>
       </c>
       <c r="B66" t="n">
-        <v>105422</v>
+        <v>105435</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8480,24 +8467,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707648</v>
+        <v>707609</v>
       </c>
       <c r="R66" t="n">
-        <v>6375072</v>
+        <v>6375033</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8531,7 +8513,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8563,10 +8545,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578818</v>
+        <v>122578771</v>
       </c>
       <c r="B67" t="n">
-        <v>105422</v>
+        <v>98215</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8575,40 +8557,40 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8617,13 +8599,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707605</v>
+        <v>707490</v>
       </c>
       <c r="R67" t="n">
-        <v>6374982</v>
+        <v>6375090</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8657,7 +8639,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8671,7 +8653,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8689,10 +8671,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578759</v>
+        <v>122578757</v>
       </c>
       <c r="B68" t="n">
-        <v>99752</v>
+        <v>98215</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8701,35 +8683,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8815,10 +8797,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578767</v>
+        <v>122578808</v>
       </c>
       <c r="B69" t="n">
-        <v>98246</v>
+        <v>98215</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8831,26 +8813,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8869,13 +8851,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707513</v>
+        <v>707678</v>
       </c>
       <c r="R69" t="n">
-        <v>6375053</v>
+        <v>6374990</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8918,7 +8900,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8936,10 +8918,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578815</v>
+        <v>122578766</v>
       </c>
       <c r="B70" t="n">
-        <v>105422</v>
+        <v>99765</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8952,27 +8934,36 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8981,13 +8972,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707638</v>
+        <v>707548</v>
       </c>
       <c r="R70" t="n">
-        <v>6374988</v>
+        <v>6375091</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9021,7 +9012,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9035,7 +9026,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9053,10 +9044,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578743</v>
+        <v>122578767</v>
       </c>
       <c r="B71" t="n">
-        <v>99752</v>
+        <v>98259</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9065,41 +9056,55 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707638</v>
+        <v>707513</v>
       </c>
       <c r="R71" t="n">
-        <v>6375036</v>
+        <v>6375053</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9131,11 +9136,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt söderut.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578754</v>
+        <v>122578741</v>
       </c>
       <c r="B3" t="n">
         <v>99765</v>
@@ -843,34 +843,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707554</v>
+        <v>707609</v>
       </c>
       <c r="R3" t="n">
-        <v>6374978</v>
+        <v>6375033</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,7 +922,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578753</v>
+        <v>122578808</v>
       </c>
       <c r="B4" t="n">
         <v>98215</v>
@@ -971,7 +957,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -990,10 +976,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707554</v>
+        <v>707678</v>
       </c>
       <c r="R4" t="n">
-        <v>6374978</v>
+        <v>6374990</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,11 +1012,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578811</v>
+        <v>122578758</v>
       </c>
       <c r="B5" t="n">
-        <v>98215</v>
+        <v>105435</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,40 +1055,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1116,13 +1097,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707652</v>
+        <v>707557</v>
       </c>
       <c r="R5" t="n">
-        <v>6374986</v>
+        <v>6375009</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1152,6 +1133,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578810</v>
+        <v>122578802</v>
       </c>
       <c r="B6" t="n">
-        <v>99765</v>
+        <v>98215</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,28 +1181,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1228,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707652</v>
+        <v>707697</v>
       </c>
       <c r="R6" t="n">
-        <v>6374986</v>
+        <v>6374969</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1264,11 +1259,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578750</v>
+        <v>122578782</v>
       </c>
       <c r="B7" t="n">
-        <v>98259</v>
+        <v>98215</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,26 +1306,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1354,13 +1344,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707569</v>
+        <v>707621</v>
       </c>
       <c r="R7" t="n">
-        <v>6374979</v>
+        <v>6375108</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1390,11 +1380,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,7 +1411,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578751</v>
+        <v>122578786</v>
       </c>
       <c r="B8" t="n">
         <v>98215</v>
@@ -1480,13 +1465,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707569</v>
+        <v>707652</v>
       </c>
       <c r="R8" t="n">
-        <v>6374979</v>
+        <v>6375083</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1520,7 +1505,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1552,7 +1537,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578784</v>
+        <v>122578804</v>
       </c>
       <c r="B9" t="n">
         <v>99765</v>
@@ -1597,10 +1582,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707648</v>
+        <v>707697</v>
       </c>
       <c r="R9" t="n">
-        <v>6375072</v>
+        <v>6374980</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1637,7 +1622,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,10 +1654,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578795</v>
+        <v>122578778</v>
       </c>
       <c r="B10" t="n">
-        <v>105435</v>
+        <v>99765</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,27 +1670,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1714,13 +1708,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707725</v>
+        <v>707599</v>
       </c>
       <c r="R10" t="n">
-        <v>6374976</v>
+        <v>6375165</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1754,7 +1748,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,7 +1762,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1786,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578773</v>
+        <v>122578755</v>
       </c>
       <c r="B11" t="n">
-        <v>99765</v>
+        <v>98215</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,35 +1792,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1840,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707489</v>
+        <v>707541</v>
       </c>
       <c r="R11" t="n">
-        <v>6375140</v>
+        <v>6374993</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1878,6 +1872,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1889,7 +1888,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1907,10 +1906,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578821</v>
+        <v>122578748</v>
       </c>
       <c r="B12" t="n">
-        <v>105435</v>
+        <v>99765</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1923,48 +1922,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707605</v>
+        <v>707590</v>
       </c>
       <c r="R12" t="n">
-        <v>6374970</v>
+        <v>6375036</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2001,7 +1986,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2015,7 +2000,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2033,10 +2018,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578759</v>
+        <v>122578800</v>
       </c>
       <c r="B13" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2049,36 +2034,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2087,13 +2072,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707557</v>
+        <v>707697</v>
       </c>
       <c r="R13" t="n">
-        <v>6375009</v>
+        <v>6374980</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2127,7 +2112,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2159,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578797</v>
+        <v>122578752</v>
       </c>
       <c r="B14" t="n">
-        <v>98215</v>
+        <v>99765</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,35 +2156,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2213,13 +2198,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707725</v>
+        <v>707569</v>
       </c>
       <c r="R14" t="n">
-        <v>6374976</v>
+        <v>6374979</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2249,6 +2234,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2280,10 +2270,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578774</v>
+        <v>122578818</v>
       </c>
       <c r="B15" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2296,36 +2286,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2334,13 +2324,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707528</v>
+        <v>707605</v>
       </c>
       <c r="R15" t="n">
-        <v>6375154</v>
+        <v>6374982</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2372,6 +2362,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2383,7 +2378,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2401,10 +2396,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578749</v>
+        <v>122578751</v>
       </c>
       <c r="B16" t="n">
-        <v>105435</v>
+        <v>98215</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2413,40 +2408,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2455,13 +2450,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707570</v>
+        <v>707569</v>
       </c>
       <c r="R16" t="n">
-        <v>6374984</v>
+        <v>6374979</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2527,7 +2522,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578744</v>
+        <v>122578742</v>
       </c>
       <c r="B17" t="n">
         <v>105435</v>
@@ -2560,31 +2555,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707626</v>
+        <v>707638</v>
       </c>
       <c r="R17" t="n">
-        <v>6375071</v>
+        <v>6375036</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2621,7 +2602,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2653,10 +2634,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578802</v>
+        <v>122578824</v>
       </c>
       <c r="B18" t="n">
-        <v>98215</v>
+        <v>99765</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2665,35 +2646,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2707,10 +2688,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707697</v>
+        <v>707606</v>
       </c>
       <c r="R18" t="n">
-        <v>6374969</v>
+        <v>6374961</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2756,7 +2737,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2774,7 +2755,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578742</v>
+        <v>122578747</v>
       </c>
       <c r="B19" t="n">
         <v>105435</v>
@@ -2814,13 +2795,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707638</v>
+        <v>707590</v>
       </c>
       <c r="R19" t="n">
         <v>6375036</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2854,7 +2835,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2886,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578758</v>
+        <v>122578784</v>
       </c>
       <c r="B20" t="n">
-        <v>105435</v>
+        <v>99765</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2902,36 +2883,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2940,13 +2912,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707557</v>
+        <v>707648</v>
       </c>
       <c r="R20" t="n">
-        <v>6375009</v>
+        <v>6375072</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2980,7 +2952,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3012,10 +2984,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578813</v>
+        <v>122578785</v>
       </c>
       <c r="B21" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3028,27 +3000,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3057,10 +3029,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707646</v>
+        <v>707648</v>
       </c>
       <c r="R21" t="n">
-        <v>6374967</v>
+        <v>6375072</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3097,7 +3069,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3129,7 +3101,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578819</v>
+        <v>122578773</v>
       </c>
       <c r="B22" t="n">
         <v>99765</v>
@@ -3164,7 +3136,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3183,13 +3155,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707605</v>
+        <v>707489</v>
       </c>
       <c r="R22" t="n">
-        <v>6374982</v>
+        <v>6375140</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3221,11 +3193,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minsta antal + spridd.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3237,7 +3204,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3255,10 +3222,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578741</v>
+        <v>122578767</v>
       </c>
       <c r="B23" t="n">
-        <v>99765</v>
+        <v>98259</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3267,41 +3234,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707609</v>
+        <v>707513</v>
       </c>
       <c r="R23" t="n">
-        <v>6375033</v>
+        <v>6375053</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3333,11 +3314,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3349,7 +3325,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3367,10 +3343,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578776</v>
+        <v>122578806</v>
       </c>
       <c r="B24" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3383,36 +3359,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3421,13 +3388,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707584</v>
+        <v>707678</v>
       </c>
       <c r="R24" t="n">
-        <v>6375172</v>
+        <v>6374990</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3459,6 +3426,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3470,7 +3442,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3488,7 +3460,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578779</v>
+        <v>122578765</v>
       </c>
       <c r="B25" t="n">
         <v>99765</v>
@@ -3533,13 +3505,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707597</v>
+        <v>707532</v>
       </c>
       <c r="R25" t="n">
-        <v>6375142</v>
+        <v>6375035</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3573,7 +3545,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3587,7 +3559,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3605,7 +3577,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578775</v>
+        <v>122578756</v>
       </c>
       <c r="B26" t="n">
         <v>99765</v>
@@ -3640,7 +3612,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3659,13 +3631,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707564</v>
+        <v>707541</v>
       </c>
       <c r="R26" t="n">
-        <v>6375169</v>
+        <v>6374993</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3697,6 +3669,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3708,7 +3685,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3726,7 +3703,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578777</v>
+        <v>122578766</v>
       </c>
       <c r="B27" t="n">
         <v>99765</v>
@@ -3761,12 +3738,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3780,13 +3757,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707591</v>
+        <v>707548</v>
       </c>
       <c r="R27" t="n">
-        <v>6375187</v>
+        <v>6375091</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3820,7 +3797,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>30 m S åker i N.</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3834,7 +3811,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3852,10 +3829,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578815</v>
+        <v>122578750</v>
       </c>
       <c r="B28" t="n">
-        <v>105435</v>
+        <v>98259</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3864,31 +3841,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>671</v>
+        <v>219862</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3897,13 +3883,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707638</v>
+        <v>707569</v>
       </c>
       <c r="R28" t="n">
-        <v>6374988</v>
+        <v>6374979</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3937,7 +3923,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3969,10 +3955,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578803</v>
+        <v>122578754</v>
       </c>
       <c r="B29" t="n">
-        <v>105435</v>
+        <v>99765</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3985,27 +3971,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4014,10 +4009,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707697</v>
+        <v>707554</v>
       </c>
       <c r="R29" t="n">
-        <v>6374980</v>
+        <v>6374978</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4054,7 +4049,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4086,7 +4081,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578769</v>
+        <v>122578813</v>
       </c>
       <c r="B30" t="n">
         <v>99765</v>
@@ -4119,16 +4114,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4140,13 +4126,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707513</v>
+        <v>707646</v>
       </c>
       <c r="R30" t="n">
-        <v>6375053</v>
+        <v>6374967</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4180,7 +4166,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4194,7 +4180,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4212,10 +4198,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578760</v>
+        <v>122578776</v>
       </c>
       <c r="B31" t="n">
-        <v>105435</v>
+        <v>99765</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4228,36 +4214,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4266,13 +4252,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707547</v>
+        <v>707584</v>
       </c>
       <c r="R31" t="n">
-        <v>6375010</v>
+        <v>6375172</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4304,11 +4290,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4320,7 +4301,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4338,7 +4319,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578782</v>
+        <v>122578797</v>
       </c>
       <c r="B32" t="n">
         <v>98215</v>
@@ -4373,7 +4354,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4392,10 +4373,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707621</v>
+        <v>707725</v>
       </c>
       <c r="R32" t="n">
-        <v>6375108</v>
+        <v>6374976</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4459,7 +4440,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578762</v>
+        <v>122578749</v>
       </c>
       <c r="B33" t="n">
         <v>105435</v>
@@ -4494,7 +4475,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4513,13 +4494,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707548</v>
+        <v>707570</v>
       </c>
       <c r="R33" t="n">
-        <v>6375014</v>
+        <v>6374984</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4585,10 +4566,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578814</v>
+        <v>122578744</v>
       </c>
       <c r="B34" t="n">
-        <v>98215</v>
+        <v>105435</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4597,40 +4578,40 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4639,13 +4620,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707638</v>
+        <v>707626</v>
       </c>
       <c r="R34" t="n">
-        <v>6374988</v>
+        <v>6375071</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4675,6 +4656,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4706,7 +4692,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578817</v>
+        <v>122578780</v>
       </c>
       <c r="B35" t="n">
         <v>99765</v>
@@ -4739,16 +4725,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4760,13 +4737,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707624</v>
+        <v>707626</v>
       </c>
       <c r="R35" t="n">
-        <v>6374996</v>
+        <v>6375120</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4800,7 +4777,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4832,10 +4809,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578812</v>
+        <v>122578769</v>
       </c>
       <c r="B36" t="n">
-        <v>105435</v>
+        <v>99765</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4848,27 +4825,36 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4877,13 +4863,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707646</v>
+        <v>707513</v>
       </c>
       <c r="R36" t="n">
-        <v>6374967</v>
+        <v>6375053</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4917,7 +4903,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4931,7 +4917,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4949,7 +4935,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578765</v>
+        <v>122578772</v>
       </c>
       <c r="B37" t="n">
         <v>99765</v>
@@ -4982,7 +4968,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4994,13 +4989,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707532</v>
+        <v>707506</v>
       </c>
       <c r="R37" t="n">
-        <v>6375035</v>
+        <v>6375110</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5034,7 +5029,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5048,7 +5043,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5066,10 +5061,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578763</v>
+        <v>122578805</v>
       </c>
       <c r="B38" t="n">
-        <v>99765</v>
+        <v>98215</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5078,35 +5073,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5120,13 +5115,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707548</v>
+        <v>707697</v>
       </c>
       <c r="R38" t="n">
-        <v>6375014</v>
+        <v>6374980</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5156,11 +5151,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5192,10 +5182,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578809</v>
+        <v>122578811</v>
       </c>
       <c r="B39" t="n">
-        <v>105435</v>
+        <v>98215</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5204,31 +5194,40 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5273,11 +5272,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5309,10 +5303,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578778</v>
+        <v>122578795</v>
       </c>
       <c r="B40" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5325,36 +5319,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5363,13 +5348,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707599</v>
+        <v>707725</v>
       </c>
       <c r="R40" t="n">
-        <v>6375165</v>
+        <v>6374976</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5403,7 +5388,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Barrblandskog mot åker i N.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5417,7 +5402,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5435,7 +5420,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578770</v>
+        <v>122578759</v>
       </c>
       <c r="B41" t="n">
         <v>99765</v>
@@ -5470,7 +5455,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5489,13 +5474,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707506</v>
+        <v>707557</v>
       </c>
       <c r="R41" t="n">
-        <v>6375077</v>
+        <v>6375009</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5529,7 +5514,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5543,7 +5528,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5561,7 +5546,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578823</v>
+        <v>122578817</v>
       </c>
       <c r="B42" t="n">
         <v>99765</v>
@@ -5596,7 +5581,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5615,10 +5600,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707605</v>
+        <v>707624</v>
       </c>
       <c r="R42" t="n">
-        <v>6374970</v>
+        <v>6374996</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5655,7 +5640,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5669,7 +5654,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5687,7 +5672,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578804</v>
+        <v>122578816</v>
       </c>
       <c r="B43" t="n">
         <v>99765</v>
@@ -5732,10 +5717,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707697</v>
+        <v>707638</v>
       </c>
       <c r="R43" t="n">
-        <v>6374980</v>
+        <v>6374988</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5772,7 +5757,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5804,10 +5789,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578764</v>
+        <v>122578753</v>
       </c>
       <c r="B44" t="n">
-        <v>99765</v>
+        <v>98215</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5816,35 +5801,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5858,13 +5843,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707538</v>
+        <v>707554</v>
       </c>
       <c r="R44" t="n">
-        <v>6375024</v>
+        <v>6374978</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5930,10 +5915,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578772</v>
+        <v>122578760</v>
       </c>
       <c r="B45" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5946,36 +5931,36 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5984,13 +5969,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707506</v>
+        <v>707547</v>
       </c>
       <c r="R45" t="n">
-        <v>6375110</v>
+        <v>6375010</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6024,7 +6009,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6038,7 +6023,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6056,10 +6041,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578805</v>
+        <v>122578746</v>
       </c>
       <c r="B46" t="n">
-        <v>98215</v>
+        <v>99765</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6068,55 +6053,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707697</v>
+        <v>707626</v>
       </c>
       <c r="R46" t="n">
-        <v>6374980</v>
+        <v>6375071</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6146,6 +6117,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6177,7 +6153,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578756</v>
+        <v>122578763</v>
       </c>
       <c r="B47" t="n">
         <v>99765</v>
@@ -6212,7 +6188,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6231,10 +6207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707541</v>
+        <v>707548</v>
       </c>
       <c r="R47" t="n">
-        <v>6374993</v>
+        <v>6375014</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -6303,7 +6279,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578825</v>
+        <v>122578796</v>
       </c>
       <c r="B48" t="n">
         <v>99765</v>
@@ -6336,16 +6312,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6357,10 +6324,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707611</v>
+        <v>707725</v>
       </c>
       <c r="R48" t="n">
-        <v>6374954</v>
+        <v>6374976</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6395,6 +6362,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6406,7 +6378,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6424,7 +6396,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578746</v>
+        <v>122578770</v>
       </c>
       <c r="B49" t="n">
         <v>99765</v>
@@ -6457,20 +6429,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707626</v>
+        <v>707506</v>
       </c>
       <c r="R49" t="n">
-        <v>6375071</v>
+        <v>6375077</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6504,7 +6490,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6518,7 +6504,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6536,10 +6522,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578785</v>
+        <v>122578771</v>
       </c>
       <c r="B50" t="n">
-        <v>105435</v>
+        <v>98215</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6548,31 +6534,40 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6581,13 +6576,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707648</v>
+        <v>707490</v>
       </c>
       <c r="R50" t="n">
-        <v>6375072</v>
+        <v>6375090</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6621,7 +6616,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6635,7 +6630,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6653,10 +6648,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578786</v>
+        <v>122578740</v>
       </c>
       <c r="B51" t="n">
-        <v>98215</v>
+        <v>105435</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6665,55 +6660,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707652</v>
+        <v>707609</v>
       </c>
       <c r="R51" t="n">
-        <v>6375083</v>
+        <v>6375033</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6747,7 +6728,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6779,10 +6760,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578747</v>
+        <v>122578764</v>
       </c>
       <c r="B52" t="n">
-        <v>105435</v>
+        <v>99765</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6795,37 +6776,51 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707590</v>
+        <v>707538</v>
       </c>
       <c r="R52" t="n">
-        <v>6375036</v>
+        <v>6375024</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6859,7 +6854,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6891,7 +6886,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578783</v>
+        <v>122578823</v>
       </c>
       <c r="B53" t="n">
         <v>99765</v>
@@ -6924,7 +6919,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6936,13 +6940,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707633</v>
+        <v>707605</v>
       </c>
       <c r="R53" t="n">
-        <v>6375094</v>
+        <v>6374970</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6976,7 +6980,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6990,7 +6994,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7008,10 +7012,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578755</v>
+        <v>122578807</v>
       </c>
       <c r="B54" t="n">
-        <v>98215</v>
+        <v>99765</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7020,37 +7024,28 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7062,13 +7057,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707541</v>
+        <v>707678</v>
       </c>
       <c r="R54" t="n">
-        <v>6374993</v>
+        <v>6374990</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7102,7 +7097,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7134,10 +7129,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578781</v>
+        <v>122578815</v>
       </c>
       <c r="B55" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7150,27 +7145,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7179,10 +7174,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707621</v>
+        <v>707638</v>
       </c>
       <c r="R55" t="n">
-        <v>6375108</v>
+        <v>6374988</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7219,7 +7214,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7251,7 +7246,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578780</v>
+        <v>122578775</v>
       </c>
       <c r="B56" t="n">
         <v>99765</v>
@@ -7284,7 +7279,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7296,13 +7300,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707626</v>
+        <v>707564</v>
       </c>
       <c r="R56" t="n">
-        <v>6375120</v>
+        <v>6375169</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7334,11 +7338,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7350,7 +7349,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7368,10 +7367,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578806</v>
+        <v>122578781</v>
       </c>
       <c r="B57" t="n">
-        <v>105435</v>
+        <v>99765</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7384,27 +7383,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7413,10 +7412,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707678</v>
+        <v>707621</v>
       </c>
       <c r="R57" t="n">
-        <v>6374990</v>
+        <v>6375108</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7453,7 +7452,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7485,7 +7484,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578743</v>
+        <v>122578777</v>
       </c>
       <c r="B58" t="n">
         <v>99765</v>
@@ -7518,20 +7517,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707638</v>
+        <v>707591</v>
       </c>
       <c r="R58" t="n">
-        <v>6375036</v>
+        <v>6375187</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7565,7 +7578,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>30 m S åker i N.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7579,7 +7592,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7597,10 +7610,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578818</v>
+        <v>122578783</v>
       </c>
       <c r="B59" t="n">
-        <v>105435</v>
+        <v>99765</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7613,36 +7626,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7651,13 +7655,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707605</v>
+        <v>707633</v>
       </c>
       <c r="R59" t="n">
-        <v>6374982</v>
+        <v>6375094</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7691,7 +7695,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7705,7 +7709,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7723,7 +7727,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578748</v>
+        <v>122578819</v>
       </c>
       <c r="B60" t="n">
         <v>99765</v>
@@ -7756,17 +7760,31 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707590</v>
+        <v>707605</v>
       </c>
       <c r="R60" t="n">
-        <v>6375036</v>
+        <v>6374982</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7803,7 +7821,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7817,7 +7835,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7835,7 +7853,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578807</v>
+        <v>122578810</v>
       </c>
       <c r="B61" t="n">
         <v>99765</v>
@@ -7880,10 +7898,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707678</v>
+        <v>707652</v>
       </c>
       <c r="R61" t="n">
-        <v>6374990</v>
+        <v>6374986</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7952,10 +7970,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578824</v>
+        <v>122578812</v>
       </c>
       <c r="B62" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7968,36 +7986,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8006,10 +8015,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707606</v>
+        <v>707646</v>
       </c>
       <c r="R62" t="n">
-        <v>6374961</v>
+        <v>6374967</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8044,6 +8053,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8055,7 +8069,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8073,10 +8087,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578816</v>
+        <v>122578809</v>
       </c>
       <c r="B63" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8089,27 +8103,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8118,10 +8132,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707638</v>
+        <v>707652</v>
       </c>
       <c r="R63" t="n">
-        <v>6374988</v>
+        <v>6374986</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8158,7 +8172,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8190,10 +8204,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578752</v>
+        <v>122578821</v>
       </c>
       <c r="B64" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8206,26 +8220,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8235,7 +8249,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8244,13 +8258,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707569</v>
+        <v>707605</v>
       </c>
       <c r="R64" t="n">
-        <v>6374979</v>
+        <v>6374970</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8284,7 +8298,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8298,7 +8312,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8316,7 +8330,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578796</v>
+        <v>122578743</v>
       </c>
       <c r="B65" t="n">
         <v>99765</v>
@@ -8350,24 +8364,19 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707725</v>
+        <v>707638</v>
       </c>
       <c r="R65" t="n">
-        <v>6374976</v>
+        <v>6375036</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8401,7 +8410,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8433,10 +8442,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578740</v>
+        <v>122578814</v>
       </c>
       <c r="B66" t="n">
-        <v>105435</v>
+        <v>98215</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8445,41 +8454,55 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707609</v>
+        <v>707638</v>
       </c>
       <c r="R66" t="n">
-        <v>6375033</v>
+        <v>6374988</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8509,11 +8532,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8545,10 +8563,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578771</v>
+        <v>122578774</v>
       </c>
       <c r="B67" t="n">
-        <v>98215</v>
+        <v>99765</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8557,30 +8575,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8599,13 +8617,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707490</v>
+        <v>707528</v>
       </c>
       <c r="R67" t="n">
-        <v>6375090</v>
+        <v>6375154</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8637,11 +8655,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>I långsträckt stensamlig, grav?</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8653,7 +8666,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8671,10 +8684,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578757</v>
+        <v>122578825</v>
       </c>
       <c r="B68" t="n">
-        <v>98215</v>
+        <v>99765</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8683,35 +8696,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8725,13 +8738,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707557</v>
+        <v>707611</v>
       </c>
       <c r="R68" t="n">
-        <v>6375009</v>
+        <v>6374954</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8763,11 +8776,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8779,7 +8787,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8797,10 +8805,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578808</v>
+        <v>122578762</v>
       </c>
       <c r="B69" t="n">
-        <v>98215</v>
+        <v>105435</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8809,40 +8817,40 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8851,13 +8859,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707678</v>
+        <v>707548</v>
       </c>
       <c r="R69" t="n">
-        <v>6374990</v>
+        <v>6375014</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8887,6 +8895,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8918,7 +8931,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578766</v>
+        <v>122578779</v>
       </c>
       <c r="B70" t="n">
         <v>99765</v>
@@ -8951,16 +8964,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8972,13 +8976,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707548</v>
+        <v>707597</v>
       </c>
       <c r="R70" t="n">
-        <v>6375091</v>
+        <v>6375142</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9012,7 +9016,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+          <t>Enstaka strå.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9026,7 +9030,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9044,10 +9048,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578767</v>
+        <v>122578757</v>
       </c>
       <c r="B71" t="n">
-        <v>98259</v>
+        <v>98215</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9060,26 +9064,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9098,13 +9102,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707513</v>
+        <v>707557</v>
       </c>
       <c r="R71" t="n">
-        <v>6375053</v>
+        <v>6375009</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9136,6 +9140,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9147,7 +9156,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578755</v>
+        <v>122578748</v>
       </c>
       <c r="B11" t="n">
-        <v>98215</v>
+        <v>99765</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,55 +1792,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707541</v>
+        <v>707590</v>
       </c>
       <c r="R11" t="n">
-        <v>6374993</v>
+        <v>6375036</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1874,7 +1860,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,10 +1892,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578748</v>
+        <v>122578800</v>
       </c>
       <c r="B12" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1922,34 +1908,48 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707590</v>
+        <v>707697</v>
       </c>
       <c r="R12" t="n">
-        <v>6375036</v>
+        <v>6374980</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,10 +2018,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578800</v>
+        <v>122578752</v>
       </c>
       <c r="B13" t="n">
-        <v>105435</v>
+        <v>99765</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2034,36 +2034,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707697</v>
+        <v>707569</v>
       </c>
       <c r="R13" t="n">
-        <v>6374980</v>
+        <v>6374979</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Inget i tallplantager mot S och O.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578752</v>
+        <v>122578818</v>
       </c>
       <c r="B14" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,36 +2160,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707569</v>
+        <v>707605</v>
       </c>
       <c r="R14" t="n">
-        <v>6374979</v>
+        <v>6374982</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578818</v>
+        <v>122578755</v>
       </c>
       <c r="B15" t="n">
-        <v>105435</v>
+        <v>98215</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2282,40 +2282,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707605</v>
+        <v>707541</v>
       </c>
       <c r="R15" t="n">
-        <v>6374982</v>
+        <v>6374993</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578812</v>
+        <v>122578743</v>
       </c>
       <c r="B62" t="n">
-        <v>105435</v>
+        <v>99765</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7986,42 +7986,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707646</v>
+        <v>707638</v>
       </c>
       <c r="R62" t="n">
-        <v>6374967</v>
+        <v>6375036</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8055,7 +8050,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8087,7 +8082,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578809</v>
+        <v>122578812</v>
       </c>
       <c r="B63" t="n">
         <v>105435</v>
@@ -8132,10 +8127,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707652</v>
+        <v>707646</v>
       </c>
       <c r="R63" t="n">
-        <v>6374986</v>
+        <v>6374967</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8172,7 +8167,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8204,7 +8199,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578821</v>
+        <v>122578809</v>
       </c>
       <c r="B64" t="n">
         <v>105435</v>
@@ -8237,16 +8232,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -8258,10 +8244,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707605</v>
+        <v>707652</v>
       </c>
       <c r="R64" t="n">
-        <v>6374970</v>
+        <v>6374986</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8298,7 +8284,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8312,7 +8298,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8330,10 +8316,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578743</v>
+        <v>122578821</v>
       </c>
       <c r="B65" t="n">
-        <v>99765</v>
+        <v>105435</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8346,37 +8332,51 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707638</v>
+        <v>707605</v>
       </c>
       <c r="R65" t="n">
-        <v>6375036</v>
+        <v>6374970</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578741</v>
+        <v>122578813</v>
       </c>
       <c r="B3" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -844,19 +844,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707609</v>
+        <v>707646</v>
       </c>
       <c r="R3" t="n">
-        <v>6375033</v>
+        <v>6374967</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578808</v>
+        <v>122578772</v>
       </c>
       <c r="B4" t="n">
-        <v>98215</v>
+        <v>99768</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,35 +939,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -976,13 +981,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707678</v>
+        <v>707506</v>
       </c>
       <c r="R4" t="n">
-        <v>6374990</v>
+        <v>6375110</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,6 +1019,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1025,7 +1035,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1043,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578758</v>
+        <v>122578819</v>
       </c>
       <c r="B5" t="n">
-        <v>105435</v>
+        <v>99768</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,36 +1069,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1097,13 +1107,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707557</v>
+        <v>707605</v>
       </c>
       <c r="R5" t="n">
-        <v>6375009</v>
+        <v>6374982</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1137,7 +1147,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1161,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1169,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578802</v>
+        <v>122578818</v>
       </c>
       <c r="B6" t="n">
-        <v>98215</v>
+        <v>105438</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,40 +1191,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1223,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707697</v>
+        <v>707605</v>
       </c>
       <c r="R6" t="n">
-        <v>6374969</v>
+        <v>6374982</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1261,6 +1271,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1272,7 +1287,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1290,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578782</v>
+        <v>122578808</v>
       </c>
       <c r="B7" t="n">
-        <v>98215</v>
+        <v>98218</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1344,10 +1359,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707621</v>
+        <v>707678</v>
       </c>
       <c r="R7" t="n">
-        <v>6375108</v>
+        <v>6374990</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1411,10 +1426,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578786</v>
+        <v>122578757</v>
       </c>
       <c r="B8" t="n">
-        <v>98215</v>
+        <v>98218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1446,7 +1461,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1465,13 +1480,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707652</v>
+        <v>707557</v>
       </c>
       <c r="R8" t="n">
-        <v>6375083</v>
+        <v>6375009</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,7 +1520,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,10 +1552,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578804</v>
+        <v>122578800</v>
       </c>
       <c r="B9" t="n">
-        <v>99765</v>
+        <v>105438</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,27 +1568,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1622,7 +1646,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578778</v>
+        <v>122578769</v>
       </c>
       <c r="B10" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,7 +1713,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1708,13 +1732,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707599</v>
+        <v>707513</v>
       </c>
       <c r="R10" t="n">
-        <v>6375165</v>
+        <v>6375053</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1748,7 +1772,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Barrblandskog mot åker i N.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1780,10 +1804,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578748</v>
+        <v>122578809</v>
       </c>
       <c r="B11" t="n">
-        <v>99765</v>
+        <v>105438</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,34 +1820,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707590</v>
+        <v>707652</v>
       </c>
       <c r="R11" t="n">
-        <v>6375036</v>
+        <v>6374986</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1892,10 +1921,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578800</v>
+        <v>122578802</v>
       </c>
       <c r="B12" t="n">
-        <v>105435</v>
+        <v>98218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1904,40 +1933,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1949,7 +1978,7 @@
         <v>707697</v>
       </c>
       <c r="R12" t="n">
-        <v>6374980</v>
+        <v>6374969</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1982,11 +2011,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,10 +2042,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578752</v>
+        <v>122578776</v>
       </c>
       <c r="B13" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2053,7 +2077,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2072,13 +2096,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707569</v>
+        <v>707584</v>
       </c>
       <c r="R13" t="n">
-        <v>6374979</v>
+        <v>6375172</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2110,11 +2134,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2126,7 +2145,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2144,10 +2163,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578818</v>
+        <v>122578807</v>
       </c>
       <c r="B14" t="n">
-        <v>105435</v>
+        <v>99768</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,36 +2179,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2198,10 +2208,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707605</v>
+        <v>707678</v>
       </c>
       <c r="R14" t="n">
-        <v>6374982</v>
+        <v>6374990</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2238,7 +2248,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2252,7 +2262,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2270,10 +2280,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578755</v>
+        <v>122578801</v>
       </c>
       <c r="B15" t="n">
-        <v>98215</v>
+        <v>99768</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2282,37 +2292,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2324,13 +2325,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707541</v>
+        <v>707697</v>
       </c>
       <c r="R15" t="n">
-        <v>6374993</v>
+        <v>6374980</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2364,7 +2365,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2396,10 +2397,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578751</v>
+        <v>122578779</v>
       </c>
       <c r="B16" t="n">
-        <v>98215</v>
+        <v>99768</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2408,37 +2409,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2450,13 +2442,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707569</v>
+        <v>707597</v>
       </c>
       <c r="R16" t="n">
-        <v>6374979</v>
+        <v>6375142</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2490,7 +2482,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Enstaka strå.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2504,7 +2496,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2522,10 +2514,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578742</v>
+        <v>122578771</v>
       </c>
       <c r="B17" t="n">
-        <v>105435</v>
+        <v>98218</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2534,41 +2526,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707638</v>
+        <v>707490</v>
       </c>
       <c r="R17" t="n">
-        <v>6375036</v>
+        <v>6375090</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2602,7 +2608,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2616,7 +2622,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2634,10 +2640,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578824</v>
+        <v>122578763</v>
       </c>
       <c r="B18" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2669,7 +2675,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2688,13 +2694,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707606</v>
+        <v>707548</v>
       </c>
       <c r="R18" t="n">
-        <v>6374961</v>
+        <v>6375014</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2726,6 +2732,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2737,7 +2748,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2755,10 +2766,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578747</v>
+        <v>122578775</v>
       </c>
       <c r="B19" t="n">
-        <v>105435</v>
+        <v>99768</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2771,37 +2782,51 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707590</v>
+        <v>707564</v>
       </c>
       <c r="R19" t="n">
-        <v>6375036</v>
+        <v>6375169</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2833,11 +2858,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2849,7 +2869,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2867,10 +2887,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578784</v>
+        <v>122578785</v>
       </c>
       <c r="B20" t="n">
-        <v>99765</v>
+        <v>105438</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2883,27 +2903,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2984,10 +3004,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578785</v>
+        <v>122578770</v>
       </c>
       <c r="B21" t="n">
-        <v>105435</v>
+        <v>99768</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3000,27 +3020,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3029,13 +3058,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707648</v>
+        <v>707506</v>
       </c>
       <c r="R21" t="n">
-        <v>6375072</v>
+        <v>6375077</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3069,7 +3098,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3083,7 +3112,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3101,10 +3130,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578773</v>
+        <v>122578751</v>
       </c>
       <c r="B22" t="n">
-        <v>99765</v>
+        <v>98218</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3113,35 +3142,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3155,10 +3184,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707489</v>
+        <v>707569</v>
       </c>
       <c r="R22" t="n">
-        <v>6375140</v>
+        <v>6374979</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3193,6 +3222,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3204,7 +3238,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3225,7 +3259,7 @@
         <v>122578767</v>
       </c>
       <c r="B23" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3343,10 +3377,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578806</v>
+        <v>122578810</v>
       </c>
       <c r="B24" t="n">
-        <v>105435</v>
+        <v>99768</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3359,27 +3393,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3388,10 +3422,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707678</v>
+        <v>707652</v>
       </c>
       <c r="R24" t="n">
-        <v>6374990</v>
+        <v>6374986</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3460,10 +3494,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578765</v>
+        <v>122578811</v>
       </c>
       <c r="B25" t="n">
-        <v>99765</v>
+        <v>98218</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3472,28 +3506,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3505,13 +3548,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707532</v>
+        <v>707652</v>
       </c>
       <c r="R25" t="n">
-        <v>6375035</v>
+        <v>6374986</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3541,11 +3584,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3577,10 +3615,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578756</v>
+        <v>122578744</v>
       </c>
       <c r="B26" t="n">
-        <v>99765</v>
+        <v>105438</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3593,26 +3631,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3622,7 +3660,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3631,13 +3669,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707541</v>
+        <v>707626</v>
       </c>
       <c r="R26" t="n">
-        <v>6374993</v>
+        <v>6375071</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3671,7 +3709,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3703,10 +3741,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578766</v>
+        <v>122578780</v>
       </c>
       <c r="B27" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3736,16 +3774,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3757,13 +3786,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707548</v>
+        <v>707626</v>
       </c>
       <c r="R27" t="n">
-        <v>6375091</v>
+        <v>6375120</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3797,7 +3826,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3811,7 +3840,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3829,10 +3858,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578750</v>
+        <v>122578743</v>
       </c>
       <c r="B28" t="n">
-        <v>98259</v>
+        <v>99768</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3841,55 +3870,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707569</v>
+        <v>707638</v>
       </c>
       <c r="R28" t="n">
-        <v>6374979</v>
+        <v>6375036</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3923,7 +3938,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3955,10 +3970,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578754</v>
+        <v>122578753</v>
       </c>
       <c r="B29" t="n">
-        <v>99765</v>
+        <v>98218</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3967,35 +3982,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4081,10 +4096,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578813</v>
+        <v>122578747</v>
       </c>
       <c r="B30" t="n">
-        <v>99765</v>
+        <v>105438</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4097,39 +4112,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707646</v>
+        <v>707590</v>
       </c>
       <c r="R30" t="n">
-        <v>6374967</v>
+        <v>6375036</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4166,7 +4176,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4198,10 +4208,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578776</v>
+        <v>122578765</v>
       </c>
       <c r="B31" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4231,16 +4241,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4252,13 +4253,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707584</v>
+        <v>707532</v>
       </c>
       <c r="R31" t="n">
-        <v>6375172</v>
+        <v>6375035</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4290,6 +4291,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spridd glest mot O-N.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4301,7 +4307,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4319,10 +4325,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578797</v>
+        <v>122578777</v>
       </c>
       <c r="B32" t="n">
-        <v>98215</v>
+        <v>99768</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4331,25 +4337,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4359,7 +4365,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4373,13 +4379,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707725</v>
+        <v>707591</v>
       </c>
       <c r="R32" t="n">
-        <v>6374976</v>
+        <v>6375187</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4411,6 +4417,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>30 m S åker i N.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4422,7 +4433,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4440,10 +4451,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578749</v>
+        <v>122578750</v>
       </c>
       <c r="B33" t="n">
-        <v>105435</v>
+        <v>98262</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4452,40 +4463,40 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>671</v>
+        <v>219862</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4494,13 +4505,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707570</v>
+        <v>707569</v>
       </c>
       <c r="R33" t="n">
-        <v>6374984</v>
+        <v>6374979</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4566,10 +4577,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578744</v>
+        <v>122578748</v>
       </c>
       <c r="B34" t="n">
-        <v>105435</v>
+        <v>99768</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4582,51 +4593,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707626</v>
+        <v>707590</v>
       </c>
       <c r="R34" t="n">
-        <v>6375071</v>
+        <v>6375036</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4660,7 +4657,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4692,10 +4689,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578780</v>
+        <v>122578762</v>
       </c>
       <c r="B35" t="n">
-        <v>99765</v>
+        <v>105438</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4708,27 +4705,36 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4737,13 +4743,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707626</v>
+        <v>707548</v>
       </c>
       <c r="R35" t="n">
-        <v>6375120</v>
+        <v>6375014</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4777,7 +4783,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4809,10 +4815,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578769</v>
+        <v>122578795</v>
       </c>
       <c r="B36" t="n">
-        <v>99765</v>
+        <v>105438</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4825,36 +4831,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4863,13 +4860,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707513</v>
+        <v>707725</v>
       </c>
       <c r="R36" t="n">
-        <v>6375053</v>
+        <v>6374976</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4903,7 +4900,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4917,7 +4914,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4935,10 +4932,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578772</v>
+        <v>122578821</v>
       </c>
       <c r="B37" t="n">
-        <v>99765</v>
+        <v>105438</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4951,26 +4948,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4980,7 +4977,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4989,13 +4986,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707506</v>
+        <v>707605</v>
       </c>
       <c r="R37" t="n">
-        <v>6375110</v>
+        <v>6374970</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5029,7 +5026,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5043,7 +5040,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5061,10 +5058,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578805</v>
+        <v>122578782</v>
       </c>
       <c r="B38" t="n">
-        <v>98215</v>
+        <v>98218</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5096,7 +5093,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5115,10 +5112,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707697</v>
+        <v>707621</v>
       </c>
       <c r="R38" t="n">
-        <v>6374980</v>
+        <v>6375108</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5182,10 +5179,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578811</v>
+        <v>122578824</v>
       </c>
       <c r="B39" t="n">
-        <v>98215</v>
+        <v>99768</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5194,35 +5191,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5236,10 +5233,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707652</v>
+        <v>707606</v>
       </c>
       <c r="R39" t="n">
-        <v>6374986</v>
+        <v>6374961</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5285,7 +5282,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5303,10 +5300,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578795</v>
+        <v>122578817</v>
       </c>
       <c r="B40" t="n">
-        <v>105435</v>
+        <v>99768</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5319,27 +5316,36 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5348,10 +5354,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707725</v>
+        <v>707624</v>
       </c>
       <c r="R40" t="n">
-        <v>6374976</v>
+        <v>6374996</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5388,7 +5394,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5420,10 +5426,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578759</v>
+        <v>122578783</v>
       </c>
       <c r="B41" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5453,16 +5459,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5474,13 +5471,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707557</v>
+        <v>707633</v>
       </c>
       <c r="R41" t="n">
-        <v>6375009</v>
+        <v>6375094</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5514,7 +5511,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5546,10 +5543,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578817</v>
+        <v>122578823</v>
       </c>
       <c r="B42" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5581,7 +5578,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5600,10 +5597,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707624</v>
+        <v>707605</v>
       </c>
       <c r="R42" t="n">
-        <v>6374996</v>
+        <v>6374970</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5640,7 +5637,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5654,7 +5651,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5672,10 +5669,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578816</v>
+        <v>122578766</v>
       </c>
       <c r="B43" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5705,7 +5702,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5717,13 +5723,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707638</v>
+        <v>707548</v>
       </c>
       <c r="R43" t="n">
-        <v>6374988</v>
+        <v>6375091</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5757,7 +5763,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5771,7 +5777,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5789,10 +5795,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578753</v>
+        <v>122578760</v>
       </c>
       <c r="B44" t="n">
-        <v>98215</v>
+        <v>105438</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5801,40 +5807,40 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5843,10 +5849,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707554</v>
+        <v>707547</v>
       </c>
       <c r="R44" t="n">
-        <v>6374978</v>
+        <v>6375010</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5915,10 +5921,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578760</v>
+        <v>122578774</v>
       </c>
       <c r="B45" t="n">
-        <v>105435</v>
+        <v>99768</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5931,36 +5937,36 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5969,13 +5975,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707547</v>
+        <v>707528</v>
       </c>
       <c r="R45" t="n">
-        <v>6375010</v>
+        <v>6375154</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6007,11 +6013,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6023,7 +6024,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6041,10 +6042,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578746</v>
+        <v>122578773</v>
       </c>
       <c r="B46" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6074,20 +6075,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707626</v>
+        <v>707489</v>
       </c>
       <c r="R46" t="n">
-        <v>6375071</v>
+        <v>6375140</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6119,11 +6134,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Stensamling, grav? Nära.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6135,7 +6145,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6153,10 +6163,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578763</v>
+        <v>122578814</v>
       </c>
       <c r="B47" t="n">
-        <v>99765</v>
+        <v>98218</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6165,35 +6175,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6207,13 +6217,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707548</v>
+        <v>707638</v>
       </c>
       <c r="R47" t="n">
-        <v>6375014</v>
+        <v>6374988</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6243,11 +6253,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6279,10 +6284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578796</v>
+        <v>122578749</v>
       </c>
       <c r="B48" t="n">
-        <v>99765</v>
+        <v>105438</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6295,27 +6300,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6324,10 +6338,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707725</v>
+        <v>707570</v>
       </c>
       <c r="R48" t="n">
-        <v>6374976</v>
+        <v>6374984</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6364,7 +6378,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6396,10 +6410,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578770</v>
+        <v>122578784</v>
       </c>
       <c r="B49" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6429,16 +6443,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6450,13 +6455,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707506</v>
+        <v>707648</v>
       </c>
       <c r="R49" t="n">
-        <v>6375077</v>
+        <v>6375072</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6490,7 +6495,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6504,7 +6509,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6522,10 +6527,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578771</v>
+        <v>122578796</v>
       </c>
       <c r="B50" t="n">
-        <v>98215</v>
+        <v>99768</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6534,37 +6539,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6576,13 +6572,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707490</v>
+        <v>707725</v>
       </c>
       <c r="R50" t="n">
-        <v>6375090</v>
+        <v>6374976</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6616,7 +6612,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6630,7 +6626,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6648,10 +6644,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578740</v>
+        <v>122578805</v>
       </c>
       <c r="B51" t="n">
-        <v>105435</v>
+        <v>98218</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6660,41 +6656,55 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707609</v>
+        <v>707697</v>
       </c>
       <c r="R51" t="n">
-        <v>6375033</v>
+        <v>6374980</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6724,11 +6734,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6760,10 +6765,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578764</v>
+        <v>122578759</v>
       </c>
       <c r="B52" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6795,7 +6800,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6814,13 +6819,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707538</v>
+        <v>707557</v>
       </c>
       <c r="R52" t="n">
-        <v>6375024</v>
+        <v>6375009</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6886,10 +6891,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578823</v>
+        <v>122578781</v>
       </c>
       <c r="B53" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6919,16 +6924,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6940,10 +6936,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707605</v>
+        <v>707621</v>
       </c>
       <c r="R53" t="n">
-        <v>6374970</v>
+        <v>6375108</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6980,7 +6976,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6994,7 +6990,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7012,10 +7008,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578807</v>
+        <v>122578816</v>
       </c>
       <c r="B54" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7057,10 +7053,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707678</v>
+        <v>707638</v>
       </c>
       <c r="R54" t="n">
-        <v>6374990</v>
+        <v>6374988</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7097,7 +7093,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7129,10 +7125,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578815</v>
+        <v>122578758</v>
       </c>
       <c r="B55" t="n">
-        <v>105435</v>
+        <v>105438</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7162,7 +7158,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7174,13 +7179,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707638</v>
+        <v>707557</v>
       </c>
       <c r="R55" t="n">
-        <v>6374988</v>
+        <v>6375009</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7214,7 +7219,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7246,10 +7251,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578775</v>
+        <v>122578741</v>
       </c>
       <c r="B56" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7279,31 +7284,17 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707564</v>
+        <v>707609</v>
       </c>
       <c r="R56" t="n">
-        <v>6375169</v>
+        <v>6375033</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7338,6 +7329,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Spridd, riklig. Strensamling, grav?</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7349,7 +7345,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7367,10 +7363,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578781</v>
+        <v>122578754</v>
       </c>
       <c r="B57" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7400,7 +7396,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7412,10 +7417,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707621</v>
+        <v>707554</v>
       </c>
       <c r="R57" t="n">
-        <v>6375108</v>
+        <v>6374978</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7452,7 +7457,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7484,10 +7489,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578777</v>
+        <v>122578797</v>
       </c>
       <c r="B58" t="n">
-        <v>99765</v>
+        <v>98218</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7496,25 +7501,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -7524,7 +7529,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7538,13 +7543,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707591</v>
+        <v>707725</v>
       </c>
       <c r="R58" t="n">
-        <v>6375187</v>
+        <v>6374976</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7576,11 +7581,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>30 m S åker i N.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7610,10 +7610,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578783</v>
+        <v>122578755</v>
       </c>
       <c r="B59" t="n">
-        <v>99765</v>
+        <v>98218</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7622,28 +7622,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7655,13 +7664,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707633</v>
+        <v>707541</v>
       </c>
       <c r="R59" t="n">
-        <v>6375094</v>
+        <v>6374993</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7695,7 +7704,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7727,10 +7736,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578819</v>
+        <v>122578786</v>
       </c>
       <c r="B60" t="n">
-        <v>99765</v>
+        <v>98218</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7739,35 +7748,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7781,10 +7790,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707605</v>
+        <v>707652</v>
       </c>
       <c r="R60" t="n">
-        <v>6374982</v>
+        <v>6375083</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7821,7 +7830,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7835,7 +7844,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7853,10 +7862,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578810</v>
+        <v>122578764</v>
       </c>
       <c r="B61" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7886,7 +7895,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7898,13 +7916,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707652</v>
+        <v>707538</v>
       </c>
       <c r="R61" t="n">
-        <v>6374986</v>
+        <v>6375024</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7938,7 +7956,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7970,10 +7988,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578743</v>
+        <v>122578746</v>
       </c>
       <c r="B62" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8010,10 +8028,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707638</v>
+        <v>707626</v>
       </c>
       <c r="R62" t="n">
-        <v>6375036</v>
+        <v>6375071</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8050,7 +8068,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8082,10 +8100,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578812</v>
+        <v>122578778</v>
       </c>
       <c r="B63" t="n">
-        <v>105435</v>
+        <v>99768</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8098,27 +8116,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8127,13 +8154,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707646</v>
+        <v>707599</v>
       </c>
       <c r="R63" t="n">
-        <v>6374967</v>
+        <v>6375165</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8167,7 +8194,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8181,7 +8208,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8199,10 +8226,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578809</v>
+        <v>122578812</v>
       </c>
       <c r="B64" t="n">
-        <v>105435</v>
+        <v>105438</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8244,10 +8271,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707652</v>
+        <v>707646</v>
       </c>
       <c r="R64" t="n">
-        <v>6374986</v>
+        <v>6374967</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8284,7 +8311,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8316,10 +8343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578821</v>
+        <v>122578806</v>
       </c>
       <c r="B65" t="n">
-        <v>105435</v>
+        <v>105438</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8349,16 +8376,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -8370,10 +8388,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707605</v>
+        <v>707678</v>
       </c>
       <c r="R65" t="n">
-        <v>6374970</v>
+        <v>6374990</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8410,7 +8428,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8424,7 +8442,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8442,10 +8460,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578814</v>
+        <v>122578752</v>
       </c>
       <c r="B66" t="n">
-        <v>98215</v>
+        <v>99768</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8454,35 +8472,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8496,13 +8514,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707638</v>
+        <v>707569</v>
       </c>
       <c r="R66" t="n">
-        <v>6374988</v>
+        <v>6374979</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8532,6 +8550,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8563,10 +8586,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578774</v>
+        <v>122578742</v>
       </c>
       <c r="B67" t="n">
-        <v>99765</v>
+        <v>105438</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8579,51 +8602,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707528</v>
+        <v>707638</v>
       </c>
       <c r="R67" t="n">
-        <v>6375154</v>
+        <v>6375036</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8655,6 +8664,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8666,7 +8680,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8684,10 +8698,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578825</v>
+        <v>122578815</v>
       </c>
       <c r="B68" t="n">
-        <v>99765</v>
+        <v>105438</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8700,36 +8714,27 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8738,10 +8743,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707611</v>
+        <v>707638</v>
       </c>
       <c r="R68" t="n">
-        <v>6374954</v>
+        <v>6374988</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8776,6 +8781,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spridd, ganska rikligt.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8787,7 +8797,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8805,10 +8815,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578762</v>
+        <v>122578740</v>
       </c>
       <c r="B69" t="n">
-        <v>105435</v>
+        <v>105438</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8838,34 +8848,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707548</v>
+        <v>707609</v>
       </c>
       <c r="R69" t="n">
-        <v>6375014</v>
+        <v>6375033</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8899,7 +8895,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8931,10 +8927,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578779</v>
+        <v>122578756</v>
       </c>
       <c r="B70" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8964,7 +8960,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8976,13 +8981,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707597</v>
+        <v>707541</v>
       </c>
       <c r="R70" t="n">
-        <v>6375142</v>
+        <v>6374993</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9016,7 +9021,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9030,7 +9035,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9048,10 +9053,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578757</v>
+        <v>122578825</v>
       </c>
       <c r="B71" t="n">
-        <v>98215</v>
+        <v>99768</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9060,35 +9065,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -9102,13 +9107,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707557</v>
+        <v>707611</v>
       </c>
       <c r="R71" t="n">
-        <v>6375009</v>
+        <v>6374954</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9140,11 +9145,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578813</v>
+        <v>122578757</v>
       </c>
       <c r="B3" t="n">
-        <v>99768</v>
+        <v>98218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,28 +822,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -855,13 +864,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707646</v>
+        <v>707557</v>
       </c>
       <c r="R3" t="n">
-        <v>6374967</v>
+        <v>6375009</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +904,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578772</v>
+        <v>122578809</v>
       </c>
       <c r="B4" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,36 +952,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -981,13 +981,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707506</v>
+        <v>707652</v>
       </c>
       <c r="R4" t="n">
-        <v>6375110</v>
+        <v>6374986</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578819</v>
+        <v>122578816</v>
       </c>
       <c r="B5" t="n">
         <v>99768</v>
@@ -1086,16 +1086,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1107,10 +1098,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707605</v>
+        <v>707638</v>
       </c>
       <c r="R5" t="n">
-        <v>6374982</v>
+        <v>6374988</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1147,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1152,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1179,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578818</v>
+        <v>122578766</v>
       </c>
       <c r="B6" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,26 +1186,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1224,7 +1215,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1233,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707605</v>
+        <v>707548</v>
       </c>
       <c r="R6" t="n">
-        <v>6374982</v>
+        <v>6375091</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,7 +1264,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,7 +1278,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578808</v>
+        <v>122578770</v>
       </c>
       <c r="B7" t="n">
-        <v>98218</v>
+        <v>99768</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,35 +1308,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1359,13 +1350,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707678</v>
+        <v>707506</v>
       </c>
       <c r="R7" t="n">
-        <v>6374990</v>
+        <v>6375077</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1397,6 +1388,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1408,7 +1404,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1426,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578757</v>
+        <v>122578824</v>
       </c>
       <c r="B8" t="n">
-        <v>98218</v>
+        <v>99768</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,35 +1434,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1480,13 +1476,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707557</v>
+        <v>707606</v>
       </c>
       <c r="R8" t="n">
-        <v>6375009</v>
+        <v>6374961</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1518,11 +1514,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1534,7 +1525,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1552,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578800</v>
+        <v>122578772</v>
       </c>
       <c r="B9" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1568,36 +1559,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1606,13 +1597,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707697</v>
+        <v>707506</v>
       </c>
       <c r="R9" t="n">
-        <v>6374980</v>
+        <v>6375110</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1646,7 +1637,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Inget i tallplantager mot S och O.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1660,7 +1651,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1678,10 +1669,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578769</v>
+        <v>122578815</v>
       </c>
       <c r="B10" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1694,36 +1685,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1732,13 +1714,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707513</v>
+        <v>707638</v>
       </c>
       <c r="R10" t="n">
-        <v>6375053</v>
+        <v>6374988</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1772,7 +1754,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,7 +1768,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1804,10 +1786,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578809</v>
+        <v>122578780</v>
       </c>
       <c r="B11" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1820,27 +1802,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1849,13 +1831,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707652</v>
+        <v>707626</v>
       </c>
       <c r="R11" t="n">
-        <v>6374986</v>
+        <v>6375120</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1889,7 +1871,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,10 +1903,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578802</v>
+        <v>122578746</v>
       </c>
       <c r="B12" t="n">
-        <v>98218</v>
+        <v>99768</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1933,55 +1915,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707697</v>
+        <v>707626</v>
       </c>
       <c r="R12" t="n">
-        <v>6374969</v>
+        <v>6375071</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2011,6 +1979,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2042,7 +2015,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578776</v>
+        <v>122578825</v>
       </c>
       <c r="B13" t="n">
         <v>99768</v>
@@ -2077,7 +2050,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2096,13 +2069,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707584</v>
+        <v>707611</v>
       </c>
       <c r="R13" t="n">
-        <v>6375172</v>
+        <v>6374954</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2145,7 +2118,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2163,7 +2136,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578807</v>
+        <v>122578777</v>
       </c>
       <c r="B14" t="n">
         <v>99768</v>
@@ -2196,7 +2169,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2208,13 +2190,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707678</v>
+        <v>707591</v>
       </c>
       <c r="R14" t="n">
-        <v>6374990</v>
+        <v>6375187</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,7 +2230,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>30 m S åker i N.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2262,7 +2244,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2280,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578801</v>
+        <v>122578797</v>
       </c>
       <c r="B15" t="n">
-        <v>99768</v>
+        <v>98218</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2292,28 +2274,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2325,10 +2316,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707697</v>
+        <v>707725</v>
       </c>
       <c r="R15" t="n">
-        <v>6374980</v>
+        <v>6374976</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2361,11 +2352,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2397,7 +2383,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578779</v>
+        <v>122578754</v>
       </c>
       <c r="B16" t="n">
         <v>99768</v>
@@ -2430,7 +2416,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2442,13 +2437,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707597</v>
+        <v>707554</v>
       </c>
       <c r="R16" t="n">
-        <v>6375142</v>
+        <v>6374978</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2482,7 +2477,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2496,7 +2491,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2514,10 +2509,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578771</v>
+        <v>122578819</v>
       </c>
       <c r="B17" t="n">
-        <v>98218</v>
+        <v>99768</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2526,30 +2521,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2568,13 +2563,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707490</v>
+        <v>707605</v>
       </c>
       <c r="R17" t="n">
-        <v>6375090</v>
+        <v>6374982</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2608,7 +2603,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2622,7 +2617,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2640,7 +2635,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578763</v>
+        <v>122578796</v>
       </c>
       <c r="B18" t="n">
         <v>99768</v>
@@ -2673,16 +2668,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2694,13 +2680,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707548</v>
+        <v>707725</v>
       </c>
       <c r="R18" t="n">
-        <v>6375014</v>
+        <v>6374976</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2734,7 +2720,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2766,10 +2752,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578775</v>
+        <v>122578786</v>
       </c>
       <c r="B19" t="n">
-        <v>99768</v>
+        <v>98218</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2778,35 +2764,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2820,13 +2806,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707564</v>
+        <v>707652</v>
       </c>
       <c r="R19" t="n">
-        <v>6375169</v>
+        <v>6375083</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2858,6 +2844,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2869,7 +2860,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2887,10 +2878,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578785</v>
+        <v>122578814</v>
       </c>
       <c r="B20" t="n">
-        <v>105438</v>
+        <v>98218</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2899,31 +2890,40 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707648</v>
+        <v>707638</v>
       </c>
       <c r="R20" t="n">
-        <v>6375072</v>
+        <v>6374988</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2968,11 +2968,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3004,10 +2999,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578770</v>
+        <v>122578762</v>
       </c>
       <c r="B21" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3020,36 +3015,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3058,13 +3053,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707506</v>
+        <v>707548</v>
       </c>
       <c r="R21" t="n">
-        <v>6375077</v>
+        <v>6375014</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3098,7 +3093,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3112,7 +3107,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3130,10 +3125,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578751</v>
+        <v>122578795</v>
       </c>
       <c r="B22" t="n">
-        <v>98218</v>
+        <v>105438</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3142,40 +3137,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3184,13 +3170,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707569</v>
+        <v>707725</v>
       </c>
       <c r="R22" t="n">
-        <v>6374979</v>
+        <v>6374976</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3224,7 +3210,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3256,10 +3242,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578767</v>
+        <v>122578818</v>
       </c>
       <c r="B23" t="n">
-        <v>98262</v>
+        <v>105438</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3268,40 +3254,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219862</v>
+        <v>671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3310,13 +3296,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707513</v>
+        <v>707605</v>
       </c>
       <c r="R23" t="n">
-        <v>6375053</v>
+        <v>6374982</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3348,6 +3334,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3359,7 +3350,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3377,10 +3368,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578810</v>
+        <v>122578751</v>
       </c>
       <c r="B24" t="n">
-        <v>99768</v>
+        <v>98218</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3389,28 +3380,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3422,13 +3422,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707652</v>
+        <v>707569</v>
       </c>
       <c r="R24" t="n">
-        <v>6374986</v>
+        <v>6374979</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578811</v>
+        <v>122578804</v>
       </c>
       <c r="B25" t="n">
-        <v>98218</v>
+        <v>99768</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3506,37 +3506,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3548,10 +3539,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707652</v>
+        <v>707697</v>
       </c>
       <c r="R25" t="n">
-        <v>6374986</v>
+        <v>6374980</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3584,6 +3575,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3615,10 +3611,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578744</v>
+        <v>122578775</v>
       </c>
       <c r="B26" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3631,26 +3627,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3660,7 +3656,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3669,10 +3665,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707626</v>
+        <v>707564</v>
       </c>
       <c r="R26" t="n">
-        <v>6375071</v>
+        <v>6375169</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3707,11 +3703,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Stensamling, grav? Nära.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3723,7 +3714,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3741,10 +3732,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578780</v>
+        <v>122578750</v>
       </c>
       <c r="B27" t="n">
-        <v>99768</v>
+        <v>98262</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3753,28 +3744,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3786,13 +3786,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707626</v>
+        <v>707569</v>
       </c>
       <c r="R27" t="n">
-        <v>6375120</v>
+        <v>6374979</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3858,7 +3858,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578743</v>
+        <v>122578741</v>
       </c>
       <c r="B28" t="n">
         <v>99768</v>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707638</v>
+        <v>707609</v>
       </c>
       <c r="R28" t="n">
-        <v>6375036</v>
+        <v>6375033</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3970,10 +3970,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578753</v>
+        <v>122578817</v>
       </c>
       <c r="B29" t="n">
-        <v>98218</v>
+        <v>99768</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3982,35 +3982,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707554</v>
+        <v>707624</v>
       </c>
       <c r="R29" t="n">
-        <v>6374978</v>
+        <v>6374996</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4096,10 +4096,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578747</v>
+        <v>122578783</v>
       </c>
       <c r="B30" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4112,37 +4112,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707590</v>
+        <v>707633</v>
       </c>
       <c r="R30" t="n">
-        <v>6375036</v>
+        <v>6375094</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4176,7 +4181,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4208,10 +4213,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578765</v>
+        <v>122578749</v>
       </c>
       <c r="B31" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4224,27 +4229,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4253,13 +4267,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707532</v>
+        <v>707570</v>
       </c>
       <c r="R31" t="n">
-        <v>6375035</v>
+        <v>6374984</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4293,7 +4307,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4325,7 +4339,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578777</v>
+        <v>122578776</v>
       </c>
       <c r="B32" t="n">
         <v>99768</v>
@@ -4360,7 +4374,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4379,13 +4393,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707591</v>
+        <v>707584</v>
       </c>
       <c r="R32" t="n">
-        <v>6375187</v>
+        <v>6375172</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4417,11 +4431,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>30 m S åker i N.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4433,7 +4442,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4451,10 +4460,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578750</v>
+        <v>122578742</v>
       </c>
       <c r="B33" t="n">
-        <v>98262</v>
+        <v>105438</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4463,55 +4472,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219862</v>
+        <v>671</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707569</v>
+        <v>707638</v>
       </c>
       <c r="R33" t="n">
-        <v>6374979</v>
+        <v>6375036</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4545,7 +4540,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4577,10 +4572,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578748</v>
+        <v>122578805</v>
       </c>
       <c r="B34" t="n">
-        <v>99768</v>
+        <v>98218</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4589,38 +4584,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707590</v>
+        <v>707697</v>
       </c>
       <c r="R34" t="n">
-        <v>6375036</v>
+        <v>6374980</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4653,11 +4662,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4689,10 +4693,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578762</v>
+        <v>122578813</v>
       </c>
       <c r="B35" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4705,36 +4709,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4743,13 +4738,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707548</v>
+        <v>707646</v>
       </c>
       <c r="R35" t="n">
-        <v>6375014</v>
+        <v>6374967</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4783,7 +4778,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4815,10 +4810,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578795</v>
+        <v>122578784</v>
       </c>
       <c r="B36" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4831,27 +4826,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4860,10 +4855,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707725</v>
+        <v>707648</v>
       </c>
       <c r="R36" t="n">
-        <v>6374976</v>
+        <v>6375072</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4900,7 +4895,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4932,10 +4927,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578821</v>
+        <v>122578810</v>
       </c>
       <c r="B37" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4948,36 +4943,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4986,10 +4972,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707605</v>
+        <v>707652</v>
       </c>
       <c r="R37" t="n">
-        <v>6374970</v>
+        <v>6374986</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5026,7 +5012,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5040,7 +5026,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5058,7 +5044,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578782</v>
+        <v>122578811</v>
       </c>
       <c r="B38" t="n">
         <v>98218</v>
@@ -5093,7 +5079,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5112,10 +5098,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707621</v>
+        <v>707652</v>
       </c>
       <c r="R38" t="n">
-        <v>6375108</v>
+        <v>6374986</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5179,10 +5165,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578824</v>
+        <v>122578740</v>
       </c>
       <c r="B39" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5195,51 +5181,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707606</v>
+        <v>707609</v>
       </c>
       <c r="R39" t="n">
-        <v>6374961</v>
+        <v>6375033</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5271,6 +5243,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Spridd, riklig. Strensamling, grav?</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5282,7 +5259,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5300,7 +5277,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578817</v>
+        <v>122578743</v>
       </c>
       <c r="B40" t="n">
         <v>99768</v>
@@ -5333,34 +5310,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707624</v>
+        <v>707638</v>
       </c>
       <c r="R40" t="n">
-        <v>6374996</v>
+        <v>6375036</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5394,7 +5357,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5426,10 +5389,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578783</v>
+        <v>122578802</v>
       </c>
       <c r="B41" t="n">
-        <v>99768</v>
+        <v>98218</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5438,28 +5401,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5471,13 +5443,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707633</v>
+        <v>707697</v>
       </c>
       <c r="R41" t="n">
-        <v>6375094</v>
+        <v>6374969</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5507,11 +5479,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5543,7 +5510,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578823</v>
+        <v>122578765</v>
       </c>
       <c r="B42" t="n">
         <v>99768</v>
@@ -5576,16 +5543,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5597,13 +5555,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707605</v>
+        <v>707532</v>
       </c>
       <c r="R42" t="n">
-        <v>6374970</v>
+        <v>6375035</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5637,7 +5595,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5651,7 +5609,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5669,10 +5627,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578766</v>
+        <v>122578812</v>
       </c>
       <c r="B43" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5685,36 +5643,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5723,13 +5672,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707548</v>
+        <v>707646</v>
       </c>
       <c r="R43" t="n">
-        <v>6375091</v>
+        <v>6374967</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5763,7 +5712,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5777,7 +5726,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5795,10 +5744,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578760</v>
+        <v>122578781</v>
       </c>
       <c r="B44" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5811,36 +5760,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5849,10 +5789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707547</v>
+        <v>707621</v>
       </c>
       <c r="R44" t="n">
-        <v>6375010</v>
+        <v>6375108</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5889,7 +5829,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5921,10 +5861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578774</v>
+        <v>122578806</v>
       </c>
       <c r="B45" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5937,36 +5877,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5975,13 +5906,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707528</v>
+        <v>707678</v>
       </c>
       <c r="R45" t="n">
-        <v>6375154</v>
+        <v>6374990</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6013,6 +5944,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6024,7 +5960,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6042,10 +5978,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578773</v>
+        <v>122578758</v>
       </c>
       <c r="B46" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6058,36 +5994,36 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6096,10 +6032,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707489</v>
+        <v>707557</v>
       </c>
       <c r="R46" t="n">
-        <v>6375140</v>
+        <v>6375009</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -6134,6 +6070,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6145,7 +6086,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6163,10 +6104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578814</v>
+        <v>122578779</v>
       </c>
       <c r="B47" t="n">
-        <v>98218</v>
+        <v>99768</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6175,37 +6116,28 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6217,13 +6149,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707638</v>
+        <v>707597</v>
       </c>
       <c r="R47" t="n">
-        <v>6374988</v>
+        <v>6375142</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6255,6 +6187,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Enstaka strå.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6266,7 +6203,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6284,10 +6221,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578749</v>
+        <v>122578755</v>
       </c>
       <c r="B48" t="n">
-        <v>105438</v>
+        <v>98218</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6296,40 +6233,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6338,13 +6275,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707570</v>
+        <v>707541</v>
       </c>
       <c r="R48" t="n">
-        <v>6374984</v>
+        <v>6374993</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6410,10 +6347,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578784</v>
+        <v>122578771</v>
       </c>
       <c r="B49" t="n">
-        <v>99768</v>
+        <v>98218</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6422,28 +6359,37 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6455,13 +6401,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707648</v>
+        <v>707490</v>
       </c>
       <c r="R49" t="n">
-        <v>6375072</v>
+        <v>6375090</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6495,7 +6441,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6509,7 +6455,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6527,10 +6473,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578796</v>
+        <v>122578808</v>
       </c>
       <c r="B50" t="n">
-        <v>99768</v>
+        <v>98218</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6539,28 +6485,37 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6572,10 +6527,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707725</v>
+        <v>707678</v>
       </c>
       <c r="R50" t="n">
-        <v>6374976</v>
+        <v>6374990</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6608,11 +6563,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6644,10 +6594,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578805</v>
+        <v>122578748</v>
       </c>
       <c r="B51" t="n">
-        <v>98218</v>
+        <v>99768</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6656,52 +6606,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707697</v>
+        <v>707590</v>
       </c>
       <c r="R51" t="n">
-        <v>6374980</v>
+        <v>6375036</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6734,6 +6670,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6765,10 +6706,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578759</v>
+        <v>122578744</v>
       </c>
       <c r="B52" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6781,26 +6722,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6810,7 +6751,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6819,13 +6760,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707557</v>
+        <v>707626</v>
       </c>
       <c r="R52" t="n">
-        <v>6375009</v>
+        <v>6375071</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6859,7 +6800,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6891,10 +6832,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578781</v>
+        <v>122578803</v>
       </c>
       <c r="B53" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6907,27 +6848,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6936,10 +6877,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707621</v>
+        <v>707697</v>
       </c>
       <c r="R53" t="n">
-        <v>6375108</v>
+        <v>6374980</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6976,7 +6917,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7008,7 +6949,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578816</v>
+        <v>122578764</v>
       </c>
       <c r="B54" t="n">
         <v>99768</v>
@@ -7041,7 +6982,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7053,13 +7003,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707638</v>
+        <v>707538</v>
       </c>
       <c r="R54" t="n">
-        <v>6374988</v>
+        <v>6375024</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7093,7 +7043,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7125,10 +7075,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578758</v>
+        <v>122578774</v>
       </c>
       <c r="B55" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7141,36 +7091,36 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7179,13 +7129,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707557</v>
+        <v>707528</v>
       </c>
       <c r="R55" t="n">
-        <v>6375009</v>
+        <v>6375154</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7217,11 +7167,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7233,7 +7178,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7251,10 +7196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578741</v>
+        <v>122578782</v>
       </c>
       <c r="B56" t="n">
-        <v>99768</v>
+        <v>98218</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7263,41 +7208,55 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707609</v>
+        <v>707621</v>
       </c>
       <c r="R56" t="n">
-        <v>6375033</v>
+        <v>6375108</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7327,11 +7286,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7363,10 +7317,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578754</v>
+        <v>122578747</v>
       </c>
       <c r="B57" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7379,48 +7333,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707554</v>
+        <v>707590</v>
       </c>
       <c r="R57" t="n">
-        <v>6374978</v>
+        <v>6375036</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7457,7 +7397,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7489,10 +7429,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578797</v>
+        <v>122578769</v>
       </c>
       <c r="B58" t="n">
-        <v>98218</v>
+        <v>99768</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7501,35 +7441,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7543,13 +7483,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707725</v>
+        <v>707513</v>
       </c>
       <c r="R58" t="n">
-        <v>6374976</v>
+        <v>6375053</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7581,6 +7521,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>3 ex.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7592,7 +7537,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7610,10 +7555,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578755</v>
+        <v>122578752</v>
       </c>
       <c r="B59" t="n">
-        <v>98218</v>
+        <v>99768</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7622,35 +7567,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7664,10 +7609,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707541</v>
+        <v>707569</v>
       </c>
       <c r="R59" t="n">
-        <v>6374993</v>
+        <v>6374979</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -7736,10 +7681,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578786</v>
+        <v>122578821</v>
       </c>
       <c r="B60" t="n">
-        <v>98218</v>
+        <v>105438</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7748,40 +7693,40 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7790,10 +7735,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707652</v>
+        <v>707605</v>
       </c>
       <c r="R60" t="n">
-        <v>6375083</v>
+        <v>6374970</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7830,7 +7775,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7844,7 +7789,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7862,7 +7807,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578764</v>
+        <v>122578763</v>
       </c>
       <c r="B61" t="n">
         <v>99768</v>
@@ -7897,7 +7842,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7916,13 +7861,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707538</v>
+        <v>707548</v>
       </c>
       <c r="R61" t="n">
-        <v>6375024</v>
+        <v>6375014</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7988,10 +7933,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578746</v>
+        <v>122578760</v>
       </c>
       <c r="B62" t="n">
-        <v>99768</v>
+        <v>105438</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8004,37 +7949,51 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707626</v>
+        <v>707547</v>
       </c>
       <c r="R62" t="n">
-        <v>6375071</v>
+        <v>6375010</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8068,7 +8027,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8100,10 +8059,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578778</v>
+        <v>122578767</v>
       </c>
       <c r="B63" t="n">
-        <v>99768</v>
+        <v>98262</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8112,35 +8071,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8154,13 +8113,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707599</v>
+        <v>707513</v>
       </c>
       <c r="R63" t="n">
-        <v>6375165</v>
+        <v>6375053</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8192,11 +8151,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Barrblandskog mot åker i N.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8208,7 +8162,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8226,10 +8180,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578812</v>
+        <v>122578759</v>
       </c>
       <c r="B64" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8242,27 +8196,36 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8271,13 +8234,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707646</v>
+        <v>707557</v>
       </c>
       <c r="R64" t="n">
-        <v>6374967</v>
+        <v>6375009</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8311,7 +8274,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8343,7 +8306,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578806</v>
+        <v>122578785</v>
       </c>
       <c r="B65" t="n">
         <v>105438</v>
@@ -8388,10 +8351,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707678</v>
+        <v>707648</v>
       </c>
       <c r="R65" t="n">
-        <v>6374990</v>
+        <v>6375072</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8428,7 +8391,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8460,7 +8423,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578752</v>
+        <v>122578756</v>
       </c>
       <c r="B66" t="n">
         <v>99768</v>
@@ -8495,7 +8458,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8514,10 +8477,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707569</v>
+        <v>707541</v>
       </c>
       <c r="R66" t="n">
-        <v>6374979</v>
+        <v>6374993</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -8586,10 +8549,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578742</v>
+        <v>122578773</v>
       </c>
       <c r="B67" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8602,37 +8565,51 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707638</v>
+        <v>707489</v>
       </c>
       <c r="R67" t="n">
-        <v>6375036</v>
+        <v>6375140</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8664,11 +8641,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8680,7 +8652,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8698,10 +8670,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578815</v>
+        <v>122578778</v>
       </c>
       <c r="B68" t="n">
-        <v>105438</v>
+        <v>99768</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8714,27 +8686,36 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8743,13 +8724,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707638</v>
+        <v>707599</v>
       </c>
       <c r="R68" t="n">
-        <v>6374988</v>
+        <v>6375165</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8783,7 +8764,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8797,7 +8778,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8815,10 +8796,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578740</v>
+        <v>122578753</v>
       </c>
       <c r="B69" t="n">
-        <v>105438</v>
+        <v>98218</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8827,41 +8808,55 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707609</v>
+        <v>707554</v>
       </c>
       <c r="R69" t="n">
-        <v>6375033</v>
+        <v>6374978</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8895,7 +8890,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8927,7 +8922,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578756</v>
+        <v>122578823</v>
       </c>
       <c r="B70" t="n">
         <v>99768</v>
@@ -8962,7 +8957,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8981,13 +8976,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707541</v>
+        <v>707605</v>
       </c>
       <c r="R70" t="n">
-        <v>6374993</v>
+        <v>6374970</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9021,7 +9016,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9035,7 +9030,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9053,7 +9048,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578825</v>
+        <v>122578807</v>
       </c>
       <c r="B71" t="n">
         <v>99768</v>
@@ -9086,16 +9081,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -9107,10 +9093,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707611</v>
+        <v>707678</v>
       </c>
       <c r="R71" t="n">
-        <v>6374954</v>
+        <v>6374990</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9145,6 +9131,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9156,7 +9147,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578757</v>
+        <v>122578803</v>
       </c>
       <c r="B3" t="n">
-        <v>98218</v>
+        <v>105439</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,40 +822,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -864,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707557</v>
+        <v>707697</v>
       </c>
       <c r="R3" t="n">
-        <v>6375009</v>
+        <v>6374980</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578809</v>
+        <v>122578801</v>
       </c>
       <c r="B4" t="n">
-        <v>105438</v>
+        <v>99769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,27 +943,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -981,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707652</v>
+        <v>707697</v>
       </c>
       <c r="R4" t="n">
-        <v>6374986</v>
+        <v>6374980</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1021,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578816</v>
+        <v>122578823</v>
       </c>
       <c r="B5" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,7 +1077,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707638</v>
+        <v>707605</v>
       </c>
       <c r="R5" t="n">
-        <v>6374988</v>
+        <v>6374970</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578766</v>
+        <v>122578740</v>
       </c>
       <c r="B6" t="n">
-        <v>99768</v>
+        <v>105439</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,51 +1186,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707548</v>
+        <v>707609</v>
       </c>
       <c r="R6" t="n">
-        <v>6375091</v>
+        <v>6375033</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,7 +1250,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,7 +1264,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578770</v>
+        <v>122578816</v>
       </c>
       <c r="B7" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1329,16 +1315,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1350,13 +1327,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707506</v>
+        <v>707638</v>
       </c>
       <c r="R7" t="n">
-        <v>6375077</v>
+        <v>6374988</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1390,7 +1367,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1381,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1422,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578824</v>
+        <v>122578783</v>
       </c>
       <c r="B8" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1455,16 +1432,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1476,13 +1444,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707606</v>
+        <v>707633</v>
       </c>
       <c r="R8" t="n">
-        <v>6374961</v>
+        <v>6375094</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1514,6 +1482,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Glest spridd.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1525,7 +1498,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1543,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578772</v>
+        <v>122578748</v>
       </c>
       <c r="B9" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1576,34 +1549,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707506</v>
+        <v>707590</v>
       </c>
       <c r="R9" t="n">
-        <v>6375110</v>
+        <v>6375036</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1637,7 +1596,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1651,7 +1610,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1669,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578815</v>
+        <v>122578770</v>
       </c>
       <c r="B10" t="n">
-        <v>105438</v>
+        <v>99769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,27 +1644,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1714,13 +1682,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707638</v>
+        <v>707506</v>
       </c>
       <c r="R10" t="n">
-        <v>6374988</v>
+        <v>6375077</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1754,7 +1722,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,7 +1736,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1786,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578780</v>
+        <v>122578764</v>
       </c>
       <c r="B11" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1819,7 +1787,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1831,13 +1808,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707626</v>
+        <v>707538</v>
       </c>
       <c r="R11" t="n">
-        <v>6375120</v>
+        <v>6375024</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1871,7 +1848,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1903,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578746</v>
+        <v>122578813</v>
       </c>
       <c r="B12" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1937,19 +1914,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707626</v>
+        <v>707646</v>
       </c>
       <c r="R12" t="n">
-        <v>6375071</v>
+        <v>6374967</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1983,7 +1965,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2015,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578825</v>
+        <v>122578781</v>
       </c>
       <c r="B13" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2048,16 +2030,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2069,10 +2042,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707611</v>
+        <v>707621</v>
       </c>
       <c r="R13" t="n">
-        <v>6374954</v>
+        <v>6375108</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2107,6 +2080,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Glest spridd.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2118,7 +2096,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2136,10 +2114,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578777</v>
+        <v>122578766</v>
       </c>
       <c r="B14" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,12 +2149,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2190,13 +2168,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707591</v>
+        <v>707548</v>
       </c>
       <c r="R14" t="n">
-        <v>6375187</v>
+        <v>6375091</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2230,7 +2208,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>30 m S åker i N.</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2244,7 +2222,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2262,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578797</v>
+        <v>122578806</v>
       </c>
       <c r="B15" t="n">
-        <v>98218</v>
+        <v>105439</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2274,40 +2252,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2316,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707725</v>
+        <v>707678</v>
       </c>
       <c r="R15" t="n">
-        <v>6374976</v>
+        <v>6374990</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2352,6 +2321,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2383,10 +2357,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578754</v>
+        <v>122578786</v>
       </c>
       <c r="B16" t="n">
-        <v>99768</v>
+        <v>98219</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2395,35 +2369,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2437,10 +2411,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707554</v>
+        <v>707652</v>
       </c>
       <c r="R16" t="n">
-        <v>6374978</v>
+        <v>6375083</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2477,7 +2451,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2509,10 +2483,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578819</v>
+        <v>122578753</v>
       </c>
       <c r="B17" t="n">
-        <v>99768</v>
+        <v>98219</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2521,35 +2495,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2563,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707605</v>
+        <v>707554</v>
       </c>
       <c r="R17" t="n">
-        <v>6374982</v>
+        <v>6374978</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2603,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2617,7 +2591,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2635,10 +2609,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578796</v>
+        <v>122578754</v>
       </c>
       <c r="B18" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2668,7 +2642,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2680,10 +2663,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707725</v>
+        <v>707554</v>
       </c>
       <c r="R18" t="n">
-        <v>6374976</v>
+        <v>6374978</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2720,7 +2703,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2752,10 +2735,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578786</v>
+        <v>122578765</v>
       </c>
       <c r="B19" t="n">
-        <v>98218</v>
+        <v>99769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2764,37 +2747,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2806,13 +2780,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707652</v>
+        <v>707532</v>
       </c>
       <c r="R19" t="n">
-        <v>6375083</v>
+        <v>6375035</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2846,7 +2820,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2878,10 +2852,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578814</v>
+        <v>122578779</v>
       </c>
       <c r="B20" t="n">
-        <v>98218</v>
+        <v>99769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2890,37 +2864,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2932,13 +2897,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707638</v>
+        <v>707597</v>
       </c>
       <c r="R20" t="n">
-        <v>6374988</v>
+        <v>6375142</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2970,6 +2935,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka strå.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2981,7 +2951,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2999,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578762</v>
+        <v>122578785</v>
       </c>
       <c r="B21" t="n">
-        <v>105438</v>
+        <v>105439</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3032,16 +3002,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3053,13 +3014,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707548</v>
+        <v>707648</v>
       </c>
       <c r="R21" t="n">
-        <v>6375014</v>
+        <v>6375072</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3093,7 +3054,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3125,10 +3086,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578795</v>
+        <v>122578784</v>
       </c>
       <c r="B22" t="n">
-        <v>105438</v>
+        <v>99769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3141,27 +3102,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3170,10 +3131,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707725</v>
+        <v>707648</v>
       </c>
       <c r="R22" t="n">
-        <v>6374976</v>
+        <v>6375072</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3210,7 +3171,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3242,10 +3203,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578818</v>
+        <v>122578775</v>
       </c>
       <c r="B23" t="n">
-        <v>105438</v>
+        <v>99769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3258,21 +3219,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3282,12 +3243,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3296,13 +3257,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707605</v>
+        <v>707564</v>
       </c>
       <c r="R23" t="n">
-        <v>6374982</v>
+        <v>6375169</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3334,11 +3295,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minsta antal + spridd.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3350,7 +3306,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3368,10 +3324,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578751</v>
+        <v>122578778</v>
       </c>
       <c r="B24" t="n">
-        <v>98218</v>
+        <v>99769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3380,35 +3336,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3422,13 +3378,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707569</v>
+        <v>707599</v>
       </c>
       <c r="R24" t="n">
-        <v>6374979</v>
+        <v>6375165</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3462,7 +3418,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3476,7 +3432,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3494,10 +3450,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578804</v>
+        <v>122578825</v>
       </c>
       <c r="B25" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3527,7 +3483,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3539,10 +3504,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707697</v>
+        <v>707611</v>
       </c>
       <c r="R25" t="n">
-        <v>6374980</v>
+        <v>6374954</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3577,11 +3542,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3593,7 +3553,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3611,10 +3571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578775</v>
+        <v>122578746</v>
       </c>
       <c r="B26" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3644,31 +3604,17 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707564</v>
+        <v>707626</v>
       </c>
       <c r="R26" t="n">
-        <v>6375169</v>
+        <v>6375071</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3703,6 +3649,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Stensamling, grav? Nära.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3714,7 +3665,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3732,10 +3683,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578750</v>
+        <v>122578782</v>
       </c>
       <c r="B27" t="n">
-        <v>98262</v>
+        <v>98219</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3748,26 +3699,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3786,13 +3737,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707569</v>
+        <v>707621</v>
       </c>
       <c r="R27" t="n">
-        <v>6374979</v>
+        <v>6375108</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3822,11 +3773,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3858,10 +3804,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578741</v>
+        <v>122578747</v>
       </c>
       <c r="B28" t="n">
-        <v>99768</v>
+        <v>105439</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3874,21 +3820,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3898,13 +3844,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707609</v>
+        <v>707590</v>
       </c>
       <c r="R28" t="n">
-        <v>6375033</v>
+        <v>6375036</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3938,7 +3884,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3970,10 +3916,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578817</v>
+        <v>122578812</v>
       </c>
       <c r="B29" t="n">
-        <v>99768</v>
+        <v>105439</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3986,36 +3932,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4024,10 +3961,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707624</v>
+        <v>707646</v>
       </c>
       <c r="R29" t="n">
-        <v>6374996</v>
+        <v>6374967</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4064,7 +4001,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4096,10 +4033,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578783</v>
+        <v>122578742</v>
       </c>
       <c r="B30" t="n">
-        <v>99768</v>
+        <v>105439</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4112,42 +4049,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707633</v>
+        <v>707638</v>
       </c>
       <c r="R30" t="n">
-        <v>6375094</v>
+        <v>6375036</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4181,7 +4113,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4213,10 +4145,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578749</v>
+        <v>122578814</v>
       </c>
       <c r="B31" t="n">
-        <v>105438</v>
+        <v>98219</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4225,40 +4157,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4267,10 +4199,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707570</v>
+        <v>707638</v>
       </c>
       <c r="R31" t="n">
-        <v>6374984</v>
+        <v>6374988</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4303,11 +4235,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4339,10 +4266,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578776</v>
+        <v>122578797</v>
       </c>
       <c r="B32" t="n">
-        <v>99768</v>
+        <v>98219</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4351,35 +4278,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4393,13 +4320,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707584</v>
+        <v>707725</v>
       </c>
       <c r="R32" t="n">
-        <v>6375172</v>
+        <v>6374976</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4442,7 +4369,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4460,10 +4387,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578742</v>
+        <v>122578815</v>
       </c>
       <c r="B33" t="n">
-        <v>105438</v>
+        <v>105439</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4494,6 +4421,11 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
@@ -4503,10 +4435,10 @@
         <v>707638</v>
       </c>
       <c r="R33" t="n">
-        <v>6375036</v>
+        <v>6374988</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4540,7 +4472,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4572,10 +4504,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578805</v>
+        <v>122578769</v>
       </c>
       <c r="B34" t="n">
-        <v>98218</v>
+        <v>99769</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4584,35 +4516,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4626,13 +4558,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707697</v>
+        <v>707513</v>
       </c>
       <c r="R34" t="n">
-        <v>6374980</v>
+        <v>6375053</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4664,6 +4596,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>3 ex.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4675,7 +4612,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4693,10 +4630,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578813</v>
+        <v>122578752</v>
       </c>
       <c r="B35" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4726,7 +4663,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4738,13 +4684,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707646</v>
+        <v>707569</v>
       </c>
       <c r="R35" t="n">
-        <v>6374967</v>
+        <v>6374979</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4778,7 +4724,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4810,10 +4756,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578784</v>
+        <v>122578762</v>
       </c>
       <c r="B36" t="n">
-        <v>99768</v>
+        <v>105439</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4826,27 +4772,36 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4855,13 +4810,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707648</v>
+        <v>707548</v>
       </c>
       <c r="R36" t="n">
-        <v>6375072</v>
+        <v>6375014</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4895,7 +4850,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4927,10 +4882,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578810</v>
+        <v>122578749</v>
       </c>
       <c r="B37" t="n">
-        <v>99768</v>
+        <v>105439</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4943,27 +4898,36 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4972,10 +4936,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707652</v>
+        <v>707570</v>
       </c>
       <c r="R37" t="n">
-        <v>6374986</v>
+        <v>6374984</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5012,7 +4976,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5044,10 +5008,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578811</v>
+        <v>122578763</v>
       </c>
       <c r="B38" t="n">
-        <v>98218</v>
+        <v>99769</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5056,35 +5020,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5098,13 +5062,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707652</v>
+        <v>707548</v>
       </c>
       <c r="R38" t="n">
-        <v>6374986</v>
+        <v>6375014</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5134,6 +5098,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5165,10 +5134,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578740</v>
+        <v>122578807</v>
       </c>
       <c r="B39" t="n">
-        <v>105438</v>
+        <v>99769</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5181,37 +5150,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707609</v>
+        <v>707678</v>
       </c>
       <c r="R39" t="n">
-        <v>6375033</v>
+        <v>6374990</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5245,7 +5219,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5277,10 +5251,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578743</v>
+        <v>122578772</v>
       </c>
       <c r="B40" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5310,20 +5284,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707638</v>
+        <v>707506</v>
       </c>
       <c r="R40" t="n">
-        <v>6375036</v>
+        <v>6375110</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5357,7 +5345,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5371,7 +5359,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5389,10 +5377,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578802</v>
+        <v>122578777</v>
       </c>
       <c r="B41" t="n">
-        <v>98218</v>
+        <v>99769</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5401,35 +5389,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5443,13 +5431,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707697</v>
+        <v>707591</v>
       </c>
       <c r="R41" t="n">
-        <v>6374969</v>
+        <v>6375187</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5481,6 +5469,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>30 m S åker i N.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5492,7 +5485,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5510,10 +5503,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578765</v>
+        <v>122578795</v>
       </c>
       <c r="B42" t="n">
-        <v>99768</v>
+        <v>105439</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5526,27 +5519,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5555,13 +5548,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707532</v>
+        <v>707725</v>
       </c>
       <c r="R42" t="n">
-        <v>6375035</v>
+        <v>6374976</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5595,7 +5588,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5627,10 +5620,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578812</v>
+        <v>122578811</v>
       </c>
       <c r="B43" t="n">
-        <v>105438</v>
+        <v>98219</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5639,31 +5632,40 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5672,10 +5674,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707646</v>
+        <v>707652</v>
       </c>
       <c r="R43" t="n">
-        <v>6374967</v>
+        <v>6374986</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5708,11 +5710,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5744,10 +5741,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578781</v>
+        <v>122578767</v>
       </c>
       <c r="B44" t="n">
-        <v>99768</v>
+        <v>98263</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5756,28 +5753,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5789,13 +5795,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707621</v>
+        <v>707513</v>
       </c>
       <c r="R44" t="n">
-        <v>6375108</v>
+        <v>6375053</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5827,11 +5833,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Glest spridd.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5843,7 +5844,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5861,10 +5862,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578806</v>
+        <v>122578818</v>
       </c>
       <c r="B45" t="n">
-        <v>105438</v>
+        <v>105439</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5894,7 +5895,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5906,10 +5916,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707678</v>
+        <v>707605</v>
       </c>
       <c r="R45" t="n">
-        <v>6374990</v>
+        <v>6374982</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5946,7 +5956,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5960,7 +5970,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5981,7 +5991,7 @@
         <v>122578758</v>
       </c>
       <c r="B46" t="n">
-        <v>105438</v>
+        <v>105439</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6104,10 +6114,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578779</v>
+        <v>122578780</v>
       </c>
       <c r="B47" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6149,13 +6159,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707597</v>
+        <v>707626</v>
       </c>
       <c r="R47" t="n">
-        <v>6375142</v>
+        <v>6375120</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6189,7 +6199,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6203,7 +6213,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6221,10 +6231,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578755</v>
+        <v>122578773</v>
       </c>
       <c r="B48" t="n">
-        <v>98218</v>
+        <v>99769</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6233,35 +6243,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6275,10 +6285,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707541</v>
+        <v>707489</v>
       </c>
       <c r="R48" t="n">
-        <v>6374993</v>
+        <v>6375140</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -6313,11 +6323,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6329,7 +6334,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6347,10 +6352,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578771</v>
+        <v>122578808</v>
       </c>
       <c r="B49" t="n">
-        <v>98218</v>
+        <v>98219</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6382,12 +6387,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6401,13 +6406,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707490</v>
+        <v>707678</v>
       </c>
       <c r="R49" t="n">
-        <v>6375090</v>
+        <v>6374990</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6439,11 +6444,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>I långsträckt stensamlig, grav?</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578808</v>
+        <v>122578757</v>
       </c>
       <c r="B50" t="n">
-        <v>98218</v>
+        <v>98219</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707678</v>
+        <v>707557</v>
       </c>
       <c r="R50" t="n">
-        <v>6374990</v>
+        <v>6375009</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6563,6 +6563,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6594,10 +6599,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578748</v>
+        <v>122578759</v>
       </c>
       <c r="B51" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6627,20 +6632,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707590</v>
+        <v>707557</v>
       </c>
       <c r="R51" t="n">
-        <v>6375036</v>
+        <v>6375009</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6674,7 +6693,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6706,10 +6725,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578744</v>
+        <v>122578810</v>
       </c>
       <c r="B52" t="n">
-        <v>105438</v>
+        <v>99769</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6722,36 +6741,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6760,13 +6770,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707626</v>
+        <v>707652</v>
       </c>
       <c r="R52" t="n">
-        <v>6375071</v>
+        <v>6374986</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6800,7 +6810,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6832,10 +6842,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578803</v>
+        <v>122578819</v>
       </c>
       <c r="B53" t="n">
-        <v>105438</v>
+        <v>99769</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6848,27 +6858,36 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6877,10 +6896,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707697</v>
+        <v>707605</v>
       </c>
       <c r="R53" t="n">
-        <v>6374980</v>
+        <v>6374982</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6917,7 +6936,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6931,7 +6950,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6949,10 +6968,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578764</v>
+        <v>122578809</v>
       </c>
       <c r="B54" t="n">
-        <v>99768</v>
+        <v>105439</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6965,36 +6984,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7003,13 +7013,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707538</v>
+        <v>707652</v>
       </c>
       <c r="R54" t="n">
-        <v>6375024</v>
+        <v>6374986</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7043,7 +7053,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7075,10 +7085,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578774</v>
+        <v>122578750</v>
       </c>
       <c r="B55" t="n">
-        <v>99768</v>
+        <v>98263</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7087,35 +7097,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7129,13 +7139,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707528</v>
+        <v>707569</v>
       </c>
       <c r="R55" t="n">
-        <v>6375154</v>
+        <v>6374979</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7167,6 +7177,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7178,7 +7193,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7196,10 +7211,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578782</v>
+        <v>122578751</v>
       </c>
       <c r="B56" t="n">
-        <v>98218</v>
+        <v>98219</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7231,7 +7246,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7250,13 +7265,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707621</v>
+        <v>707569</v>
       </c>
       <c r="R56" t="n">
-        <v>6375108</v>
+        <v>6374979</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7286,6 +7301,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7317,10 +7337,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578747</v>
+        <v>122578805</v>
       </c>
       <c r="B57" t="n">
-        <v>105438</v>
+        <v>98219</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7329,38 +7349,52 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707590</v>
+        <v>707697</v>
       </c>
       <c r="R57" t="n">
-        <v>6375036</v>
+        <v>6374980</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7393,11 +7427,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7429,10 +7458,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578769</v>
+        <v>122578744</v>
       </c>
       <c r="B58" t="n">
-        <v>99768</v>
+        <v>105439</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7445,26 +7474,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7474,7 +7503,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7483,13 +7512,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707513</v>
+        <v>707626</v>
       </c>
       <c r="R58" t="n">
-        <v>6375053</v>
+        <v>6375071</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7523,7 +7552,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7537,7 +7566,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7555,10 +7584,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578752</v>
+        <v>122578802</v>
       </c>
       <c r="B59" t="n">
-        <v>99768</v>
+        <v>98219</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7567,35 +7596,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7609,13 +7638,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707569</v>
+        <v>707697</v>
       </c>
       <c r="R59" t="n">
-        <v>6374979</v>
+        <v>6374969</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7645,11 +7674,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7681,10 +7705,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578821</v>
+        <v>122578776</v>
       </c>
       <c r="B60" t="n">
-        <v>105438</v>
+        <v>99769</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7697,26 +7721,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7726,7 +7750,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7735,13 +7759,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707605</v>
+        <v>707584</v>
       </c>
       <c r="R60" t="n">
-        <v>6374970</v>
+        <v>6375172</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7773,11 +7797,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Minsta antal + spridd.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7789,7 +7808,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7807,10 +7826,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578763</v>
+        <v>122578774</v>
       </c>
       <c r="B61" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7842,7 +7861,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7861,13 +7880,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707548</v>
+        <v>707528</v>
       </c>
       <c r="R61" t="n">
-        <v>6375014</v>
+        <v>6375154</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7899,11 +7918,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7915,7 +7929,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7933,10 +7947,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578760</v>
+        <v>122578821</v>
       </c>
       <c r="B62" t="n">
-        <v>105438</v>
+        <v>105439</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7968,12 +7982,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -7987,10 +8001,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707547</v>
+        <v>707605</v>
       </c>
       <c r="R62" t="n">
-        <v>6375010</v>
+        <v>6374970</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8027,7 +8041,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8041,7 +8055,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8059,10 +8073,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578767</v>
+        <v>122578771</v>
       </c>
       <c r="B63" t="n">
-        <v>98262</v>
+        <v>98219</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8075,21 +8089,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8099,7 +8113,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8113,10 +8127,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707513</v>
+        <v>707490</v>
       </c>
       <c r="R63" t="n">
-        <v>6375053</v>
+        <v>6375090</v>
       </c>
       <c r="S63" t="n">
         <v>7</v>
@@ -8149,6 +8163,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8180,10 +8199,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578759</v>
+        <v>122578824</v>
       </c>
       <c r="B64" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8215,7 +8234,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8234,13 +8253,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707557</v>
+        <v>707606</v>
       </c>
       <c r="R64" t="n">
-        <v>6375009</v>
+        <v>6374961</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8272,11 +8291,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8288,7 +8302,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8306,10 +8320,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578785</v>
+        <v>122578756</v>
       </c>
       <c r="B65" t="n">
-        <v>105438</v>
+        <v>99769</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8322,27 +8336,36 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8351,13 +8374,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707648</v>
+        <v>707541</v>
       </c>
       <c r="R65" t="n">
-        <v>6375072</v>
+        <v>6374993</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8391,7 +8414,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8423,10 +8446,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578756</v>
+        <v>122578743</v>
       </c>
       <c r="B66" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8456,34 +8479,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707541</v>
+        <v>707638</v>
       </c>
       <c r="R66" t="n">
-        <v>6374993</v>
+        <v>6375036</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8517,7 +8526,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8549,10 +8558,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578773</v>
+        <v>122578755</v>
       </c>
       <c r="B67" t="n">
-        <v>99768</v>
+        <v>98219</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8561,35 +8570,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8603,10 +8612,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707489</v>
+        <v>707541</v>
       </c>
       <c r="R67" t="n">
-        <v>6375140</v>
+        <v>6374993</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -8641,6 +8650,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8652,7 +8666,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8670,10 +8684,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578778</v>
+        <v>122578741</v>
       </c>
       <c r="B68" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8703,34 +8717,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707599</v>
+        <v>707609</v>
       </c>
       <c r="R68" t="n">
-        <v>6375165</v>
+        <v>6375033</v>
       </c>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Barrblandskog mot åker i N.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8796,10 +8796,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578753</v>
+        <v>122578760</v>
       </c>
       <c r="B69" t="n">
-        <v>98218</v>
+        <v>105439</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8808,40 +8808,40 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707554</v>
+        <v>707547</v>
       </c>
       <c r="R69" t="n">
-        <v>6374978</v>
+        <v>6375010</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8922,10 +8922,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578823</v>
+        <v>122578796</v>
       </c>
       <c r="B70" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8955,16 +8955,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8976,10 +8967,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707605</v>
+        <v>707725</v>
       </c>
       <c r="R70" t="n">
-        <v>6374970</v>
+        <v>6374976</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9016,7 +9007,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9030,7 +9021,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9048,10 +9039,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578807</v>
+        <v>122578817</v>
       </c>
       <c r="B71" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9081,7 +9072,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707678</v>
+        <v>707624</v>
       </c>
       <c r="R71" t="n">
-        <v>6374990</v>
+        <v>6374996</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9133,7 +9133,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -3804,10 +3804,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578747</v>
+        <v>122578814</v>
       </c>
       <c r="B28" t="n">
-        <v>105439</v>
+        <v>98219</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3816,38 +3816,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707590</v>
+        <v>707638</v>
       </c>
       <c r="R28" t="n">
-        <v>6375036</v>
+        <v>6374988</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3880,11 +3894,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3916,7 +3925,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578812</v>
+        <v>122578747</v>
       </c>
       <c r="B29" t="n">
         <v>105439</v>
@@ -3950,21 +3959,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707646</v>
+        <v>707590</v>
       </c>
       <c r="R29" t="n">
-        <v>6374967</v>
+        <v>6375036</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4001,7 +4005,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4033,7 +4037,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578742</v>
+        <v>122578812</v>
       </c>
       <c r="B30" t="n">
         <v>105439</v>
@@ -4067,19 +4071,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707638</v>
+        <v>707646</v>
       </c>
       <c r="R30" t="n">
-        <v>6375036</v>
+        <v>6374967</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4113,7 +4122,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4145,10 +4154,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578814</v>
+        <v>122578742</v>
       </c>
       <c r="B31" t="n">
-        <v>98219</v>
+        <v>105439</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4157,42 +4166,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
@@ -4202,10 +4197,10 @@
         <v>707638</v>
       </c>
       <c r="R31" t="n">
-        <v>6374988</v>
+        <v>6375036</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4235,6 +4230,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5741,10 +5741,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578767</v>
+        <v>122578818</v>
       </c>
       <c r="B44" t="n">
-        <v>98263</v>
+        <v>105439</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5753,40 +5753,40 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219862</v>
+        <v>671</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5795,13 +5795,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707513</v>
+        <v>707605</v>
       </c>
       <c r="R44" t="n">
-        <v>6375053</v>
+        <v>6374982</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5833,6 +5833,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5844,7 +5849,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5862,7 +5867,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578818</v>
+        <v>122578758</v>
       </c>
       <c r="B45" t="n">
         <v>105439</v>
@@ -5897,7 +5902,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5916,13 +5921,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707605</v>
+        <v>707557</v>
       </c>
       <c r="R45" t="n">
-        <v>6374982</v>
+        <v>6375009</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5956,7 +5961,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5970,7 +5975,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5988,10 +5993,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578758</v>
+        <v>122578780</v>
       </c>
       <c r="B46" t="n">
-        <v>105439</v>
+        <v>99769</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6004,36 +6009,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6042,13 +6038,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707557</v>
+        <v>707626</v>
       </c>
       <c r="R46" t="n">
-        <v>6375009</v>
+        <v>6375120</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6082,7 +6078,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6114,7 +6110,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578780</v>
+        <v>122578773</v>
       </c>
       <c r="B47" t="n">
         <v>99769</v>
@@ -6147,7 +6143,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6159,13 +6164,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707626</v>
+        <v>707489</v>
       </c>
       <c r="R47" t="n">
-        <v>6375120</v>
+        <v>6375140</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6197,11 +6202,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578773</v>
+        <v>122578767</v>
       </c>
       <c r="B48" t="n">
-        <v>99769</v>
+        <v>98263</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6243,35 +6243,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6285,13 +6285,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707489</v>
+        <v>707513</v>
       </c>
       <c r="R48" t="n">
-        <v>6375140</v>
+        <v>6375053</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6968,10 +6968,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578809</v>
+        <v>122578750</v>
       </c>
       <c r="B54" t="n">
-        <v>105439</v>
+        <v>98263</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6980,31 +6980,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>671</v>
+        <v>219862</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7013,13 +7022,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707652</v>
+        <v>707569</v>
       </c>
       <c r="R54" t="n">
-        <v>6374986</v>
+        <v>6374979</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7053,7 +7062,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7085,10 +7094,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578750</v>
+        <v>122578809</v>
       </c>
       <c r="B55" t="n">
-        <v>98263</v>
+        <v>105439</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7097,40 +7106,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219862</v>
+        <v>671</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7139,13 +7139,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707569</v>
+        <v>707652</v>
       </c>
       <c r="R55" t="n">
-        <v>6374979</v>
+        <v>6374986</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8199,10 +8199,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578824</v>
+        <v>122578755</v>
       </c>
       <c r="B64" t="n">
-        <v>99769</v>
+        <v>98219</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8211,35 +8211,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8253,13 +8253,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707606</v>
+        <v>707541</v>
       </c>
       <c r="R64" t="n">
-        <v>6374961</v>
+        <v>6374993</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8291,6 +8291,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8302,7 +8307,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8320,7 +8325,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578756</v>
+        <v>122578824</v>
       </c>
       <c r="B65" t="n">
         <v>99769</v>
@@ -8355,7 +8360,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8374,13 +8379,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707541</v>
+        <v>707606</v>
       </c>
       <c r="R65" t="n">
-        <v>6374993</v>
+        <v>6374961</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8412,11 +8417,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8446,7 +8446,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578743</v>
+        <v>122578756</v>
       </c>
       <c r="B66" t="n">
         <v>99769</v>
@@ -8479,20 +8479,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707638</v>
+        <v>707541</v>
       </c>
       <c r="R66" t="n">
-        <v>6375036</v>
+        <v>6374993</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8526,7 +8540,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8558,10 +8572,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578755</v>
+        <v>122578743</v>
       </c>
       <c r="B67" t="n">
-        <v>98219</v>
+        <v>99769</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8570,55 +8584,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707541</v>
+        <v>707638</v>
       </c>
       <c r="R67" t="n">
-        <v>6374993</v>
+        <v>6375036</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578803</v>
+        <v>122578825</v>
       </c>
       <c r="B3" t="n">
-        <v>105439</v>
+        <v>99772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,27 +826,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +864,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707697</v>
+        <v>707611</v>
       </c>
       <c r="R3" t="n">
-        <v>6374980</v>
+        <v>6374954</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,11 +902,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -909,7 +913,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578801</v>
+        <v>122578760</v>
       </c>
       <c r="B4" t="n">
-        <v>99769</v>
+        <v>105442</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,27 +947,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -972,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707697</v>
+        <v>707547</v>
       </c>
       <c r="R4" t="n">
-        <v>6374980</v>
+        <v>6375010</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1012,7 +1025,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1057,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578823</v>
+        <v>122578795</v>
       </c>
       <c r="B5" t="n">
-        <v>99769</v>
+        <v>105442</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,36 +1073,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1098,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707605</v>
+        <v>707725</v>
       </c>
       <c r="R5" t="n">
-        <v>6374970</v>
+        <v>6374976</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1138,7 +1142,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,7 +1156,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,10 +1174,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578740</v>
+        <v>122578805</v>
       </c>
       <c r="B6" t="n">
-        <v>105439</v>
+        <v>98222</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,41 +1186,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707609</v>
+        <v>707697</v>
       </c>
       <c r="R6" t="n">
-        <v>6375033</v>
+        <v>6374980</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,11 +1264,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578816</v>
+        <v>122578802</v>
       </c>
       <c r="B7" t="n">
-        <v>99769</v>
+        <v>98222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,28 +1307,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1327,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707638</v>
+        <v>707697</v>
       </c>
       <c r="R7" t="n">
-        <v>6374988</v>
+        <v>6374969</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1363,11 +1385,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578783</v>
+        <v>122578762</v>
       </c>
       <c r="B8" t="n">
-        <v>99769</v>
+        <v>105442</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,27 +1432,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1444,13 +1470,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707633</v>
+        <v>707548</v>
       </c>
       <c r="R8" t="n">
-        <v>6375094</v>
+        <v>6375014</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1484,7 +1510,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,10 +1542,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578748</v>
+        <v>122578749</v>
       </c>
       <c r="B9" t="n">
-        <v>99769</v>
+        <v>105442</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,34 +1558,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707590</v>
+        <v>707570</v>
       </c>
       <c r="R9" t="n">
-        <v>6375036</v>
+        <v>6374984</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1596,7 +1636,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,10 +1668,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578770</v>
+        <v>122578780</v>
       </c>
       <c r="B10" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,16 +1701,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1682,13 +1713,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707506</v>
+        <v>707626</v>
       </c>
       <c r="R10" t="n">
-        <v>6375077</v>
+        <v>6375120</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,7 +1753,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,7 +1767,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1754,10 +1785,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578764</v>
+        <v>122578824</v>
       </c>
       <c r="B11" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,7 +1820,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1808,13 +1839,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707538</v>
+        <v>707606</v>
       </c>
       <c r="R11" t="n">
-        <v>6375024</v>
+        <v>6374961</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1846,11 +1877,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1862,7 +1888,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1880,10 +1906,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578813</v>
+        <v>122578816</v>
       </c>
       <c r="B12" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1925,10 +1951,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707646</v>
+        <v>707638</v>
       </c>
       <c r="R12" t="n">
-        <v>6374967</v>
+        <v>6374988</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1965,7 +1991,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,10 +2023,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578781</v>
+        <v>122578801</v>
       </c>
       <c r="B13" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2042,10 +2068,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707621</v>
+        <v>707697</v>
       </c>
       <c r="R13" t="n">
-        <v>6375108</v>
+        <v>6374980</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2082,7 +2108,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,7 +2143,7 @@
         <v>122578766</v>
       </c>
       <c r="B14" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2240,10 +2266,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578806</v>
+        <v>122578769</v>
       </c>
       <c r="B15" t="n">
-        <v>105439</v>
+        <v>99772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2256,27 +2282,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2285,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707678</v>
+        <v>707513</v>
       </c>
       <c r="R15" t="n">
-        <v>6374990</v>
+        <v>6375053</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2325,7 +2360,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2339,7 +2374,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2357,10 +2392,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578786</v>
+        <v>122578815</v>
       </c>
       <c r="B16" t="n">
-        <v>98219</v>
+        <v>105442</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,40 +2404,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2411,10 +2437,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707652</v>
+        <v>707638</v>
       </c>
       <c r="R16" t="n">
-        <v>6375083</v>
+        <v>6374988</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2451,7 +2477,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2483,10 +2509,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578753</v>
+        <v>122578758</v>
       </c>
       <c r="B17" t="n">
-        <v>98219</v>
+        <v>105442</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,40 +2521,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2537,13 +2563,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707554</v>
+        <v>707557</v>
       </c>
       <c r="R17" t="n">
-        <v>6374978</v>
+        <v>6375009</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2609,10 +2635,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578754</v>
+        <v>122578776</v>
       </c>
       <c r="B18" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2644,7 +2670,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2663,13 +2689,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707554</v>
+        <v>707584</v>
       </c>
       <c r="R18" t="n">
-        <v>6374978</v>
+        <v>6375172</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2701,11 +2727,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2717,7 +2738,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2735,10 +2756,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578765</v>
+        <v>122578810</v>
       </c>
       <c r="B19" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2780,13 +2801,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707532</v>
+        <v>707652</v>
       </c>
       <c r="R19" t="n">
-        <v>6375035</v>
+        <v>6374986</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2820,7 +2841,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2852,10 +2873,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578779</v>
+        <v>122578748</v>
       </c>
       <c r="B20" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,24 +2907,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707597</v>
+        <v>707590</v>
       </c>
       <c r="R20" t="n">
-        <v>6375142</v>
+        <v>6375036</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2937,7 +2953,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2951,7 +2967,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2969,10 +2985,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578785</v>
+        <v>122578800</v>
       </c>
       <c r="B21" t="n">
-        <v>105439</v>
+        <v>105442</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3002,7 +3018,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3014,10 +3039,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707648</v>
+        <v>707697</v>
       </c>
       <c r="R21" t="n">
-        <v>6375072</v>
+        <v>6374980</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3054,7 +3079,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3086,10 +3111,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578784</v>
+        <v>122578773</v>
       </c>
       <c r="B22" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3119,7 +3144,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3131,13 +3165,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707648</v>
+        <v>707489</v>
       </c>
       <c r="R22" t="n">
-        <v>6375072</v>
+        <v>6375140</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3169,11 +3203,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3185,7 +3214,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3203,10 +3232,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578775</v>
+        <v>122578809</v>
       </c>
       <c r="B23" t="n">
-        <v>99769</v>
+        <v>105442</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3219,36 +3248,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3257,13 +3277,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707564</v>
+        <v>707652</v>
       </c>
       <c r="R23" t="n">
-        <v>6375169</v>
+        <v>6374986</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3295,6 +3315,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3306,7 +3331,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3324,10 +3349,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578778</v>
+        <v>122578806</v>
       </c>
       <c r="B24" t="n">
-        <v>99769</v>
+        <v>105442</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3340,36 +3365,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3378,13 +3394,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707599</v>
+        <v>707678</v>
       </c>
       <c r="R24" t="n">
-        <v>6375165</v>
+        <v>6374990</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3418,7 +3434,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Barrblandskog mot åker i N.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,7 +3448,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3450,10 +3466,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578825</v>
+        <v>122578755</v>
       </c>
       <c r="B25" t="n">
-        <v>99769</v>
+        <v>98222</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3462,35 +3478,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3504,13 +3520,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707611</v>
+        <v>707541</v>
       </c>
       <c r="R25" t="n">
-        <v>6374954</v>
+        <v>6374993</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3542,6 +3558,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3553,7 +3574,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3571,10 +3592,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578746</v>
+        <v>122578786</v>
       </c>
       <c r="B26" t="n">
-        <v>99769</v>
+        <v>98222</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3583,41 +3604,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707626</v>
+        <v>707652</v>
       </c>
       <c r="R26" t="n">
-        <v>6375071</v>
+        <v>6375083</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3651,7 +3686,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3683,10 +3718,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578782</v>
+        <v>122578814</v>
       </c>
       <c r="B27" t="n">
-        <v>98219</v>
+        <v>98222</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3718,7 +3753,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3737,10 +3772,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707621</v>
+        <v>707638</v>
       </c>
       <c r="R27" t="n">
-        <v>6375108</v>
+        <v>6374988</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3804,10 +3839,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578814</v>
+        <v>122578783</v>
       </c>
       <c r="B28" t="n">
-        <v>98219</v>
+        <v>99772</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3816,37 +3851,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3858,13 +3884,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707638</v>
+        <v>707633</v>
       </c>
       <c r="R28" t="n">
-        <v>6374988</v>
+        <v>6375094</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3894,6 +3920,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3925,10 +3956,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578747</v>
+        <v>122578796</v>
       </c>
       <c r="B29" t="n">
-        <v>105439</v>
+        <v>99772</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3941,34 +3972,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707590</v>
+        <v>707725</v>
       </c>
       <c r="R29" t="n">
-        <v>6375036</v>
+        <v>6374976</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4005,7 +4041,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4037,10 +4073,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578812</v>
+        <v>122578742</v>
       </c>
       <c r="B30" t="n">
-        <v>105439</v>
+        <v>105442</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4071,24 +4107,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707646</v>
+        <v>707638</v>
       </c>
       <c r="R30" t="n">
-        <v>6374967</v>
+        <v>6375036</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4122,7 +4153,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4154,10 +4185,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578742</v>
+        <v>122578808</v>
       </c>
       <c r="B31" t="n">
-        <v>105439</v>
+        <v>98222</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4166,41 +4197,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707638</v>
+        <v>707678</v>
       </c>
       <c r="R31" t="n">
-        <v>6375036</v>
+        <v>6374990</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4230,11 +4275,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4266,10 +4306,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578797</v>
+        <v>122578774</v>
       </c>
       <c r="B32" t="n">
-        <v>98219</v>
+        <v>99772</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4278,35 +4318,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4320,13 +4360,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707725</v>
+        <v>707528</v>
       </c>
       <c r="R32" t="n">
-        <v>6374976</v>
+        <v>6375154</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4369,7 +4409,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4387,10 +4427,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578815</v>
+        <v>122578765</v>
       </c>
       <c r="B33" t="n">
-        <v>105439</v>
+        <v>99772</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4403,27 +4443,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4432,13 +4472,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707638</v>
+        <v>707532</v>
       </c>
       <c r="R33" t="n">
-        <v>6374988</v>
+        <v>6375035</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4472,7 +4512,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4504,10 +4544,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578769</v>
+        <v>122578756</v>
       </c>
       <c r="B34" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4539,7 +4579,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4558,13 +4598,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707513</v>
+        <v>707541</v>
       </c>
       <c r="R34" t="n">
-        <v>6375053</v>
+        <v>6374993</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4598,7 +4638,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4612,7 +4652,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4630,10 +4670,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578752</v>
+        <v>122578782</v>
       </c>
       <c r="B35" t="n">
-        <v>99769</v>
+        <v>98222</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4642,25 +4682,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4670,7 +4710,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4684,13 +4724,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707569</v>
+        <v>707621</v>
       </c>
       <c r="R35" t="n">
-        <v>6374979</v>
+        <v>6375108</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4720,11 +4760,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4756,10 +4791,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578762</v>
+        <v>122578823</v>
       </c>
       <c r="B36" t="n">
-        <v>105439</v>
+        <v>99772</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4772,36 +4807,36 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4810,13 +4845,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707548</v>
+        <v>707605</v>
       </c>
       <c r="R36" t="n">
-        <v>6375014</v>
+        <v>6374970</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4850,7 +4885,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4864,7 +4899,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4882,10 +4917,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578749</v>
+        <v>122578779</v>
       </c>
       <c r="B37" t="n">
-        <v>105439</v>
+        <v>99772</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4898,36 +4933,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4936,13 +4962,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707570</v>
+        <v>707597</v>
       </c>
       <c r="R37" t="n">
-        <v>6374984</v>
+        <v>6375142</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4976,7 +5002,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Enstaka strå.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4990,7 +5016,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5008,10 +5034,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578763</v>
+        <v>122578747</v>
       </c>
       <c r="B38" t="n">
-        <v>99769</v>
+        <v>105442</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5024,51 +5050,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707548</v>
+        <v>707590</v>
       </c>
       <c r="R38" t="n">
-        <v>6375014</v>
+        <v>6375036</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5102,7 +5114,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5134,10 +5146,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578807</v>
+        <v>122578767</v>
       </c>
       <c r="B39" t="n">
-        <v>99769</v>
+        <v>98266</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5146,28 +5158,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5179,13 +5200,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707678</v>
+        <v>707513</v>
       </c>
       <c r="R39" t="n">
-        <v>6374990</v>
+        <v>6375053</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5217,11 +5238,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5233,7 +5249,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5251,10 +5267,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578772</v>
+        <v>122578797</v>
       </c>
       <c r="B40" t="n">
-        <v>99769</v>
+        <v>98222</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5263,35 +5279,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5305,13 +5321,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707506</v>
+        <v>707725</v>
       </c>
       <c r="R40" t="n">
-        <v>6375110</v>
+        <v>6374976</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5343,11 +5359,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>2 ex.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5359,7 +5370,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5377,10 +5388,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578777</v>
+        <v>122578751</v>
       </c>
       <c r="B41" t="n">
-        <v>99769</v>
+        <v>98222</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5389,35 +5400,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5431,13 +5442,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707591</v>
+        <v>707569</v>
       </c>
       <c r="R41" t="n">
-        <v>6375187</v>
+        <v>6374979</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5471,7 +5482,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>30 m S åker i N.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5485,7 +5496,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5503,10 +5514,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578795</v>
+        <v>122578754</v>
       </c>
       <c r="B42" t="n">
-        <v>105439</v>
+        <v>99772</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5519,27 +5530,36 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5548,10 +5568,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707725</v>
+        <v>707554</v>
       </c>
       <c r="R42" t="n">
-        <v>6374976</v>
+        <v>6374978</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5588,7 +5608,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5620,10 +5640,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578811</v>
+        <v>122578778</v>
       </c>
       <c r="B43" t="n">
-        <v>98219</v>
+        <v>99772</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5632,35 +5652,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5674,13 +5694,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707652</v>
+        <v>707599</v>
       </c>
       <c r="R43" t="n">
-        <v>6374986</v>
+        <v>6375165</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5712,6 +5732,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Barrblandskog mot åker i N.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5723,7 +5748,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5741,10 +5766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578818</v>
+        <v>122578785</v>
       </c>
       <c r="B44" t="n">
-        <v>105439</v>
+        <v>105442</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5774,16 +5799,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5795,10 +5811,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707605</v>
+        <v>707648</v>
       </c>
       <c r="R44" t="n">
-        <v>6374982</v>
+        <v>6375072</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5835,7 +5851,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5849,7 +5865,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5867,10 +5883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578758</v>
+        <v>122578763</v>
       </c>
       <c r="B45" t="n">
-        <v>105439</v>
+        <v>99772</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5883,36 +5899,36 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5921,10 +5937,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707557</v>
+        <v>707548</v>
       </c>
       <c r="R45" t="n">
-        <v>6375009</v>
+        <v>6375014</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5993,10 +6009,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578780</v>
+        <v>122578759</v>
       </c>
       <c r="B46" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6026,7 +6042,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6038,13 +6063,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707626</v>
+        <v>707557</v>
       </c>
       <c r="R46" t="n">
-        <v>6375120</v>
+        <v>6375009</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6078,7 +6103,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6110,10 +6135,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578773</v>
+        <v>122578752</v>
       </c>
       <c r="B47" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6145,7 +6170,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6164,10 +6189,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707489</v>
+        <v>707569</v>
       </c>
       <c r="R47" t="n">
-        <v>6375140</v>
+        <v>6374979</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -6202,6 +6227,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6213,7 +6243,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6231,10 +6261,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578767</v>
+        <v>122578770</v>
       </c>
       <c r="B48" t="n">
-        <v>98263</v>
+        <v>99772</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6243,35 +6273,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6285,10 +6315,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707513</v>
+        <v>707506</v>
       </c>
       <c r="R48" t="n">
-        <v>6375053</v>
+        <v>6375077</v>
       </c>
       <c r="S48" t="n">
         <v>7</v>
@@ -6321,6 +6351,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6352,10 +6387,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578808</v>
+        <v>122578743</v>
       </c>
       <c r="B49" t="n">
-        <v>98219</v>
+        <v>99772</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6364,55 +6399,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707678</v>
+        <v>707638</v>
       </c>
       <c r="R49" t="n">
-        <v>6374990</v>
+        <v>6375036</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6442,6 +6463,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6473,10 +6499,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578757</v>
+        <v>122578772</v>
       </c>
       <c r="B50" t="n">
-        <v>98219</v>
+        <v>99772</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6485,35 +6511,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6527,13 +6553,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707557</v>
+        <v>707506</v>
       </c>
       <c r="R50" t="n">
-        <v>6375009</v>
+        <v>6375110</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6567,7 +6593,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6581,7 +6607,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6599,10 +6625,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578759</v>
+        <v>122578817</v>
       </c>
       <c r="B51" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6634,7 +6660,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6653,13 +6679,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707557</v>
+        <v>707624</v>
       </c>
       <c r="R51" t="n">
-        <v>6375009</v>
+        <v>6374996</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6693,7 +6719,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6725,10 +6751,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578810</v>
+        <v>122578746</v>
       </c>
       <c r="B52" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6759,24 +6785,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707652</v>
+        <v>707626</v>
       </c>
       <c r="R52" t="n">
-        <v>6374986</v>
+        <v>6375071</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6810,7 +6831,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6842,10 +6863,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578819</v>
+        <v>122578740</v>
       </c>
       <c r="B53" t="n">
-        <v>99769</v>
+        <v>105442</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6858,51 +6879,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707605</v>
+        <v>707609</v>
       </c>
       <c r="R53" t="n">
-        <v>6374982</v>
+        <v>6375033</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6936,7 +6943,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6950,7 +6957,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6968,10 +6975,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578750</v>
+        <v>122578812</v>
       </c>
       <c r="B54" t="n">
-        <v>98263</v>
+        <v>105442</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6980,40 +6987,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219862</v>
+        <v>671</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7022,13 +7020,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707569</v>
+        <v>707646</v>
       </c>
       <c r="R54" t="n">
-        <v>6374979</v>
+        <v>6374967</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7062,7 +7060,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7094,10 +7092,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578809</v>
+        <v>122578818</v>
       </c>
       <c r="B55" t="n">
-        <v>105439</v>
+        <v>105442</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7127,7 +7125,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7139,10 +7146,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707652</v>
+        <v>707605</v>
       </c>
       <c r="R55" t="n">
-        <v>6374986</v>
+        <v>6374982</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7179,7 +7186,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7193,7 +7200,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7211,10 +7218,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578751</v>
+        <v>122578741</v>
       </c>
       <c r="B56" t="n">
-        <v>98219</v>
+        <v>99772</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7223,55 +7230,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707569</v>
+        <v>707609</v>
       </c>
       <c r="R56" t="n">
-        <v>6374979</v>
+        <v>6375033</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7305,7 +7298,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7337,10 +7330,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578805</v>
+        <v>122578819</v>
       </c>
       <c r="B57" t="n">
-        <v>98219</v>
+        <v>99772</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7349,35 +7342,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7391,10 +7384,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707697</v>
+        <v>707605</v>
       </c>
       <c r="R57" t="n">
-        <v>6374980</v>
+        <v>6374982</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7429,6 +7422,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7440,7 +7438,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7458,10 +7456,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578744</v>
+        <v>122578821</v>
       </c>
       <c r="B58" t="n">
-        <v>105439</v>
+        <v>105442</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7493,7 +7491,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7512,13 +7510,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707626</v>
+        <v>707605</v>
       </c>
       <c r="R58" t="n">
-        <v>6375071</v>
+        <v>6374970</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7552,7 +7550,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7566,7 +7564,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7584,10 +7582,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578802</v>
+        <v>122578753</v>
       </c>
       <c r="B59" t="n">
-        <v>98219</v>
+        <v>98222</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7619,7 +7617,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7638,10 +7636,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707697</v>
+        <v>707554</v>
       </c>
       <c r="R59" t="n">
-        <v>6374969</v>
+        <v>6374978</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7674,6 +7672,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7705,10 +7708,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578776</v>
+        <v>122578781</v>
       </c>
       <c r="B60" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7738,16 +7741,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7759,13 +7753,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707584</v>
+        <v>707621</v>
       </c>
       <c r="R60" t="n">
-        <v>6375172</v>
+        <v>6375108</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7797,6 +7791,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Glest spridd.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7808,7 +7807,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7826,10 +7825,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578774</v>
+        <v>122578784</v>
       </c>
       <c r="B61" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7859,16 +7858,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7880,13 +7870,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707528</v>
+        <v>707648</v>
       </c>
       <c r="R61" t="n">
-        <v>6375154</v>
+        <v>6375072</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7918,6 +7908,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Glest spridd, men saknas mot O-NO..</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7929,7 +7924,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7947,10 +7942,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578821</v>
+        <v>122578764</v>
       </c>
       <c r="B62" t="n">
-        <v>105439</v>
+        <v>99772</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7963,26 +7958,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7992,7 +7987,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8001,13 +7996,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707605</v>
+        <v>707538</v>
       </c>
       <c r="R62" t="n">
-        <v>6374970</v>
+        <v>6375024</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8041,7 +8036,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8055,7 +8050,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8073,10 +8068,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578771</v>
+        <v>122578750</v>
       </c>
       <c r="B63" t="n">
-        <v>98219</v>
+        <v>98266</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8089,31 +8084,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8127,13 +8122,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707490</v>
+        <v>707569</v>
       </c>
       <c r="R63" t="n">
-        <v>6375090</v>
+        <v>6374979</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8167,7 +8162,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8181,7 +8176,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8199,10 +8194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578755</v>
+        <v>122578771</v>
       </c>
       <c r="B64" t="n">
-        <v>98219</v>
+        <v>98222</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8239,7 +8234,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8253,13 +8248,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707541</v>
+        <v>707490</v>
       </c>
       <c r="R64" t="n">
-        <v>6374993</v>
+        <v>6375090</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8293,7 +8288,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8307,7 +8302,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8325,10 +8320,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578824</v>
+        <v>122578775</v>
       </c>
       <c r="B65" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8360,7 +8355,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8379,13 +8374,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707606</v>
+        <v>707564</v>
       </c>
       <c r="R65" t="n">
-        <v>6374961</v>
+        <v>6375169</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8428,7 +8423,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8446,10 +8441,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578756</v>
+        <v>122578813</v>
       </c>
       <c r="B66" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8479,16 +8474,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8500,13 +8486,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707541</v>
+        <v>707646</v>
       </c>
       <c r="R66" t="n">
-        <v>6374993</v>
+        <v>6374967</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8540,7 +8526,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8572,10 +8558,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578743</v>
+        <v>122578757</v>
       </c>
       <c r="B67" t="n">
-        <v>99769</v>
+        <v>98222</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8584,41 +8570,55 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707638</v>
+        <v>707557</v>
       </c>
       <c r="R67" t="n">
-        <v>6375036</v>
+        <v>6375009</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8684,10 +8684,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578741</v>
+        <v>122578777</v>
       </c>
       <c r="B68" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8717,20 +8717,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707609</v>
+        <v>707591</v>
       </c>
       <c r="R68" t="n">
-        <v>6375033</v>
+        <v>6375187</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8764,7 +8778,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>30 m S åker i N.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8778,7 +8792,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8796,10 +8810,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578760</v>
+        <v>122578811</v>
       </c>
       <c r="B69" t="n">
-        <v>105439</v>
+        <v>98222</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8808,40 +8822,40 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8850,10 +8864,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707547</v>
+        <v>707652</v>
       </c>
       <c r="R69" t="n">
-        <v>6375010</v>
+        <v>6374986</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8886,11 +8900,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8922,10 +8931,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578796</v>
+        <v>122578807</v>
       </c>
       <c r="B70" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8967,10 +8976,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707725</v>
+        <v>707678</v>
       </c>
       <c r="R70" t="n">
-        <v>6374976</v>
+        <v>6374990</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9039,10 +9048,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578817</v>
+        <v>122578744</v>
       </c>
       <c r="B71" t="n">
-        <v>99769</v>
+        <v>105442</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9055,26 +9064,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9084,7 +9093,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9093,13 +9102,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707624</v>
+        <v>707626</v>
       </c>
       <c r="R71" t="n">
-        <v>6374996</v>
+        <v>6375071</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9133,7 +9142,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578825</v>
+        <v>122578786</v>
       </c>
       <c r="B3" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707611</v>
+        <v>707652</v>
       </c>
       <c r="R3" t="n">
-        <v>6374954</v>
+        <v>6375083</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -902,6 +902,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -913,7 +918,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -931,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578760</v>
+        <v>122578753</v>
       </c>
       <c r="B4" t="n">
-        <v>105442</v>
+        <v>98222</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,40 +948,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -985,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707547</v>
+        <v>707554</v>
       </c>
       <c r="R4" t="n">
-        <v>6375010</v>
+        <v>6374978</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1057,7 +1062,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578795</v>
+        <v>122578740</v>
       </c>
       <c r="B5" t="n">
         <v>105442</v>
@@ -1091,24 +1096,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707725</v>
+        <v>707609</v>
       </c>
       <c r="R5" t="n">
-        <v>6374976</v>
+        <v>6375033</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,10 +1174,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578805</v>
+        <v>122578754</v>
       </c>
       <c r="B6" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,35 +1186,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707697</v>
+        <v>707554</v>
       </c>
       <c r="R6" t="n">
-        <v>6374980</v>
+        <v>6374978</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1264,6 +1264,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578802</v>
+        <v>122578823</v>
       </c>
       <c r="B7" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,35 +1312,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1349,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707697</v>
+        <v>707605</v>
       </c>
       <c r="R7" t="n">
-        <v>6374969</v>
+        <v>6374970</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1387,6 +1392,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1398,7 +1408,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1416,10 +1426,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578762</v>
+        <v>122578807</v>
       </c>
       <c r="B8" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,36 +1442,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1470,13 +1471,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707548</v>
+        <v>707678</v>
       </c>
       <c r="R8" t="n">
-        <v>6375014</v>
+        <v>6374990</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1510,7 +1511,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578749</v>
+        <v>122578756</v>
       </c>
       <c r="B9" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1558,36 +1559,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1596,13 +1597,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707570</v>
+        <v>707541</v>
       </c>
       <c r="R9" t="n">
-        <v>6374984</v>
+        <v>6374993</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1668,7 +1669,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578780</v>
+        <v>122578763</v>
       </c>
       <c r="B10" t="n">
         <v>99772</v>
@@ -1701,7 +1702,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1713,13 +1723,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707626</v>
+        <v>707548</v>
       </c>
       <c r="R10" t="n">
-        <v>6375120</v>
+        <v>6375014</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1753,7 +1763,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,10 +1795,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578824</v>
+        <v>122578750</v>
       </c>
       <c r="B11" t="n">
-        <v>99772</v>
+        <v>98266</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1797,35 +1807,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1839,13 +1849,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707606</v>
+        <v>707569</v>
       </c>
       <c r="R11" t="n">
-        <v>6374961</v>
+        <v>6374979</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1877,6 +1887,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1888,7 +1903,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1906,10 +1921,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578816</v>
+        <v>122578744</v>
       </c>
       <c r="B12" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1922,27 +1937,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1951,13 +1975,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707638</v>
+        <v>707626</v>
       </c>
       <c r="R12" t="n">
-        <v>6374988</v>
+        <v>6375071</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1991,7 +2015,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,10 +2047,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578801</v>
+        <v>122578803</v>
       </c>
       <c r="B13" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2039,27 +2063,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2108,7 +2132,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,7 +2164,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578766</v>
+        <v>122578759</v>
       </c>
       <c r="B14" t="n">
         <v>99772</v>
@@ -2175,12 +2199,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2194,13 +2218,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707548</v>
+        <v>707557</v>
       </c>
       <c r="R14" t="n">
-        <v>6375091</v>
+        <v>6375009</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2234,7 +2258,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,7 +2272,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2266,10 +2290,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578769</v>
+        <v>122578821</v>
       </c>
       <c r="B15" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2282,26 +2306,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2311,7 +2335,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,13 +2344,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707513</v>
+        <v>707605</v>
       </c>
       <c r="R15" t="n">
-        <v>6375053</v>
+        <v>6374970</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2360,7 +2384,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2374,7 +2398,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2392,10 +2416,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578815</v>
+        <v>122578819</v>
       </c>
       <c r="B16" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2408,27 +2432,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2437,10 +2470,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707638</v>
+        <v>707605</v>
       </c>
       <c r="R16" t="n">
-        <v>6374988</v>
+        <v>6374982</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2477,7 +2510,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2491,7 +2524,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2509,10 +2542,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578758</v>
+        <v>122578804</v>
       </c>
       <c r="B17" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2525,36 +2558,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2563,13 +2587,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707557</v>
+        <v>707697</v>
       </c>
       <c r="R17" t="n">
-        <v>6375009</v>
+        <v>6374980</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2603,7 +2627,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2635,7 +2659,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578776</v>
+        <v>122578770</v>
       </c>
       <c r="B18" t="n">
         <v>99772</v>
@@ -2670,7 +2694,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2689,10 +2713,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707584</v>
+        <v>707506</v>
       </c>
       <c r="R18" t="n">
-        <v>6375172</v>
+        <v>6375077</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
@@ -2727,6 +2751,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2738,7 +2767,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2756,7 +2785,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578810</v>
+        <v>122578769</v>
       </c>
       <c r="B19" t="n">
         <v>99772</v>
@@ -2789,7 +2818,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2801,13 +2839,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707652</v>
+        <v>707513</v>
       </c>
       <c r="R19" t="n">
-        <v>6374986</v>
+        <v>6375053</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2841,7 +2879,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2855,7 +2893,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2873,7 +2911,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578748</v>
+        <v>122578817</v>
       </c>
       <c r="B20" t="n">
         <v>99772</v>
@@ -2906,17 +2944,31 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707590</v>
+        <v>707624</v>
       </c>
       <c r="R20" t="n">
-        <v>6375036</v>
+        <v>6374996</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2953,7 +3005,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2985,10 +3037,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578800</v>
+        <v>122578765</v>
       </c>
       <c r="B21" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3001,36 +3053,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3039,13 +3082,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707697</v>
+        <v>707532</v>
       </c>
       <c r="R21" t="n">
-        <v>6374980</v>
+        <v>6375035</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3079,7 +3122,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Inget i tallplantager mot S och O.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3111,10 +3154,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578773</v>
+        <v>122578809</v>
       </c>
       <c r="B22" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3127,36 +3170,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3165,13 +3199,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707489</v>
+        <v>707652</v>
       </c>
       <c r="R22" t="n">
-        <v>6375140</v>
+        <v>6374986</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3203,6 +3237,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3214,7 +3253,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3232,10 +3271,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578809</v>
+        <v>122578775</v>
       </c>
       <c r="B23" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3248,27 +3287,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3277,13 +3325,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707652</v>
+        <v>707564</v>
       </c>
       <c r="R23" t="n">
-        <v>6374986</v>
+        <v>6375169</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3315,11 +3363,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3331,7 +3374,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3349,10 +3392,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578806</v>
+        <v>122578772</v>
       </c>
       <c r="B24" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3365,27 +3408,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3394,13 +3446,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707678</v>
+        <v>707506</v>
       </c>
       <c r="R24" t="n">
-        <v>6374990</v>
+        <v>6375110</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3434,7 +3486,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3448,7 +3500,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3466,10 +3518,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578755</v>
+        <v>122578746</v>
       </c>
       <c r="B25" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3478,55 +3530,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707541</v>
+        <v>707626</v>
       </c>
       <c r="R25" t="n">
-        <v>6374993</v>
+        <v>6375071</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3560,7 +3598,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3592,10 +3630,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578786</v>
+        <v>122578747</v>
       </c>
       <c r="B26" t="n">
-        <v>98222</v>
+        <v>105442</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3604,52 +3642,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707652</v>
+        <v>707590</v>
       </c>
       <c r="R26" t="n">
-        <v>6375083</v>
+        <v>6375036</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3686,7 +3710,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3718,10 +3742,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578814</v>
+        <v>122578764</v>
       </c>
       <c r="B27" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3730,35 +3754,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3772,13 +3796,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707638</v>
+        <v>707538</v>
       </c>
       <c r="R27" t="n">
-        <v>6374988</v>
+        <v>6375024</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3808,6 +3832,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3839,7 +3868,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578783</v>
+        <v>122578752</v>
       </c>
       <c r="B28" t="n">
         <v>99772</v>
@@ -3872,7 +3901,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3884,13 +3922,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707633</v>
+        <v>707569</v>
       </c>
       <c r="R28" t="n">
-        <v>6375094</v>
+        <v>6374979</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3924,7 +3962,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3956,10 +3994,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578796</v>
+        <v>122578818</v>
       </c>
       <c r="B29" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3972,27 +4010,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4001,10 +4048,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707725</v>
+        <v>707605</v>
       </c>
       <c r="R29" t="n">
-        <v>6374976</v>
+        <v>6374982</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4041,7 +4088,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4055,7 +4102,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4073,10 +4120,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578742</v>
+        <v>122578825</v>
       </c>
       <c r="B30" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4089,37 +4136,51 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707638</v>
+        <v>707611</v>
       </c>
       <c r="R30" t="n">
-        <v>6375036</v>
+        <v>6374954</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4151,11 +4212,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4167,7 +4223,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4185,10 +4241,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578808</v>
+        <v>122578783</v>
       </c>
       <c r="B31" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4197,37 +4253,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4239,13 +4286,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707678</v>
+        <v>707633</v>
       </c>
       <c r="R31" t="n">
-        <v>6374990</v>
+        <v>6375094</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4275,6 +4322,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4306,10 +4358,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578774</v>
+        <v>122578806</v>
       </c>
       <c r="B32" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4322,36 +4374,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4360,13 +4403,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707528</v>
+        <v>707678</v>
       </c>
       <c r="R32" t="n">
-        <v>6375154</v>
+        <v>6374990</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4398,6 +4441,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4409,7 +4457,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4427,10 +4475,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578765</v>
+        <v>122578758</v>
       </c>
       <c r="B33" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4443,27 +4491,36 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4472,13 +4529,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707532</v>
+        <v>707557</v>
       </c>
       <c r="R33" t="n">
-        <v>6375035</v>
+        <v>6375009</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4512,7 +4569,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4544,7 +4601,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578756</v>
+        <v>122578810</v>
       </c>
       <c r="B34" t="n">
         <v>99772</v>
@@ -4577,16 +4634,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4598,13 +4646,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707541</v>
+        <v>707652</v>
       </c>
       <c r="R34" t="n">
-        <v>6374993</v>
+        <v>6374986</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4638,7 +4686,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4670,7 +4718,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578782</v>
+        <v>122578751</v>
       </c>
       <c r="B35" t="n">
         <v>98222</v>
@@ -4705,7 +4753,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4724,13 +4772,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707621</v>
+        <v>707569</v>
       </c>
       <c r="R35" t="n">
-        <v>6375108</v>
+        <v>6374979</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4760,6 +4808,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4791,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578823</v>
+        <v>122578802</v>
       </c>
       <c r="B36" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4803,35 +4856,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4845,10 +4898,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707605</v>
+        <v>707697</v>
       </c>
       <c r="R36" t="n">
-        <v>6374970</v>
+        <v>6374969</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4883,11 +4936,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Minsta antal + spridd.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4899,7 +4947,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4917,7 +4965,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578779</v>
+        <v>122578780</v>
       </c>
       <c r="B37" t="n">
         <v>99772</v>
@@ -4962,13 +5010,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707597</v>
+        <v>707626</v>
       </c>
       <c r="R37" t="n">
-        <v>6375142</v>
+        <v>6375120</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5002,7 +5050,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5016,7 +5064,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5034,10 +5082,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578747</v>
+        <v>122578743</v>
       </c>
       <c r="B38" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5050,21 +5098,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5074,13 +5122,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707590</v>
+        <v>707638</v>
       </c>
       <c r="R38" t="n">
         <v>6375036</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5114,7 +5162,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5146,10 +5194,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578767</v>
+        <v>122578824</v>
       </c>
       <c r="B39" t="n">
-        <v>98266</v>
+        <v>99772</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5158,35 +5206,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5200,13 +5248,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707513</v>
+        <v>707606</v>
       </c>
       <c r="R39" t="n">
-        <v>6375053</v>
+        <v>6374961</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5249,7 +5297,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5267,10 +5315,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578797</v>
+        <v>122578762</v>
       </c>
       <c r="B40" t="n">
-        <v>98222</v>
+        <v>105442</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5279,40 +5327,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5321,13 +5369,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707725</v>
+        <v>707548</v>
       </c>
       <c r="R40" t="n">
-        <v>6374976</v>
+        <v>6375014</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5357,6 +5405,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5388,10 +5441,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578751</v>
+        <v>122578795</v>
       </c>
       <c r="B41" t="n">
-        <v>98222</v>
+        <v>105442</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5400,40 +5453,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5442,13 +5486,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707569</v>
+        <v>707725</v>
       </c>
       <c r="R41" t="n">
-        <v>6374979</v>
+        <v>6374976</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5482,7 +5526,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5514,10 +5558,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578754</v>
+        <v>122578808</v>
       </c>
       <c r="B42" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5526,35 +5570,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5568,10 +5612,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707554</v>
+        <v>707678</v>
       </c>
       <c r="R42" t="n">
-        <v>6374978</v>
+        <v>6374990</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5604,11 +5648,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5640,7 +5679,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578778</v>
+        <v>122578776</v>
       </c>
       <c r="B43" t="n">
         <v>99772</v>
@@ -5675,7 +5714,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5694,13 +5733,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707599</v>
+        <v>707584</v>
       </c>
       <c r="R43" t="n">
-        <v>6375165</v>
+        <v>6375172</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5732,11 +5771,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Barrblandskog mot åker i N.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5748,7 +5782,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5766,7 +5800,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578785</v>
+        <v>122578742</v>
       </c>
       <c r="B44" t="n">
         <v>105442</v>
@@ -5800,24 +5834,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707648</v>
+        <v>707638</v>
       </c>
       <c r="R44" t="n">
-        <v>6375072</v>
+        <v>6375036</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5851,7 +5880,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5883,7 +5912,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578763</v>
+        <v>122578748</v>
       </c>
       <c r="B45" t="n">
         <v>99772</v>
@@ -5916,34 +5945,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707548</v>
+        <v>707590</v>
       </c>
       <c r="R45" t="n">
-        <v>6375014</v>
+        <v>6375036</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5977,7 +5992,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6009,7 +6024,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578759</v>
+        <v>122578741</v>
       </c>
       <c r="B46" t="n">
         <v>99772</v>
@@ -6042,34 +6057,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707557</v>
+        <v>707609</v>
       </c>
       <c r="R46" t="n">
-        <v>6375009</v>
+        <v>6375033</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6103,7 +6104,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6135,10 +6136,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578752</v>
+        <v>122578812</v>
       </c>
       <c r="B47" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6151,36 +6152,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6189,13 +6181,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707569</v>
+        <v>707646</v>
       </c>
       <c r="R47" t="n">
-        <v>6374979</v>
+        <v>6374967</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6229,7 +6221,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6261,7 +6253,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578770</v>
+        <v>122578774</v>
       </c>
       <c r="B48" t="n">
         <v>99772</v>
@@ -6296,7 +6288,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6315,13 +6307,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707506</v>
+        <v>707528</v>
       </c>
       <c r="R48" t="n">
-        <v>6375077</v>
+        <v>6375154</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6353,11 +6345,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>2 ex.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6369,7 +6356,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6387,7 +6374,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578743</v>
+        <v>122578781</v>
       </c>
       <c r="B49" t="n">
         <v>99772</v>
@@ -6421,19 +6408,24 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707638</v>
+        <v>707621</v>
       </c>
       <c r="R49" t="n">
-        <v>6375036</v>
+        <v>6375108</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6467,7 +6459,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6499,7 +6491,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578772</v>
+        <v>122578777</v>
       </c>
       <c r="B50" t="n">
         <v>99772</v>
@@ -6534,7 +6526,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6553,13 +6545,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707506</v>
+        <v>707591</v>
       </c>
       <c r="R50" t="n">
-        <v>6375110</v>
+        <v>6375187</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6593,7 +6585,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>30 m S åker i N.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6607,7 +6599,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6625,10 +6617,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578817</v>
+        <v>122578782</v>
       </c>
       <c r="B51" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6637,35 +6629,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6679,10 +6671,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707624</v>
+        <v>707621</v>
       </c>
       <c r="R51" t="n">
-        <v>6374996</v>
+        <v>6375108</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6715,11 +6707,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6751,10 +6738,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578746</v>
+        <v>122578757</v>
       </c>
       <c r="B52" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6763,41 +6750,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707626</v>
+        <v>707557</v>
       </c>
       <c r="R52" t="n">
-        <v>6375071</v>
+        <v>6375009</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6831,7 +6832,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6863,7 +6864,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578740</v>
+        <v>122578749</v>
       </c>
       <c r="B53" t="n">
         <v>105442</v>
@@ -6896,20 +6897,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707609</v>
+        <v>707570</v>
       </c>
       <c r="R53" t="n">
-        <v>6375033</v>
+        <v>6374984</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6943,7 +6958,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6975,7 +6990,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578812</v>
+        <v>122578785</v>
       </c>
       <c r="B54" t="n">
         <v>105442</v>
@@ -7020,10 +7035,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707646</v>
+        <v>707648</v>
       </c>
       <c r="R54" t="n">
-        <v>6374967</v>
+        <v>6375072</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7060,7 +7075,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7092,10 +7107,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578818</v>
+        <v>122578816</v>
       </c>
       <c r="B55" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7108,36 +7123,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7146,10 +7152,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707605</v>
+        <v>707638</v>
       </c>
       <c r="R55" t="n">
-        <v>6374982</v>
+        <v>6374988</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7186,7 +7192,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7200,7 +7206,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7218,10 +7224,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578741</v>
+        <v>122578815</v>
       </c>
       <c r="B56" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7234,37 +7240,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707609</v>
+        <v>707638</v>
       </c>
       <c r="R56" t="n">
-        <v>6375033</v>
+        <v>6374988</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7298,7 +7309,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7330,7 +7341,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578819</v>
+        <v>122578779</v>
       </c>
       <c r="B57" t="n">
         <v>99772</v>
@@ -7363,16 +7374,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7384,13 +7386,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707605</v>
+        <v>707597</v>
       </c>
       <c r="R57" t="n">
-        <v>6374982</v>
+        <v>6375142</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7424,7 +7426,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Enstaka strå.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7438,7 +7440,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7456,10 +7458,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578821</v>
+        <v>122578797</v>
       </c>
       <c r="B58" t="n">
-        <v>105442</v>
+        <v>98222</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7468,40 +7470,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7510,10 +7512,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707605</v>
+        <v>707725</v>
       </c>
       <c r="R58" t="n">
-        <v>6374970</v>
+        <v>6374976</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7548,11 +7550,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minsta antal + spridd.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7564,7 +7561,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7582,7 +7579,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578753</v>
+        <v>122578771</v>
       </c>
       <c r="B59" t="n">
         <v>98222</v>
@@ -7617,12 +7614,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7636,13 +7633,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707554</v>
+        <v>707490</v>
       </c>
       <c r="R59" t="n">
-        <v>6374978</v>
+        <v>6375090</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7676,7 +7673,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7690,7 +7687,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7708,10 +7705,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578781</v>
+        <v>122578811</v>
       </c>
       <c r="B60" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7720,28 +7717,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7753,10 +7759,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707621</v>
+        <v>707652</v>
       </c>
       <c r="R60" t="n">
-        <v>6375108</v>
+        <v>6374986</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7789,11 +7795,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7825,10 +7826,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578784</v>
+        <v>122578755</v>
       </c>
       <c r="B61" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7837,28 +7838,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7870,13 +7880,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707648</v>
+        <v>707541</v>
       </c>
       <c r="R61" t="n">
-        <v>6375072</v>
+        <v>6374993</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7910,7 +7920,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7942,7 +7952,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578764</v>
+        <v>122578784</v>
       </c>
       <c r="B62" t="n">
         <v>99772</v>
@@ -7975,16 +7985,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7996,13 +7997,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707538</v>
+        <v>707648</v>
       </c>
       <c r="R62" t="n">
-        <v>6375024</v>
+        <v>6375072</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8036,7 +8037,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8068,10 +8069,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578750</v>
+        <v>122578773</v>
       </c>
       <c r="B63" t="n">
-        <v>98266</v>
+        <v>99772</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8080,35 +8081,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8122,10 +8123,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707569</v>
+        <v>707489</v>
       </c>
       <c r="R63" t="n">
-        <v>6374979</v>
+        <v>6375140</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -8160,11 +8161,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8176,7 +8172,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8194,10 +8190,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578771</v>
+        <v>122578778</v>
       </c>
       <c r="B64" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8206,30 +8202,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8248,13 +8244,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707490</v>
+        <v>707599</v>
       </c>
       <c r="R64" t="n">
-        <v>6375090</v>
+        <v>6375165</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8288,7 +8284,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8302,7 +8298,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8320,10 +8316,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578775</v>
+        <v>122578760</v>
       </c>
       <c r="B65" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8336,36 +8332,36 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8374,13 +8370,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707564</v>
+        <v>707547</v>
       </c>
       <c r="R65" t="n">
-        <v>6375169</v>
+        <v>6375010</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8412,6 +8408,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8423,7 +8424,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8558,10 +8559,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578757</v>
+        <v>122578766</v>
       </c>
       <c r="B67" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8570,35 +8571,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8612,13 +8613,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707557</v>
+        <v>707548</v>
       </c>
       <c r="R67" t="n">
-        <v>6375009</v>
+        <v>6375091</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8652,7 +8653,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8666,7 +8667,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8684,7 +8685,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578777</v>
+        <v>122578796</v>
       </c>
       <c r="B68" t="n">
         <v>99772</v>
@@ -8717,16 +8718,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8738,13 +8730,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707591</v>
+        <v>707725</v>
       </c>
       <c r="R68" t="n">
-        <v>6375187</v>
+        <v>6374976</v>
       </c>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8778,7 +8770,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>30 m S åker i N.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8792,7 +8784,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8810,7 +8802,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578811</v>
+        <v>122578814</v>
       </c>
       <c r="B69" t="n">
         <v>98222</v>
@@ -8845,7 +8837,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8864,10 +8856,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707652</v>
+        <v>707638</v>
       </c>
       <c r="R69" t="n">
-        <v>6374986</v>
+        <v>6374988</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8931,10 +8923,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578807</v>
+        <v>122578805</v>
       </c>
       <c r="B70" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8943,28 +8935,37 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8976,10 +8977,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707678</v>
+        <v>707697</v>
       </c>
       <c r="R70" t="n">
-        <v>6374990</v>
+        <v>6374980</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9012,11 +9013,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9048,10 +9044,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578744</v>
+        <v>122578767</v>
       </c>
       <c r="B71" t="n">
-        <v>105442</v>
+        <v>98266</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9060,40 +9056,40 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>671</v>
+        <v>219862</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9102,13 +9098,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707626</v>
+        <v>707513</v>
       </c>
       <c r="R71" t="n">
-        <v>6375071</v>
+        <v>6375053</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9140,11 +9136,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Stensamling, grav? Nära.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9156,7 +9147,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578769</v>
+        <v>122578809</v>
       </c>
       <c r="B19" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2801,36 +2801,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2839,13 +2830,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707513</v>
+        <v>707652</v>
       </c>
       <c r="R19" t="n">
-        <v>6375053</v>
+        <v>6374986</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2879,7 +2870,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2893,7 +2884,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2911,7 +2902,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578817</v>
+        <v>122578769</v>
       </c>
       <c r="B20" t="n">
         <v>99772</v>
@@ -2946,7 +2937,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2965,13 +2956,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707624</v>
+        <v>707513</v>
       </c>
       <c r="R20" t="n">
-        <v>6374996</v>
+        <v>6375053</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3005,7 +2996,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3019,7 +3010,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3037,7 +3028,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578765</v>
+        <v>122578817</v>
       </c>
       <c r="B21" t="n">
         <v>99772</v>
@@ -3070,7 +3061,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707532</v>
+        <v>707624</v>
       </c>
       <c r="R21" t="n">
-        <v>6375035</v>
+        <v>6374996</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,10 +3154,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578809</v>
+        <v>122578765</v>
       </c>
       <c r="B22" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3170,27 +3170,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3199,13 +3199,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707652</v>
+        <v>707532</v>
       </c>
       <c r="R22" t="n">
-        <v>6374986</v>
+        <v>6375035</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4601,7 +4601,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578810</v>
+        <v>122578780</v>
       </c>
       <c r="B34" t="n">
         <v>99772</v>
@@ -4646,13 +4646,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707652</v>
+        <v>707626</v>
       </c>
       <c r="R34" t="n">
-        <v>6374986</v>
+        <v>6375120</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4718,10 +4718,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578751</v>
+        <v>122578743</v>
       </c>
       <c r="B35" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4730,55 +4730,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707569</v>
+        <v>707638</v>
       </c>
       <c r="R35" t="n">
-        <v>6374979</v>
+        <v>6375036</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4812,7 +4798,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4844,10 +4830,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578802</v>
+        <v>122578810</v>
       </c>
       <c r="B36" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4856,37 +4842,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4898,10 +4875,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707697</v>
+        <v>707652</v>
       </c>
       <c r="R36" t="n">
-        <v>6374969</v>
+        <v>6374986</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4934,6 +4911,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4965,10 +4947,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578780</v>
+        <v>122578751</v>
       </c>
       <c r="B37" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4977,28 +4959,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5010,13 +5001,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707626</v>
+        <v>707569</v>
       </c>
       <c r="R37" t="n">
-        <v>6375120</v>
+        <v>6374979</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5050,7 +5041,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5082,10 +5073,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578743</v>
+        <v>122578802</v>
       </c>
       <c r="B38" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5094,41 +5085,55 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707638</v>
+        <v>707697</v>
       </c>
       <c r="R38" t="n">
-        <v>6375036</v>
+        <v>6374969</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5158,11 +5163,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578809</v>
+        <v>122578769</v>
       </c>
       <c r="B19" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2801,27 +2801,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2830,13 +2839,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707652</v>
+        <v>707513</v>
       </c>
       <c r="R19" t="n">
-        <v>6374986</v>
+        <v>6375053</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2870,7 +2879,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2884,7 +2893,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2902,7 +2911,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578769</v>
+        <v>122578817</v>
       </c>
       <c r="B20" t="n">
         <v>99772</v>
@@ -2937,7 +2946,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2956,13 +2965,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707513</v>
+        <v>707624</v>
       </c>
       <c r="R20" t="n">
-        <v>6375053</v>
+        <v>6374996</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2996,7 +3005,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3010,7 +3019,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3028,7 +3037,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578817</v>
+        <v>122578765</v>
       </c>
       <c r="B21" t="n">
         <v>99772</v>
@@ -3061,16 +3070,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707624</v>
+        <v>707532</v>
       </c>
       <c r="R21" t="n">
-        <v>6374996</v>
+        <v>6375035</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,10 +3154,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578765</v>
+        <v>122578809</v>
       </c>
       <c r="B22" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3170,27 +3170,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3199,13 +3199,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707532</v>
+        <v>707652</v>
       </c>
       <c r="R22" t="n">
-        <v>6375035</v>
+        <v>6374986</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578769</v>
+        <v>122578809</v>
       </c>
       <c r="B19" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2801,36 +2801,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2839,13 +2830,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707513</v>
+        <v>707652</v>
       </c>
       <c r="R19" t="n">
-        <v>6375053</v>
+        <v>6374986</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2879,7 +2870,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2893,7 +2884,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2911,7 +2902,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578817</v>
+        <v>122578769</v>
       </c>
       <c r="B20" t="n">
         <v>99772</v>
@@ -2946,7 +2937,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2965,13 +2956,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707624</v>
+        <v>707513</v>
       </c>
       <c r="R20" t="n">
-        <v>6374996</v>
+        <v>6375053</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3005,7 +2996,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3019,7 +3010,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3037,7 +3028,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578765</v>
+        <v>122578817</v>
       </c>
       <c r="B21" t="n">
         <v>99772</v>
@@ -3070,7 +3061,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707532</v>
+        <v>707624</v>
       </c>
       <c r="R21" t="n">
-        <v>6375035</v>
+        <v>6374996</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,10 +3154,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578809</v>
+        <v>122578765</v>
       </c>
       <c r="B22" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3170,27 +3170,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3199,13 +3199,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707652</v>
+        <v>707532</v>
       </c>
       <c r="R22" t="n">
-        <v>6374986</v>
+        <v>6375035</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -7826,10 +7826,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578755</v>
+        <v>122578784</v>
       </c>
       <c r="B61" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7838,37 +7838,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7880,13 +7871,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707541</v>
+        <v>707648</v>
       </c>
       <c r="R61" t="n">
-        <v>6374993</v>
+        <v>6375072</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7920,7 +7911,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7952,7 +7943,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578784</v>
+        <v>122578773</v>
       </c>
       <c r="B62" t="n">
         <v>99772</v>
@@ -7985,7 +7976,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7997,13 +7997,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707648</v>
+        <v>707489</v>
       </c>
       <c r="R62" t="n">
-        <v>6375072</v>
+        <v>6375140</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8035,11 +8035,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8051,7 +8046,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8069,7 +8064,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578773</v>
+        <v>122578778</v>
       </c>
       <c r="B63" t="n">
         <v>99772</v>
@@ -8104,7 +8099,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8123,13 +8118,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707489</v>
+        <v>707599</v>
       </c>
       <c r="R63" t="n">
-        <v>6375140</v>
+        <v>6375165</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8159,6 +8154,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8190,10 +8190,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578778</v>
+        <v>122578755</v>
       </c>
       <c r="B64" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8202,35 +8202,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8244,13 +8244,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707599</v>
+        <v>707541</v>
       </c>
       <c r="R64" t="n">
-        <v>6375165</v>
+        <v>6374993</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Barrblandskog mot åker i N.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8442,7 +8442,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578813</v>
+        <v>122578766</v>
       </c>
       <c r="B66" t="n">
         <v>99772</v>
@@ -8475,7 +8475,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8487,13 +8496,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707646</v>
+        <v>707548</v>
       </c>
       <c r="R66" t="n">
-        <v>6374967</v>
+        <v>6375091</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8527,7 +8536,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8541,7 +8550,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8559,10 +8568,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578766</v>
+        <v>122578814</v>
       </c>
       <c r="B67" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8571,35 +8580,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8613,13 +8622,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707548</v>
+        <v>707638</v>
       </c>
       <c r="R67" t="n">
-        <v>6375091</v>
+        <v>6374988</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8651,11 +8660,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8667,7 +8671,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8685,10 +8689,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578796</v>
+        <v>122578767</v>
       </c>
       <c r="B68" t="n">
-        <v>99772</v>
+        <v>98266</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8697,28 +8701,37 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8730,13 +8743,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707725</v>
+        <v>707513</v>
       </c>
       <c r="R68" t="n">
-        <v>6374976</v>
+        <v>6375053</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8768,11 +8781,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8784,7 +8792,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8802,10 +8810,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578814</v>
+        <v>122578813</v>
       </c>
       <c r="B69" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8814,37 +8822,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8856,10 +8855,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707638</v>
+        <v>707646</v>
       </c>
       <c r="R69" t="n">
-        <v>6374988</v>
+        <v>6374967</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8892,6 +8891,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8923,10 +8927,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578805</v>
+        <v>122578796</v>
       </c>
       <c r="B70" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8935,37 +8939,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8977,10 +8972,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707697</v>
+        <v>707725</v>
       </c>
       <c r="R70" t="n">
-        <v>6374980</v>
+        <v>6374976</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9013,6 +9008,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9044,10 +9044,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578767</v>
+        <v>122578805</v>
       </c>
       <c r="B71" t="n">
-        <v>98266</v>
+        <v>98222</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9060,21 +9060,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -9098,13 +9098,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707513</v>
+        <v>707697</v>
       </c>
       <c r="R71" t="n">
-        <v>6375053</v>
+        <v>6374980</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -2416,7 +2416,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578819</v>
+        <v>122578804</v>
       </c>
       <c r="B16" t="n">
         <v>99772</v>
@@ -2449,16 +2449,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2470,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707605</v>
+        <v>707697</v>
       </c>
       <c r="R16" t="n">
-        <v>6374982</v>
+        <v>6374980</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2510,7 +2501,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2524,7 +2515,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2542,7 +2533,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578804</v>
+        <v>122578819</v>
       </c>
       <c r="B17" t="n">
         <v>99772</v>
@@ -2575,7 +2566,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707697</v>
+        <v>707605</v>
       </c>
       <c r="R17" t="n">
-        <v>6374980</v>
+        <v>6374982</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -3868,7 +3868,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578752</v>
+        <v>122578783</v>
       </c>
       <c r="B28" t="n">
         <v>99772</v>
@@ -3901,16 +3901,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3922,13 +3913,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707569</v>
+        <v>707633</v>
       </c>
       <c r="R28" t="n">
-        <v>6374979</v>
+        <v>6375094</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3962,7 +3953,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3994,7 +3985,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578818</v>
+        <v>122578806</v>
       </c>
       <c r="B29" t="n">
         <v>105442</v>
@@ -4027,16 +4018,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4048,10 +4030,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707605</v>
+        <v>707678</v>
       </c>
       <c r="R29" t="n">
-        <v>6374982</v>
+        <v>6374990</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4088,7 +4070,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4102,7 +4084,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4120,7 +4102,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578825</v>
+        <v>122578752</v>
       </c>
       <c r="B30" t="n">
         <v>99772</v>
@@ -4155,7 +4137,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4174,13 +4156,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707611</v>
+        <v>707569</v>
       </c>
       <c r="R30" t="n">
-        <v>6374954</v>
+        <v>6374979</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4212,6 +4194,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4223,7 +4210,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4241,10 +4228,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578783</v>
+        <v>122578818</v>
       </c>
       <c r="B31" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4257,27 +4244,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4286,13 +4282,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707633</v>
+        <v>707605</v>
       </c>
       <c r="R31" t="n">
-        <v>6375094</v>
+        <v>6374982</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4326,7 +4322,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4340,7 +4336,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4358,10 +4354,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578806</v>
+        <v>122578825</v>
       </c>
       <c r="B32" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4374,27 +4370,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4403,10 +4408,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707678</v>
+        <v>707611</v>
       </c>
       <c r="R32" t="n">
-        <v>6374990</v>
+        <v>6374954</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4441,11 +4446,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578780</v>
+        <v>122578810</v>
       </c>
       <c r="B34" t="n">
         <v>99772</v>
@@ -4646,13 +4646,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707626</v>
+        <v>707652</v>
       </c>
       <c r="R34" t="n">
-        <v>6375120</v>
+        <v>6374986</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4718,10 +4718,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578743</v>
+        <v>122578751</v>
       </c>
       <c r="B35" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4730,41 +4730,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707638</v>
+        <v>707569</v>
       </c>
       <c r="R35" t="n">
-        <v>6375036</v>
+        <v>6374979</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4798,7 +4812,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4830,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578810</v>
+        <v>122578802</v>
       </c>
       <c r="B36" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4842,28 +4856,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4875,10 +4898,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707652</v>
+        <v>707697</v>
       </c>
       <c r="R36" t="n">
-        <v>6374986</v>
+        <v>6374969</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4911,11 +4934,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4947,10 +4965,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578751</v>
+        <v>122578780</v>
       </c>
       <c r="B37" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4959,37 +4977,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5001,13 +5010,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707569</v>
+        <v>707626</v>
       </c>
       <c r="R37" t="n">
-        <v>6374979</v>
+        <v>6375120</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5041,7 +5050,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5073,10 +5082,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578802</v>
+        <v>122578743</v>
       </c>
       <c r="B38" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5085,55 +5094,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707697</v>
+        <v>707638</v>
       </c>
       <c r="R38" t="n">
-        <v>6374969</v>
+        <v>6375036</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5163,6 +5158,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -7826,10 +7826,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578784</v>
+        <v>122578755</v>
       </c>
       <c r="B61" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7838,28 +7838,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7871,13 +7880,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707648</v>
+        <v>707541</v>
       </c>
       <c r="R61" t="n">
-        <v>6375072</v>
+        <v>6374993</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7911,7 +7920,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7943,7 +7952,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578773</v>
+        <v>122578784</v>
       </c>
       <c r="B62" t="n">
         <v>99772</v>
@@ -7976,16 +7985,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7997,13 +7997,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707489</v>
+        <v>707648</v>
       </c>
       <c r="R62" t="n">
-        <v>6375140</v>
+        <v>6375072</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8035,6 +8035,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Glest spridd, men saknas mot O-NO..</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8046,7 +8051,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8064,7 +8069,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578778</v>
+        <v>122578773</v>
       </c>
       <c r="B63" t="n">
         <v>99772</v>
@@ -8099,7 +8104,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8118,13 +8123,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707599</v>
+        <v>707489</v>
       </c>
       <c r="R63" t="n">
-        <v>6375165</v>
+        <v>6375140</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8154,11 +8159,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8190,10 +8190,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578755</v>
+        <v>122578778</v>
       </c>
       <c r="B64" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8202,35 +8202,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8244,13 +8244,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707541</v>
+        <v>707599</v>
       </c>
       <c r="R64" t="n">
-        <v>6374993</v>
+        <v>6375165</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -3868,7 +3868,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578783</v>
+        <v>122578752</v>
       </c>
       <c r="B28" t="n">
         <v>99772</v>
@@ -3901,7 +3901,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3913,13 +3922,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707633</v>
+        <v>707569</v>
       </c>
       <c r="R28" t="n">
-        <v>6375094</v>
+        <v>6374979</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3953,7 +3962,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3985,7 +3994,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578806</v>
+        <v>122578818</v>
       </c>
       <c r="B29" t="n">
         <v>105442</v>
@@ -4018,7 +4027,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4030,10 +4048,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707678</v>
+        <v>707605</v>
       </c>
       <c r="R29" t="n">
-        <v>6374990</v>
+        <v>6374982</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4070,7 +4088,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4084,7 +4102,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4102,7 +4120,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578752</v>
+        <v>122578825</v>
       </c>
       <c r="B30" t="n">
         <v>99772</v>
@@ -4137,7 +4155,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4156,13 +4174,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707569</v>
+        <v>707611</v>
       </c>
       <c r="R30" t="n">
-        <v>6374979</v>
+        <v>6374954</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4194,11 +4212,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4210,7 +4223,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4228,10 +4241,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578818</v>
+        <v>122578783</v>
       </c>
       <c r="B31" t="n">
-        <v>105442</v>
+        <v>99772</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4244,36 +4257,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4282,13 +4286,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707605</v>
+        <v>707633</v>
       </c>
       <c r="R31" t="n">
-        <v>6374982</v>
+        <v>6375094</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4322,7 +4326,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4336,7 +4340,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4354,10 +4358,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578825</v>
+        <v>122578806</v>
       </c>
       <c r="B32" t="n">
-        <v>99772</v>
+        <v>105442</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4370,36 +4374,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4408,10 +4403,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707611</v>
+        <v>707678</v>
       </c>
       <c r="R32" t="n">
-        <v>6374954</v>
+        <v>6374990</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4446,6 +4441,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -7826,10 +7826,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578755</v>
+        <v>122578784</v>
       </c>
       <c r="B61" t="n">
-        <v>98222</v>
+        <v>99772</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7838,37 +7838,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7880,13 +7871,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707541</v>
+        <v>707648</v>
       </c>
       <c r="R61" t="n">
-        <v>6374993</v>
+        <v>6375072</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7920,7 +7911,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7952,7 +7943,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578784</v>
+        <v>122578773</v>
       </c>
       <c r="B62" t="n">
         <v>99772</v>
@@ -7985,7 +7976,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7997,13 +7997,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707648</v>
+        <v>707489</v>
       </c>
       <c r="R62" t="n">
-        <v>6375072</v>
+        <v>6375140</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8035,11 +8035,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8051,7 +8046,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8069,7 +8064,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578773</v>
+        <v>122578778</v>
       </c>
       <c r="B63" t="n">
         <v>99772</v>
@@ -8104,7 +8099,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8123,13 +8118,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707489</v>
+        <v>707599</v>
       </c>
       <c r="R63" t="n">
-        <v>6375140</v>
+        <v>6375165</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8159,6 +8154,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8190,10 +8190,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578778</v>
+        <v>122578755</v>
       </c>
       <c r="B64" t="n">
-        <v>99772</v>
+        <v>98222</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8202,35 +8202,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8244,13 +8244,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707599</v>
+        <v>707541</v>
       </c>
       <c r="R64" t="n">
-        <v>6375165</v>
+        <v>6374993</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Barrblandskog mot åker i N.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578786</v>
+        <v>122578751</v>
       </c>
       <c r="B3" t="n">
-        <v>98222</v>
+        <v>98325</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -864,13 +864,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707652</v>
+        <v>707569</v>
       </c>
       <c r="R3" t="n">
-        <v>6375083</v>
+        <v>6374979</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578753</v>
+        <v>122578776</v>
       </c>
       <c r="B4" t="n">
-        <v>98222</v>
+        <v>99875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,35 +948,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -990,13 +990,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707554</v>
+        <v>707584</v>
       </c>
       <c r="R4" t="n">
-        <v>6374978</v>
+        <v>6375172</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,11 +1028,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1044,7 +1039,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,10 +1057,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578740</v>
+        <v>122578815</v>
       </c>
       <c r="B5" t="n">
-        <v>105442</v>
+        <v>105545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,19 +1091,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707609</v>
+        <v>707638</v>
       </c>
       <c r="R5" t="n">
-        <v>6375033</v>
+        <v>6374988</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,10 +1174,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578754</v>
+        <v>122578814</v>
       </c>
       <c r="B6" t="n">
-        <v>99772</v>
+        <v>98325</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,35 +1186,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707554</v>
+        <v>707638</v>
       </c>
       <c r="R6" t="n">
-        <v>6374978</v>
+        <v>6374988</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1264,11 +1264,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578823</v>
+        <v>122578783</v>
       </c>
       <c r="B7" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1333,16 +1328,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1354,13 +1340,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707605</v>
+        <v>707633</v>
       </c>
       <c r="R7" t="n">
-        <v>6374970</v>
+        <v>6375094</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1394,7 +1380,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,7 +1394,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1426,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578807</v>
+        <v>122578744</v>
       </c>
       <c r="B8" t="n">
-        <v>99772</v>
+        <v>105545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,27 +1428,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1471,13 +1466,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707678</v>
+        <v>707626</v>
       </c>
       <c r="R8" t="n">
-        <v>6374990</v>
+        <v>6375071</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1511,7 +1506,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578756</v>
+        <v>122578813</v>
       </c>
       <c r="B9" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1576,16 +1571,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1597,13 +1583,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707541</v>
+        <v>707646</v>
       </c>
       <c r="R9" t="n">
-        <v>6374993</v>
+        <v>6374967</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1637,7 +1623,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,10 +1655,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578763</v>
+        <v>122578821</v>
       </c>
       <c r="B10" t="n">
-        <v>99772</v>
+        <v>105545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,26 +1671,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1714,7 +1700,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1723,13 +1709,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707548</v>
+        <v>707605</v>
       </c>
       <c r="R10" t="n">
-        <v>6375014</v>
+        <v>6374970</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1763,7 +1749,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1777,7 +1763,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1795,10 +1781,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578750</v>
+        <v>122578759</v>
       </c>
       <c r="B11" t="n">
-        <v>98266</v>
+        <v>99875</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1807,35 +1793,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1849,10 +1835,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707569</v>
+        <v>707557</v>
       </c>
       <c r="R11" t="n">
-        <v>6374979</v>
+        <v>6375009</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1921,10 +1907,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578744</v>
+        <v>122578766</v>
       </c>
       <c r="B12" t="n">
-        <v>105442</v>
+        <v>99875</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1937,36 +1923,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1975,13 +1961,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707626</v>
+        <v>707548</v>
       </c>
       <c r="R12" t="n">
-        <v>6375071</v>
+        <v>6375091</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2015,7 +2001,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2029,7 +2015,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2047,10 +2033,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578803</v>
+        <v>122578800</v>
       </c>
       <c r="B13" t="n">
-        <v>105442</v>
+        <v>105545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2080,7 +2066,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2132,7 +2127,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2164,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578759</v>
+        <v>122578754</v>
       </c>
       <c r="B14" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2199,7 +2194,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2218,13 +2213,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707557</v>
+        <v>707554</v>
       </c>
       <c r="R14" t="n">
-        <v>6375009</v>
+        <v>6374978</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2290,10 +2285,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578821</v>
+        <v>122578765</v>
       </c>
       <c r="B15" t="n">
-        <v>105442</v>
+        <v>99875</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2306,36 +2301,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2344,13 +2330,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707605</v>
+        <v>707532</v>
       </c>
       <c r="R15" t="n">
-        <v>6374970</v>
+        <v>6375035</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2384,7 +2370,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2398,7 +2384,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2416,10 +2402,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578804</v>
+        <v>122578808</v>
       </c>
       <c r="B16" t="n">
-        <v>99772</v>
+        <v>98325</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2428,28 +2414,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2461,10 +2456,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707697</v>
+        <v>707678</v>
       </c>
       <c r="R16" t="n">
-        <v>6374980</v>
+        <v>6374990</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2497,11 +2492,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2533,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578819</v>
+        <v>122578817</v>
       </c>
       <c r="B17" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2587,10 +2577,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707605</v>
+        <v>707624</v>
       </c>
       <c r="R17" t="n">
-        <v>6374982</v>
+        <v>6374996</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2627,7 +2617,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2641,7 +2631,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2659,10 +2649,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578770</v>
+        <v>122578775</v>
       </c>
       <c r="B18" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2694,7 +2684,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2713,13 +2703,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707506</v>
+        <v>707564</v>
       </c>
       <c r="R18" t="n">
-        <v>6375077</v>
+        <v>6375169</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2751,11 +2741,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2 ex.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2767,7 +2752,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2788,7 +2773,7 @@
         <v>122578809</v>
       </c>
       <c r="B19" t="n">
-        <v>105442</v>
+        <v>105545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2902,10 +2887,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578769</v>
+        <v>122578785</v>
       </c>
       <c r="B20" t="n">
-        <v>99772</v>
+        <v>105545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2918,36 +2903,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2956,13 +2932,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707513</v>
+        <v>707648</v>
       </c>
       <c r="R20" t="n">
-        <v>6375053</v>
+        <v>6375072</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2996,7 +2972,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3010,7 +2986,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3028,10 +3004,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578817</v>
+        <v>122578812</v>
       </c>
       <c r="B21" t="n">
-        <v>99772</v>
+        <v>105545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3044,36 +3020,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3082,10 +3049,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707624</v>
+        <v>707646</v>
       </c>
       <c r="R21" t="n">
-        <v>6374996</v>
+        <v>6374967</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3122,7 +3089,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,10 +3121,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578765</v>
+        <v>122578784</v>
       </c>
       <c r="B22" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3199,13 +3166,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707532</v>
+        <v>707648</v>
       </c>
       <c r="R22" t="n">
-        <v>6375035</v>
+        <v>6375072</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3239,7 +3206,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3271,10 +3238,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578775</v>
+        <v>122578742</v>
       </c>
       <c r="B23" t="n">
-        <v>99772</v>
+        <v>105545</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3287,48 +3254,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707564</v>
+        <v>707638</v>
       </c>
       <c r="R23" t="n">
-        <v>6375169</v>
+        <v>6375036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3363,6 +3316,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3374,7 +3332,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3392,10 +3350,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578772</v>
+        <v>122578819</v>
       </c>
       <c r="B24" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3427,7 +3385,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3446,13 +3404,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707506</v>
+        <v>707605</v>
       </c>
       <c r="R24" t="n">
-        <v>6375110</v>
+        <v>6374982</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3486,7 +3444,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3500,7 +3458,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3518,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578746</v>
+        <v>122578795</v>
       </c>
       <c r="B25" t="n">
-        <v>99772</v>
+        <v>105545</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3534,37 +3492,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707626</v>
+        <v>707725</v>
       </c>
       <c r="R25" t="n">
-        <v>6375071</v>
+        <v>6374976</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3598,7 +3561,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3630,10 +3593,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578747</v>
+        <v>122578758</v>
       </c>
       <c r="B26" t="n">
-        <v>105442</v>
+        <v>105545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3663,20 +3626,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707590</v>
+        <v>707557</v>
       </c>
       <c r="R26" t="n">
-        <v>6375036</v>
+        <v>6375009</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3710,7 +3687,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3742,10 +3719,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578764</v>
+        <v>122578778</v>
       </c>
       <c r="B27" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3796,13 +3773,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707538</v>
+        <v>707599</v>
       </c>
       <c r="R27" t="n">
-        <v>6375024</v>
+        <v>6375165</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3836,7 +3813,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3850,7 +3827,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3868,10 +3845,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578752</v>
+        <v>122578802</v>
       </c>
       <c r="B28" t="n">
-        <v>99772</v>
+        <v>98325</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3880,35 +3857,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3922,13 +3899,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707569</v>
+        <v>707697</v>
       </c>
       <c r="R28" t="n">
-        <v>6374979</v>
+        <v>6374969</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3958,11 +3935,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3994,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578818</v>
+        <v>122578797</v>
       </c>
       <c r="B29" t="n">
-        <v>105442</v>
+        <v>98325</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4006,40 +3978,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4048,10 +4020,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707605</v>
+        <v>707725</v>
       </c>
       <c r="R29" t="n">
-        <v>6374982</v>
+        <v>6374976</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4086,11 +4058,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minsta antal + spridd.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4102,7 +4069,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4120,10 +4087,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578825</v>
+        <v>122578781</v>
       </c>
       <c r="B30" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4153,16 +4120,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4174,10 +4132,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707611</v>
+        <v>707621</v>
       </c>
       <c r="R30" t="n">
-        <v>6374954</v>
+        <v>6375108</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4212,6 +4170,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Glest spridd.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4223,7 +4186,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4241,10 +4204,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578783</v>
+        <v>122578806</v>
       </c>
       <c r="B31" t="n">
-        <v>99772</v>
+        <v>105545</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4257,27 +4220,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4286,13 +4249,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707633</v>
+        <v>707678</v>
       </c>
       <c r="R31" t="n">
-        <v>6375094</v>
+        <v>6374990</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4326,7 +4289,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4358,10 +4321,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578806</v>
+        <v>122578816</v>
       </c>
       <c r="B32" t="n">
-        <v>105442</v>
+        <v>99875</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4374,27 +4337,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4403,10 +4366,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707678</v>
+        <v>707638</v>
       </c>
       <c r="R32" t="n">
-        <v>6374990</v>
+        <v>6374988</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4443,7 +4406,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4475,10 +4438,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578758</v>
+        <v>122578818</v>
       </c>
       <c r="B33" t="n">
-        <v>105442</v>
+        <v>105545</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4510,7 +4473,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4529,13 +4492,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707557</v>
+        <v>707605</v>
       </c>
       <c r="R33" t="n">
-        <v>6375009</v>
+        <v>6374982</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4569,7 +4532,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4583,7 +4546,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4604,7 +4567,7 @@
         <v>122578810</v>
       </c>
       <c r="B34" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4718,10 +4681,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578751</v>
+        <v>122578760</v>
       </c>
       <c r="B35" t="n">
-        <v>98222</v>
+        <v>105545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4730,40 +4693,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4772,13 +4735,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707569</v>
+        <v>707547</v>
       </c>
       <c r="R35" t="n">
-        <v>6374979</v>
+        <v>6375010</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4844,10 +4807,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578802</v>
+        <v>122578767</v>
       </c>
       <c r="B36" t="n">
-        <v>98222</v>
+        <v>98369</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4860,21 +4823,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4898,13 +4861,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707697</v>
+        <v>707513</v>
       </c>
       <c r="R36" t="n">
-        <v>6374969</v>
+        <v>6375053</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4947,7 +4910,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4965,10 +4928,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578780</v>
+        <v>122578772</v>
       </c>
       <c r="B37" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4998,7 +4961,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5010,13 +4982,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707626</v>
+        <v>707506</v>
       </c>
       <c r="R37" t="n">
-        <v>6375120</v>
+        <v>6375110</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5050,7 +5022,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5064,7 +5036,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5082,10 +5054,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578743</v>
+        <v>122578801</v>
       </c>
       <c r="B38" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5116,19 +5088,24 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707638</v>
+        <v>707697</v>
       </c>
       <c r="R38" t="n">
-        <v>6375036</v>
+        <v>6374980</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5162,7 +5139,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5194,10 +5171,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578824</v>
+        <v>122578743</v>
       </c>
       <c r="B39" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5227,34 +5204,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707606</v>
+        <v>707638</v>
       </c>
       <c r="R39" t="n">
-        <v>6374961</v>
+        <v>6375036</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5286,6 +5249,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt söderut.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5297,7 +5265,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5315,10 +5283,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578762</v>
+        <v>122578811</v>
       </c>
       <c r="B40" t="n">
-        <v>105442</v>
+        <v>98325</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5327,40 +5295,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5369,13 +5337,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707548</v>
+        <v>707652</v>
       </c>
       <c r="R40" t="n">
-        <v>6375014</v>
+        <v>6374986</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5405,11 +5373,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5441,10 +5404,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578795</v>
+        <v>122578757</v>
       </c>
       <c r="B41" t="n">
-        <v>105442</v>
+        <v>98325</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5453,31 +5416,40 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5486,13 +5458,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707725</v>
+        <v>707557</v>
       </c>
       <c r="R41" t="n">
-        <v>6374976</v>
+        <v>6375009</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5526,7 +5498,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5558,10 +5530,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578808</v>
+        <v>122578780</v>
       </c>
       <c r="B42" t="n">
-        <v>98222</v>
+        <v>99875</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5570,37 +5542,28 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5612,13 +5575,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707678</v>
+        <v>707626</v>
       </c>
       <c r="R42" t="n">
-        <v>6374990</v>
+        <v>6375120</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5648,6 +5611,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5679,10 +5647,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578776</v>
+        <v>122578756</v>
       </c>
       <c r="B43" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5714,7 +5682,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5733,13 +5701,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707584</v>
+        <v>707541</v>
       </c>
       <c r="R43" t="n">
-        <v>6375172</v>
+        <v>6374993</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5771,6 +5739,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5782,7 +5755,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5800,10 +5773,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578742</v>
+        <v>122578770</v>
       </c>
       <c r="B44" t="n">
-        <v>105442</v>
+        <v>99875</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5816,37 +5789,51 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707638</v>
+        <v>707506</v>
       </c>
       <c r="R44" t="n">
-        <v>6375036</v>
+        <v>6375077</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5880,7 +5867,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5894,7 +5881,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5912,10 +5899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578748</v>
+        <v>122578763</v>
       </c>
       <c r="B45" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5945,20 +5932,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707590</v>
+        <v>707548</v>
       </c>
       <c r="R45" t="n">
-        <v>6375036</v>
+        <v>6375014</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5992,7 +5993,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6024,10 +6025,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578741</v>
+        <v>122578749</v>
       </c>
       <c r="B46" t="n">
-        <v>99772</v>
+        <v>105545</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6040,37 +6041,51 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707609</v>
+        <v>707570</v>
       </c>
       <c r="R46" t="n">
-        <v>6375033</v>
+        <v>6374984</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6104,7 +6119,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6136,10 +6151,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578812</v>
+        <v>122578740</v>
       </c>
       <c r="B47" t="n">
-        <v>105442</v>
+        <v>105545</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6170,24 +6185,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707646</v>
+        <v>707609</v>
       </c>
       <c r="R47" t="n">
-        <v>6374967</v>
+        <v>6375033</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6221,7 +6231,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6253,10 +6263,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578774</v>
+        <v>122578764</v>
       </c>
       <c r="B48" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6288,7 +6298,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6307,13 +6317,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707528</v>
+        <v>707538</v>
       </c>
       <c r="R48" t="n">
-        <v>6375154</v>
+        <v>6375024</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6345,6 +6355,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6356,7 +6371,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6374,10 +6389,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578781</v>
+        <v>122578746</v>
       </c>
       <c r="B49" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6408,24 +6423,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707621</v>
+        <v>707626</v>
       </c>
       <c r="R49" t="n">
-        <v>6375108</v>
+        <v>6375071</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6459,7 +6469,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6491,10 +6501,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578777</v>
+        <v>122578796</v>
       </c>
       <c r="B50" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6524,16 +6534,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6545,13 +6546,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707591</v>
+        <v>707725</v>
       </c>
       <c r="R50" t="n">
-        <v>6375187</v>
+        <v>6374976</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6585,7 +6586,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>30 m S åker i N.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6599,7 +6600,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6617,10 +6618,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578782</v>
+        <v>122578825</v>
       </c>
       <c r="B51" t="n">
-        <v>98222</v>
+        <v>99875</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6629,35 +6630,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6671,10 +6672,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707621</v>
+        <v>707611</v>
       </c>
       <c r="R51" t="n">
-        <v>6375108</v>
+        <v>6374954</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6720,7 +6721,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6738,10 +6739,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578757</v>
+        <v>122578750</v>
       </c>
       <c r="B52" t="n">
-        <v>98222</v>
+        <v>98369</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6754,21 +6755,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6792,10 +6793,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707557</v>
+        <v>707569</v>
       </c>
       <c r="R52" t="n">
-        <v>6375009</v>
+        <v>6374979</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -6864,10 +6865,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578749</v>
+        <v>122578805</v>
       </c>
       <c r="B53" t="n">
-        <v>105442</v>
+        <v>98325</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6876,40 +6877,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6918,10 +6919,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707570</v>
+        <v>707697</v>
       </c>
       <c r="R53" t="n">
-        <v>6374984</v>
+        <v>6374980</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6954,11 +6955,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6990,10 +6986,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578785</v>
+        <v>122578786</v>
       </c>
       <c r="B54" t="n">
-        <v>105442</v>
+        <v>98325</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7002,31 +6998,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7035,10 +7040,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707648</v>
+        <v>707652</v>
       </c>
       <c r="R54" t="n">
-        <v>6375072</v>
+        <v>6375083</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7075,7 +7080,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7107,10 +7112,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578816</v>
+        <v>122578753</v>
       </c>
       <c r="B55" t="n">
-        <v>99772</v>
+        <v>98325</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7119,28 +7124,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7152,10 +7166,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707638</v>
+        <v>707554</v>
       </c>
       <c r="R55" t="n">
-        <v>6374988</v>
+        <v>6374978</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7192,7 +7206,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7224,10 +7238,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578815</v>
+        <v>122578747</v>
       </c>
       <c r="B56" t="n">
-        <v>105442</v>
+        <v>105545</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7258,21 +7272,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707638</v>
+        <v>707590</v>
       </c>
       <c r="R56" t="n">
-        <v>6374988</v>
+        <v>6375036</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7309,7 +7318,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7341,10 +7350,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578779</v>
+        <v>122578824</v>
       </c>
       <c r="B57" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7374,7 +7383,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7386,13 +7404,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707597</v>
+        <v>707606</v>
       </c>
       <c r="R57" t="n">
-        <v>6375142</v>
+        <v>6374961</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7424,11 +7442,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Enstaka strå.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7440,7 +7453,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7458,10 +7471,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578797</v>
+        <v>122578752</v>
       </c>
       <c r="B58" t="n">
-        <v>98222</v>
+        <v>99875</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7470,35 +7483,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7512,13 +7525,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707725</v>
+        <v>707569</v>
       </c>
       <c r="R58" t="n">
-        <v>6374976</v>
+        <v>6374979</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7548,6 +7561,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7579,10 +7597,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578771</v>
+        <v>122578755</v>
       </c>
       <c r="B59" t="n">
-        <v>98222</v>
+        <v>98325</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7619,7 +7637,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7633,13 +7651,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707490</v>
+        <v>707541</v>
       </c>
       <c r="R59" t="n">
-        <v>6375090</v>
+        <v>6374993</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7673,7 +7691,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7687,7 +7705,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7705,10 +7723,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578811</v>
+        <v>122578769</v>
       </c>
       <c r="B60" t="n">
-        <v>98222</v>
+        <v>99875</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7717,35 +7735,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7759,13 +7777,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707652</v>
+        <v>707513</v>
       </c>
       <c r="R60" t="n">
-        <v>6374986</v>
+        <v>6375053</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7797,6 +7815,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>3 ex.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7808,7 +7831,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7826,10 +7849,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578784</v>
+        <v>122578773</v>
       </c>
       <c r="B61" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7859,7 +7882,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7871,13 +7903,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707648</v>
+        <v>707489</v>
       </c>
       <c r="R61" t="n">
-        <v>6375072</v>
+        <v>6375140</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7909,11 +7941,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7925,7 +7952,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7943,10 +7970,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578773</v>
+        <v>122578741</v>
       </c>
       <c r="B62" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7976,34 +8003,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707489</v>
+        <v>707609</v>
       </c>
       <c r="R62" t="n">
-        <v>6375140</v>
+        <v>6375033</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8035,6 +8048,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spridd, riklig. Strensamling, grav?</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8046,7 +8064,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8064,10 +8082,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578778</v>
+        <v>122578762</v>
       </c>
       <c r="B63" t="n">
-        <v>99772</v>
+        <v>105545</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8080,36 +8098,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8118,13 +8136,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707599</v>
+        <v>707548</v>
       </c>
       <c r="R63" t="n">
-        <v>6375165</v>
+        <v>6375014</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8158,7 +8176,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Barrblandskog mot åker i N.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8172,7 +8190,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8190,10 +8208,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578755</v>
+        <v>122578779</v>
       </c>
       <c r="B64" t="n">
-        <v>98222</v>
+        <v>99875</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8202,37 +8220,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8244,13 +8253,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707541</v>
+        <v>707597</v>
       </c>
       <c r="R64" t="n">
-        <v>6374993</v>
+        <v>6375142</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8284,7 +8293,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Enstaka strå.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8298,7 +8307,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8316,10 +8325,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578760</v>
+        <v>122578774</v>
       </c>
       <c r="B65" t="n">
-        <v>105442</v>
+        <v>99875</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8332,36 +8341,36 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8370,13 +8379,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707547</v>
+        <v>707528</v>
       </c>
       <c r="R65" t="n">
-        <v>6375010</v>
+        <v>6375154</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8408,11 +8417,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8424,7 +8428,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8442,10 +8446,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578766</v>
+        <v>122578807</v>
       </c>
       <c r="B66" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8475,16 +8479,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8496,13 +8491,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707548</v>
+        <v>707678</v>
       </c>
       <c r="R66" t="n">
-        <v>6375091</v>
+        <v>6374990</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8536,7 +8531,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8550,7 +8545,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8568,10 +8563,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578814</v>
+        <v>122578777</v>
       </c>
       <c r="B67" t="n">
-        <v>98222</v>
+        <v>99875</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8580,35 +8575,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8622,13 +8617,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707638</v>
+        <v>707591</v>
       </c>
       <c r="R67" t="n">
-        <v>6374988</v>
+        <v>6375187</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8660,6 +8655,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>30 m S åker i N.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578767</v>
+        <v>122578782</v>
       </c>
       <c r="B68" t="n">
-        <v>98266</v>
+        <v>98325</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8705,26 +8705,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707513</v>
+        <v>707621</v>
       </c>
       <c r="R68" t="n">
-        <v>6375053</v>
+        <v>6375108</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8810,10 +8810,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578813</v>
+        <v>122578748</v>
       </c>
       <c r="B69" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8844,21 +8844,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707646</v>
+        <v>707590</v>
       </c>
       <c r="R69" t="n">
-        <v>6374967</v>
+        <v>6375036</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8895,7 +8890,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8927,10 +8922,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578796</v>
+        <v>122578823</v>
       </c>
       <c r="B70" t="n">
-        <v>99772</v>
+        <v>99875</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8960,7 +8955,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8972,10 +8976,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707725</v>
+        <v>707605</v>
       </c>
       <c r="R70" t="n">
-        <v>6374976</v>
+        <v>6374970</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9012,7 +9016,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9026,7 +9030,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9044,10 +9048,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578805</v>
+        <v>122578771</v>
       </c>
       <c r="B71" t="n">
-        <v>98222</v>
+        <v>98325</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9084,7 +9088,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -9098,13 +9102,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707697</v>
+        <v>707490</v>
       </c>
       <c r="R71" t="n">
-        <v>6374980</v>
+        <v>6375090</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9136,6 +9140,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>I långsträckt stensamlig, grav?</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9147,7 +9156,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -3004,10 +3004,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578812</v>
+        <v>122578802</v>
       </c>
       <c r="B21" t="n">
-        <v>105545</v>
+        <v>98325</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3016,31 +3016,40 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3049,10 +3058,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707646</v>
+        <v>707697</v>
       </c>
       <c r="R21" t="n">
-        <v>6374967</v>
+        <v>6374969</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3085,11 +3094,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3121,10 +3125,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578784</v>
+        <v>122578812</v>
       </c>
       <c r="B22" t="n">
-        <v>99875</v>
+        <v>105545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3137,27 +3141,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3166,10 +3170,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707648</v>
+        <v>707646</v>
       </c>
       <c r="R22" t="n">
-        <v>6375072</v>
+        <v>6374967</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3206,7 +3210,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3238,10 +3242,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578742</v>
+        <v>122578784</v>
       </c>
       <c r="B23" t="n">
-        <v>105545</v>
+        <v>99875</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3254,37 +3258,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707638</v>
+        <v>707648</v>
       </c>
       <c r="R23" t="n">
-        <v>6375036</v>
+        <v>6375072</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3318,7 +3327,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3350,10 +3359,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578819</v>
+        <v>122578742</v>
       </c>
       <c r="B24" t="n">
-        <v>99875</v>
+        <v>105545</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3366,51 +3375,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707605</v>
+        <v>707638</v>
       </c>
       <c r="R24" t="n">
-        <v>6374982</v>
+        <v>6375036</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3444,7 +3439,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3458,7 +3453,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3476,10 +3471,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578795</v>
+        <v>122578819</v>
       </c>
       <c r="B25" t="n">
-        <v>105545</v>
+        <v>99875</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3492,27 +3487,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3521,10 +3525,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707725</v>
+        <v>707605</v>
       </c>
       <c r="R25" t="n">
-        <v>6374976</v>
+        <v>6374982</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3561,7 +3565,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3575,7 +3579,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3593,7 +3597,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578758</v>
+        <v>122578795</v>
       </c>
       <c r="B26" t="n">
         <v>105545</v>
@@ -3626,16 +3630,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3647,13 +3642,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707557</v>
+        <v>707725</v>
       </c>
       <c r="R26" t="n">
-        <v>6375009</v>
+        <v>6374976</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3687,7 +3682,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3719,10 +3714,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578778</v>
+        <v>122578758</v>
       </c>
       <c r="B27" t="n">
-        <v>99875</v>
+        <v>105545</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3735,36 +3730,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3773,13 +3768,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707599</v>
+        <v>707557</v>
       </c>
       <c r="R27" t="n">
-        <v>6375165</v>
+        <v>6375009</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3813,7 +3808,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Barrblandskog mot åker i N.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3827,7 +3822,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3845,10 +3840,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578802</v>
+        <v>122578778</v>
       </c>
       <c r="B28" t="n">
-        <v>98325</v>
+        <v>99875</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3857,35 +3852,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3899,13 +3894,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707697</v>
+        <v>707599</v>
       </c>
       <c r="R28" t="n">
-        <v>6374969</v>
+        <v>6375165</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3937,6 +3932,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Barrblandskog mot åker i N.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -8810,10 +8810,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578748</v>
+        <v>122578771</v>
       </c>
       <c r="B69" t="n">
-        <v>99875</v>
+        <v>98325</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8822,41 +8822,55 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707590</v>
+        <v>707490</v>
       </c>
       <c r="R69" t="n">
-        <v>6375036</v>
+        <v>6375090</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8890,7 +8904,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8904,7 +8918,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8922,7 +8936,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578823</v>
+        <v>122578748</v>
       </c>
       <c r="B70" t="n">
         <v>99875</v>
@@ -8955,31 +8969,17 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707605</v>
+        <v>707590</v>
       </c>
       <c r="R70" t="n">
-        <v>6374970</v>
+        <v>6375036</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9048,10 +9048,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578771</v>
+        <v>122578823</v>
       </c>
       <c r="B71" t="n">
-        <v>98325</v>
+        <v>99875</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9060,30 +9060,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9102,13 +9102,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707490</v>
+        <v>707605</v>
       </c>
       <c r="R71" t="n">
-        <v>6375090</v>
+        <v>6374970</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578751</v>
+        <v>122578780</v>
       </c>
       <c r="B3" t="n">
-        <v>98325</v>
+        <v>99883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,37 +822,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -864,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707569</v>
+        <v>707626</v>
       </c>
       <c r="R3" t="n">
-        <v>6374979</v>
+        <v>6375120</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578776</v>
+        <v>122578823</v>
       </c>
       <c r="B4" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -971,7 +962,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -990,13 +981,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707584</v>
+        <v>707605</v>
       </c>
       <c r="R4" t="n">
-        <v>6375172</v>
+        <v>6374970</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,6 +1019,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,7 +1035,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1057,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578815</v>
+        <v>122578819</v>
       </c>
       <c r="B5" t="n">
-        <v>105545</v>
+        <v>99883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,27 +1069,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1102,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707638</v>
+        <v>707605</v>
       </c>
       <c r="R5" t="n">
-        <v>6374988</v>
+        <v>6374982</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1142,7 +1147,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,7 +1161,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1174,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578814</v>
+        <v>122578777</v>
       </c>
       <c r="B6" t="n">
-        <v>98325</v>
+        <v>99883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,35 +1191,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1228,13 +1233,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707638</v>
+        <v>707591</v>
       </c>
       <c r="R6" t="n">
-        <v>6374988</v>
+        <v>6375187</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1266,6 +1271,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>30 m S åker i N.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1277,7 +1287,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1295,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578783</v>
+        <v>122578767</v>
       </c>
       <c r="B7" t="n">
-        <v>99875</v>
+        <v>98377</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,28 +1317,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1340,10 +1359,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707633</v>
+        <v>707513</v>
       </c>
       <c r="R7" t="n">
-        <v>6375094</v>
+        <v>6375053</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1378,11 +1397,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Glest spridd.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1394,7 +1408,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,10 +1426,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578744</v>
+        <v>122578778</v>
       </c>
       <c r="B8" t="n">
-        <v>105545</v>
+        <v>99883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,26 +1442,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1457,7 +1471,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1466,13 +1480,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707626</v>
+        <v>707599</v>
       </c>
       <c r="R8" t="n">
-        <v>6375071</v>
+        <v>6375165</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1506,7 +1520,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,7 +1534,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1538,10 +1552,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578813</v>
+        <v>122578808</v>
       </c>
       <c r="B9" t="n">
-        <v>99875</v>
+        <v>98333</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,28 +1564,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1583,10 +1606,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707646</v>
+        <v>707678</v>
       </c>
       <c r="R9" t="n">
-        <v>6374967</v>
+        <v>6374990</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1619,11 +1642,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1655,10 +1673,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578821</v>
+        <v>122578824</v>
       </c>
       <c r="B10" t="n">
-        <v>105545</v>
+        <v>99883</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,26 +1689,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1700,7 +1718,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1709,10 +1727,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707605</v>
+        <v>707606</v>
       </c>
       <c r="R10" t="n">
-        <v>6374970</v>
+        <v>6374961</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1747,11 +1765,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minsta antal + spridd.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1763,7 +1776,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1781,10 +1794,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578759</v>
+        <v>122578765</v>
       </c>
       <c r="B11" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1814,16 +1827,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1835,13 +1839,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707557</v>
+        <v>707532</v>
       </c>
       <c r="R11" t="n">
-        <v>6375009</v>
+        <v>6375035</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1875,7 +1879,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1907,10 +1911,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578766</v>
+        <v>122578762</v>
       </c>
       <c r="B12" t="n">
-        <v>99875</v>
+        <v>105553</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1923,36 +1927,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1964,10 +1968,10 @@
         <v>707548</v>
       </c>
       <c r="R12" t="n">
-        <v>6375091</v>
+        <v>6375014</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2001,7 +2005,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2015,7 +2019,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2033,10 +2037,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578800</v>
+        <v>122578812</v>
       </c>
       <c r="B13" t="n">
-        <v>105545</v>
+        <v>105553</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2066,16 +2070,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2087,10 +2082,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707697</v>
+        <v>707646</v>
       </c>
       <c r="R13" t="n">
-        <v>6374980</v>
+        <v>6374967</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2127,7 +2122,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Inget i tallplantager mot S och O.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2159,10 +2154,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578754</v>
+        <v>122578784</v>
       </c>
       <c r="B14" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2192,16 +2187,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2213,10 +2199,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707554</v>
+        <v>707648</v>
       </c>
       <c r="R14" t="n">
-        <v>6374978</v>
+        <v>6375072</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2253,7 +2239,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2285,10 +2271,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578765</v>
+        <v>122578759</v>
       </c>
       <c r="B15" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2318,7 +2304,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2330,13 +2325,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707532</v>
+        <v>707557</v>
       </c>
       <c r="R15" t="n">
-        <v>6375035</v>
+        <v>6375009</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2370,7 +2365,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2402,10 +2397,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578808</v>
+        <v>122578815</v>
       </c>
       <c r="B16" t="n">
-        <v>98325</v>
+        <v>105553</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2414,40 +2409,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2456,10 +2442,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707678</v>
+        <v>707638</v>
       </c>
       <c r="R16" t="n">
-        <v>6374990</v>
+        <v>6374988</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2492,6 +2478,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,10 +2514,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578817</v>
+        <v>122578773</v>
       </c>
       <c r="B17" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2558,7 +2549,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2577,13 +2568,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707624</v>
+        <v>707489</v>
       </c>
       <c r="R17" t="n">
-        <v>6374996</v>
+        <v>6375140</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2615,11 +2606,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spridd, ganska rikligt.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2631,7 +2617,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2649,10 +2635,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578775</v>
+        <v>122578809</v>
       </c>
       <c r="B18" t="n">
-        <v>99875</v>
+        <v>105553</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2665,36 +2651,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2703,13 +2680,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707564</v>
+        <v>707652</v>
       </c>
       <c r="R18" t="n">
-        <v>6375169</v>
+        <v>6374986</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2741,6 +2718,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2752,7 +2734,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2770,10 +2752,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578809</v>
+        <v>122578766</v>
       </c>
       <c r="B19" t="n">
-        <v>105545</v>
+        <v>99883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2786,27 +2768,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2815,13 +2806,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707652</v>
+        <v>707548</v>
       </c>
       <c r="R19" t="n">
-        <v>6374986</v>
+        <v>6375091</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2855,7 +2846,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2869,7 +2860,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2887,10 +2878,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578785</v>
+        <v>122578797</v>
       </c>
       <c r="B20" t="n">
-        <v>105545</v>
+        <v>98333</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2899,31 +2890,40 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707648</v>
+        <v>707725</v>
       </c>
       <c r="R20" t="n">
-        <v>6375072</v>
+        <v>6374976</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2968,11 +2968,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3004,10 +2999,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578802</v>
+        <v>122578795</v>
       </c>
       <c r="B21" t="n">
-        <v>98325</v>
+        <v>105553</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3016,40 +3011,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3058,10 +3044,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707697</v>
+        <v>707725</v>
       </c>
       <c r="R21" t="n">
-        <v>6374969</v>
+        <v>6374976</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3094,6 +3080,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3125,10 +3116,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578812</v>
+        <v>122578802</v>
       </c>
       <c r="B22" t="n">
-        <v>105545</v>
+        <v>98333</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3137,31 +3128,40 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707646</v>
+        <v>707697</v>
       </c>
       <c r="R22" t="n">
-        <v>6374967</v>
+        <v>6374969</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3206,11 +3206,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3242,10 +3237,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578784</v>
+        <v>122578744</v>
       </c>
       <c r="B23" t="n">
-        <v>99875</v>
+        <v>105553</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3258,27 +3253,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3287,13 +3291,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707648</v>
+        <v>707626</v>
       </c>
       <c r="R23" t="n">
-        <v>6375072</v>
+        <v>6375071</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3327,7 +3331,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3359,10 +3363,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578742</v>
+        <v>122578801</v>
       </c>
       <c r="B24" t="n">
-        <v>105545</v>
+        <v>99883</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3375,37 +3379,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707638</v>
+        <v>707697</v>
       </c>
       <c r="R24" t="n">
-        <v>6375036</v>
+        <v>6374980</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3439,7 +3448,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3471,10 +3480,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578819</v>
+        <v>122578796</v>
       </c>
       <c r="B25" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3504,16 +3513,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3525,10 +3525,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707605</v>
+        <v>707725</v>
       </c>
       <c r="R25" t="n">
-        <v>6374982</v>
+        <v>6374976</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578795</v>
+        <v>122578749</v>
       </c>
       <c r="B26" t="n">
-        <v>105545</v>
+        <v>105553</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3630,7 +3630,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3642,10 +3651,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707725</v>
+        <v>707570</v>
       </c>
       <c r="R26" t="n">
-        <v>6374976</v>
+        <v>6374984</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3682,7 +3691,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3714,10 +3723,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578758</v>
+        <v>122578741</v>
       </c>
       <c r="B27" t="n">
-        <v>105545</v>
+        <v>99883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3730,51 +3739,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707557</v>
+        <v>707609</v>
       </c>
       <c r="R27" t="n">
-        <v>6375009</v>
+        <v>6375033</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3808,7 +3803,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3840,10 +3835,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578778</v>
+        <v>122578774</v>
       </c>
       <c r="B28" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3875,7 +3870,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3894,10 +3889,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707599</v>
+        <v>707528</v>
       </c>
       <c r="R28" t="n">
-        <v>6375165</v>
+        <v>6375154</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
@@ -3930,11 +3925,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3966,10 +3956,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578797</v>
+        <v>122578811</v>
       </c>
       <c r="B29" t="n">
-        <v>98325</v>
+        <v>98333</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4020,10 +4010,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707725</v>
+        <v>707652</v>
       </c>
       <c r="R29" t="n">
-        <v>6374976</v>
+        <v>6374986</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4087,10 +4077,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578781</v>
+        <v>122578748</v>
       </c>
       <c r="B30" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4121,21 +4111,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707621</v>
+        <v>707590</v>
       </c>
       <c r="R30" t="n">
-        <v>6375108</v>
+        <v>6375036</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4172,7 +4157,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4204,10 +4189,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578806</v>
+        <v>122578763</v>
       </c>
       <c r="B31" t="n">
-        <v>105545</v>
+        <v>99883</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4220,27 +4205,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4249,13 +4243,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707678</v>
+        <v>707548</v>
       </c>
       <c r="R31" t="n">
-        <v>6374990</v>
+        <v>6375014</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4289,7 +4283,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4321,10 +4315,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578816</v>
+        <v>122578814</v>
       </c>
       <c r="B32" t="n">
-        <v>99875</v>
+        <v>98333</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4333,28 +4327,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4402,11 +4405,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4438,10 +4436,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578818</v>
+        <v>122578783</v>
       </c>
       <c r="B33" t="n">
-        <v>105545</v>
+        <v>99883</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4454,36 +4452,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4492,13 +4481,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707605</v>
+        <v>707633</v>
       </c>
       <c r="R33" t="n">
-        <v>6374982</v>
+        <v>6375094</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4532,7 +4521,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4546,7 +4535,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4564,10 +4553,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578810</v>
+        <v>122578760</v>
       </c>
       <c r="B34" t="n">
-        <v>99875</v>
+        <v>105553</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4580,27 +4569,36 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4609,10 +4607,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707652</v>
+        <v>707547</v>
       </c>
       <c r="R34" t="n">
-        <v>6374986</v>
+        <v>6375010</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4649,7 +4647,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4681,10 +4679,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578760</v>
+        <v>122578764</v>
       </c>
       <c r="B35" t="n">
-        <v>105545</v>
+        <v>99883</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4697,36 +4695,36 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4735,13 +4733,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707547</v>
+        <v>707538</v>
       </c>
       <c r="R35" t="n">
-        <v>6375010</v>
+        <v>6375024</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4807,10 +4805,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578767</v>
+        <v>122578817</v>
       </c>
       <c r="B36" t="n">
-        <v>98369</v>
+        <v>99883</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4819,35 +4817,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4861,13 +4859,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707513</v>
+        <v>707624</v>
       </c>
       <c r="R36" t="n">
-        <v>6375053</v>
+        <v>6374996</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4899,6 +4897,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd, ganska rikligt.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4910,7 +4913,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4931,7 +4934,7 @@
         <v>122578772</v>
       </c>
       <c r="B37" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5054,10 +5057,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578801</v>
+        <v>122578776</v>
       </c>
       <c r="B38" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5087,7 +5090,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5099,13 +5111,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707697</v>
+        <v>707584</v>
       </c>
       <c r="R38" t="n">
-        <v>6374980</v>
+        <v>6375172</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5137,11 +5149,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5153,7 +5160,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5171,10 +5178,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578743</v>
+        <v>122578807</v>
       </c>
       <c r="B39" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5205,19 +5212,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707638</v>
+        <v>707678</v>
       </c>
       <c r="R39" t="n">
-        <v>6375036</v>
+        <v>6374990</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5251,7 +5263,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5283,10 +5295,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578811</v>
+        <v>122578781</v>
       </c>
       <c r="B40" t="n">
-        <v>98325</v>
+        <v>99883</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5295,37 +5307,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5337,10 +5340,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707652</v>
+        <v>707621</v>
       </c>
       <c r="R40" t="n">
-        <v>6374986</v>
+        <v>6375108</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5373,6 +5376,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5404,10 +5412,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578757</v>
+        <v>122578746</v>
       </c>
       <c r="B41" t="n">
-        <v>98325</v>
+        <v>99883</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5416,55 +5424,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707557</v>
+        <v>707626</v>
       </c>
       <c r="R41" t="n">
-        <v>6375009</v>
+        <v>6375071</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5498,7 +5492,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5530,10 +5524,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578780</v>
+        <v>122578752</v>
       </c>
       <c r="B42" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5563,7 +5557,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5575,13 +5578,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707626</v>
+        <v>707569</v>
       </c>
       <c r="R42" t="n">
-        <v>6375120</v>
+        <v>6374979</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5615,7 +5618,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5647,10 +5650,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578756</v>
+        <v>122578818</v>
       </c>
       <c r="B43" t="n">
-        <v>99875</v>
+        <v>105553</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5663,36 +5666,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5701,13 +5704,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707541</v>
+        <v>707605</v>
       </c>
       <c r="R43" t="n">
-        <v>6374993</v>
+        <v>6374982</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5741,7 +5744,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5755,7 +5758,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5773,10 +5776,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578770</v>
+        <v>122578758</v>
       </c>
       <c r="B44" t="n">
-        <v>99875</v>
+        <v>105553</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5789,36 +5792,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5827,13 +5830,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707506</v>
+        <v>707557</v>
       </c>
       <c r="R44" t="n">
-        <v>6375077</v>
+        <v>6375009</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5867,7 +5870,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5881,7 +5884,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5899,10 +5902,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578763</v>
+        <v>122578770</v>
       </c>
       <c r="B45" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5934,7 +5937,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5953,13 +5956,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707548</v>
+        <v>707506</v>
       </c>
       <c r="R45" t="n">
-        <v>6375014</v>
+        <v>6375077</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5993,7 +5996,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6007,7 +6010,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6025,10 +6028,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578749</v>
+        <v>122578800</v>
       </c>
       <c r="B46" t="n">
-        <v>105545</v>
+        <v>105553</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6060,12 +6063,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6079,10 +6082,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707570</v>
+        <v>707697</v>
       </c>
       <c r="R46" t="n">
-        <v>6374984</v>
+        <v>6374980</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6119,7 +6122,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6151,10 +6154,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578740</v>
+        <v>122578775</v>
       </c>
       <c r="B47" t="n">
-        <v>105545</v>
+        <v>99883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6167,34 +6170,48 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707609</v>
+        <v>707564</v>
       </c>
       <c r="R47" t="n">
-        <v>6375033</v>
+        <v>6375169</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6229,11 +6246,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6245,7 +6257,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6263,10 +6275,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578764</v>
+        <v>122578751</v>
       </c>
       <c r="B48" t="n">
-        <v>99875</v>
+        <v>98333</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6275,35 +6287,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6317,13 +6329,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707538</v>
+        <v>707569</v>
       </c>
       <c r="R48" t="n">
-        <v>6375024</v>
+        <v>6374979</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6389,10 +6401,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578746</v>
+        <v>122578757</v>
       </c>
       <c r="B49" t="n">
-        <v>99875</v>
+        <v>98333</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6401,41 +6413,55 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707626</v>
+        <v>707557</v>
       </c>
       <c r="R49" t="n">
-        <v>6375071</v>
+        <v>6375009</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6469,7 +6495,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6501,10 +6527,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578796</v>
+        <v>122578769</v>
       </c>
       <c r="B50" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6534,7 +6560,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6546,13 +6581,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707725</v>
+        <v>707513</v>
       </c>
       <c r="R50" t="n">
-        <v>6374976</v>
+        <v>6375053</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6586,7 +6621,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6600,7 +6635,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6618,10 +6653,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578825</v>
+        <v>122578813</v>
       </c>
       <c r="B51" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6651,16 +6686,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6672,10 +6698,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707611</v>
+        <v>707646</v>
       </c>
       <c r="R51" t="n">
-        <v>6374954</v>
+        <v>6374967</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6710,6 +6736,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6721,7 +6752,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6739,10 +6770,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578750</v>
+        <v>122578742</v>
       </c>
       <c r="B52" t="n">
-        <v>98369</v>
+        <v>105553</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6751,55 +6782,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219862</v>
+        <v>671</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707569</v>
+        <v>707638</v>
       </c>
       <c r="R52" t="n">
-        <v>6374979</v>
+        <v>6375036</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6833,7 +6850,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6865,10 +6882,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578805</v>
+        <v>122578743</v>
       </c>
       <c r="B53" t="n">
-        <v>98325</v>
+        <v>99883</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6877,55 +6894,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707697</v>
+        <v>707638</v>
       </c>
       <c r="R53" t="n">
-        <v>6374980</v>
+        <v>6375036</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6955,6 +6958,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6986,10 +6994,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578786</v>
+        <v>122578816</v>
       </c>
       <c r="B54" t="n">
-        <v>98325</v>
+        <v>99883</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6998,37 +7006,28 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7040,10 +7039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707652</v>
+        <v>707638</v>
       </c>
       <c r="R54" t="n">
-        <v>6375083</v>
+        <v>6374988</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7080,7 +7079,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7112,10 +7111,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578753</v>
+        <v>122578756</v>
       </c>
       <c r="B55" t="n">
-        <v>98325</v>
+        <v>99883</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7124,35 +7123,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7166,13 +7165,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707554</v>
+        <v>707541</v>
       </c>
       <c r="R55" t="n">
-        <v>6374978</v>
+        <v>6374993</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7241,7 +7240,7 @@
         <v>122578747</v>
       </c>
       <c r="B56" t="n">
-        <v>105545</v>
+        <v>105553</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7350,10 +7349,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578824</v>
+        <v>122578805</v>
       </c>
       <c r="B57" t="n">
-        <v>99875</v>
+        <v>98333</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7362,35 +7361,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7404,10 +7403,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707606</v>
+        <v>707697</v>
       </c>
       <c r="R57" t="n">
-        <v>6374961</v>
+        <v>6374980</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7453,7 +7452,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7471,10 +7470,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578752</v>
+        <v>122578753</v>
       </c>
       <c r="B58" t="n">
-        <v>99875</v>
+        <v>98333</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7483,35 +7482,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7525,13 +7524,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707569</v>
+        <v>707554</v>
       </c>
       <c r="R58" t="n">
-        <v>6374979</v>
+        <v>6374978</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7600,7 +7599,7 @@
         <v>122578755</v>
       </c>
       <c r="B59" t="n">
-        <v>98325</v>
+        <v>98333</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7723,10 +7722,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578769</v>
+        <v>122578806</v>
       </c>
       <c r="B60" t="n">
-        <v>99875</v>
+        <v>105553</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7739,36 +7738,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7777,13 +7767,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707513</v>
+        <v>707678</v>
       </c>
       <c r="R60" t="n">
-        <v>6375053</v>
+        <v>6374990</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7817,7 +7807,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7831,7 +7821,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7849,10 +7839,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578773</v>
+        <v>122578785</v>
       </c>
       <c r="B61" t="n">
-        <v>99875</v>
+        <v>105553</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7865,36 +7855,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7903,13 +7884,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707489</v>
+        <v>707648</v>
       </c>
       <c r="R61" t="n">
-        <v>6375140</v>
+        <v>6375072</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7941,6 +7922,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Glest spridd, men saknas mot O-NO..</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7952,7 +7938,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7970,10 +7956,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578741</v>
+        <v>122578825</v>
       </c>
       <c r="B62" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8003,20 +7989,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707609</v>
+        <v>707611</v>
       </c>
       <c r="R62" t="n">
-        <v>6375033</v>
+        <v>6374954</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8048,11 +8048,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8064,7 +8059,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8082,10 +8077,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578762</v>
+        <v>122578750</v>
       </c>
       <c r="B63" t="n">
-        <v>105545</v>
+        <v>98377</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8094,40 +8089,40 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>671</v>
+        <v>219862</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8136,10 +8131,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707548</v>
+        <v>707569</v>
       </c>
       <c r="R63" t="n">
-        <v>6375014</v>
+        <v>6374979</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -8208,10 +8203,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578779</v>
+        <v>122578771</v>
       </c>
       <c r="B64" t="n">
-        <v>99875</v>
+        <v>98333</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8220,28 +8215,37 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8253,13 +8257,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707597</v>
+        <v>707490</v>
       </c>
       <c r="R64" t="n">
-        <v>6375142</v>
+        <v>6375090</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8293,7 +8297,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8307,7 +8311,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8325,10 +8329,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578774</v>
+        <v>122578782</v>
       </c>
       <c r="B65" t="n">
-        <v>99875</v>
+        <v>98333</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8337,35 +8341,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8379,13 +8383,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707528</v>
+        <v>707621</v>
       </c>
       <c r="R65" t="n">
-        <v>6375154</v>
+        <v>6375108</v>
       </c>
       <c r="S65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8428,7 +8432,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8446,10 +8450,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578807</v>
+        <v>122578786</v>
       </c>
       <c r="B66" t="n">
-        <v>99875</v>
+        <v>98333</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8458,28 +8462,37 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8491,10 +8504,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707678</v>
+        <v>707652</v>
       </c>
       <c r="R66" t="n">
-        <v>6374990</v>
+        <v>6375083</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8531,7 +8544,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8563,10 +8576,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578777</v>
+        <v>122578740</v>
       </c>
       <c r="B67" t="n">
-        <v>99875</v>
+        <v>105553</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8579,51 +8592,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707591</v>
+        <v>707609</v>
       </c>
       <c r="R67" t="n">
-        <v>6375187</v>
+        <v>6375033</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8657,7 +8656,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>30 m S åker i N.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8671,7 +8670,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8689,10 +8688,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578782</v>
+        <v>122578754</v>
       </c>
       <c r="B68" t="n">
-        <v>98325</v>
+        <v>99883</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8701,35 +8700,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8743,10 +8742,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707621</v>
+        <v>707554</v>
       </c>
       <c r="R68" t="n">
-        <v>6375108</v>
+        <v>6374978</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8779,6 +8778,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8810,10 +8814,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578771</v>
+        <v>122578821</v>
       </c>
       <c r="B69" t="n">
-        <v>98325</v>
+        <v>105553</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8822,30 +8826,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8855,7 +8859,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8864,13 +8868,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707490</v>
+        <v>707605</v>
       </c>
       <c r="R69" t="n">
-        <v>6375090</v>
+        <v>6374970</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8904,7 +8908,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8918,7 +8922,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8936,10 +8940,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578748</v>
+        <v>122578810</v>
       </c>
       <c r="B70" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8970,16 +8974,21 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707590</v>
+        <v>707652</v>
       </c>
       <c r="R70" t="n">
-        <v>6375036</v>
+        <v>6374986</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9048,10 +9057,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578823</v>
+        <v>122578779</v>
       </c>
       <c r="B71" t="n">
-        <v>99875</v>
+        <v>99883</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9081,16 +9090,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -9102,13 +9102,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707605</v>
+        <v>707597</v>
       </c>
       <c r="R71" t="n">
-        <v>6374970</v>
+        <v>6375142</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Enstaka strå.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578780</v>
+        <v>122578783</v>
       </c>
       <c r="B3" t="n">
         <v>99883</v>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707626</v>
+        <v>707633</v>
       </c>
       <c r="R3" t="n">
-        <v>6375120</v>
+        <v>6375094</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,7 +927,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578823</v>
+        <v>122578741</v>
       </c>
       <c r="B4" t="n">
         <v>99883</v>
@@ -960,34 +960,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707605</v>
+        <v>707609</v>
       </c>
       <c r="R4" t="n">
-        <v>6374970</v>
+        <v>6375033</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,7 +1007,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1021,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578819</v>
+        <v>122578823</v>
       </c>
       <c r="B5" t="n">
         <v>99883</v>
@@ -1088,7 +1074,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1110,7 +1096,7 @@
         <v>707605</v>
       </c>
       <c r="R5" t="n">
-        <v>6374982</v>
+        <v>6374970</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1179,7 +1165,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578777</v>
+        <v>122578776</v>
       </c>
       <c r="B6" t="n">
         <v>99883</v>
@@ -1214,7 +1200,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1233,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707591</v>
+        <v>707584</v>
       </c>
       <c r="R6" t="n">
-        <v>6375187</v>
+        <v>6375172</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1271,11 +1257,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>30 m S åker i N.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1287,7 +1268,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1286,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578767</v>
+        <v>122578755</v>
       </c>
       <c r="B7" t="n">
-        <v>98377</v>
+        <v>98333</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,21 +1302,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1359,13 +1340,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707513</v>
+        <v>707541</v>
       </c>
       <c r="R7" t="n">
-        <v>6375053</v>
+        <v>6374993</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1397,6 +1378,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1408,7 +1394,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1426,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578778</v>
+        <v>122578749</v>
       </c>
       <c r="B8" t="n">
-        <v>99883</v>
+        <v>105553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,36 +1428,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1480,13 +1466,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707599</v>
+        <v>707570</v>
       </c>
       <c r="R8" t="n">
-        <v>6375165</v>
+        <v>6374984</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1520,7 +1506,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Barrblandskog mot åker i N.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1552,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578808</v>
+        <v>122578762</v>
       </c>
       <c r="B9" t="n">
-        <v>98333</v>
+        <v>105553</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,40 +1550,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1606,13 +1592,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707678</v>
+        <v>707548</v>
       </c>
       <c r="R9" t="n">
-        <v>6374990</v>
+        <v>6375014</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1642,6 +1628,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,10 +1664,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578824</v>
+        <v>122578800</v>
       </c>
       <c r="B10" t="n">
-        <v>99883</v>
+        <v>105553</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,21 +1680,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1713,12 +1704,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1727,10 +1718,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707606</v>
+        <v>707697</v>
       </c>
       <c r="R10" t="n">
-        <v>6374961</v>
+        <v>6374980</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1765,6 +1756,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Inget i tallplantager mot S och O.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1776,7 +1772,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1794,7 +1790,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578765</v>
+        <v>122578810</v>
       </c>
       <c r="B11" t="n">
         <v>99883</v>
@@ -1839,13 +1835,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707532</v>
+        <v>707652</v>
       </c>
       <c r="R11" t="n">
-        <v>6375035</v>
+        <v>6374986</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1879,7 +1875,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1911,10 +1907,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578762</v>
+        <v>122578756</v>
       </c>
       <c r="B12" t="n">
-        <v>105553</v>
+        <v>99883</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1927,36 +1923,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1965,10 +1961,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707548</v>
+        <v>707541</v>
       </c>
       <c r="R12" t="n">
-        <v>6375014</v>
+        <v>6374993</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -2037,7 +2033,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578812</v>
+        <v>122578818</v>
       </c>
       <c r="B13" t="n">
         <v>105553</v>
@@ -2070,7 +2066,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2082,10 +2087,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707646</v>
+        <v>707605</v>
       </c>
       <c r="R13" t="n">
-        <v>6374967</v>
+        <v>6374982</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2122,7 +2127,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,7 +2141,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2154,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578784</v>
+        <v>122578751</v>
       </c>
       <c r="B14" t="n">
-        <v>99883</v>
+        <v>98333</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2166,28 +2171,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2199,13 +2213,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707648</v>
+        <v>707569</v>
       </c>
       <c r="R14" t="n">
-        <v>6375072</v>
+        <v>6374979</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2239,7 +2253,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2271,7 +2285,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578759</v>
+        <v>122578819</v>
       </c>
       <c r="B15" t="n">
         <v>99883</v>
@@ -2306,7 +2320,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2325,13 +2339,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707557</v>
+        <v>707605</v>
       </c>
       <c r="R15" t="n">
-        <v>6375009</v>
+        <v>6374982</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2365,7 +2379,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2379,7 +2393,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2397,10 +2411,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578815</v>
+        <v>122578816</v>
       </c>
       <c r="B16" t="n">
-        <v>105553</v>
+        <v>99883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2413,27 +2427,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2514,10 +2528,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578773</v>
+        <v>122578744</v>
       </c>
       <c r="B17" t="n">
-        <v>99883</v>
+        <v>105553</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2530,26 +2544,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2559,7 +2573,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2568,13 +2582,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707489</v>
+        <v>707626</v>
       </c>
       <c r="R17" t="n">
-        <v>6375140</v>
+        <v>6375071</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2606,6 +2620,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Stensamling, grav? Nära.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2617,7 +2636,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2635,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578809</v>
+        <v>122578781</v>
       </c>
       <c r="B18" t="n">
-        <v>105553</v>
+        <v>99883</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2651,27 +2670,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2680,10 +2699,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707652</v>
+        <v>707621</v>
       </c>
       <c r="R18" t="n">
-        <v>6374986</v>
+        <v>6375108</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2720,7 +2739,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2752,10 +2771,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578766</v>
+        <v>122578805</v>
       </c>
       <c r="B19" t="n">
-        <v>99883</v>
+        <v>98333</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2764,35 +2783,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2806,13 +2825,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707548</v>
+        <v>707697</v>
       </c>
       <c r="R19" t="n">
-        <v>6375091</v>
+        <v>6374980</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2844,11 +2863,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2860,7 +2874,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2878,7 +2892,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578797</v>
+        <v>122578757</v>
       </c>
       <c r="B20" t="n">
         <v>98333</v>
@@ -2913,7 +2927,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2932,13 +2946,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707725</v>
+        <v>707557</v>
       </c>
       <c r="R20" t="n">
-        <v>6374976</v>
+        <v>6375009</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2968,6 +2982,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2999,10 +3018,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578795</v>
+        <v>122578824</v>
       </c>
       <c r="B21" t="n">
-        <v>105553</v>
+        <v>99883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3015,27 +3034,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3044,10 +3072,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707725</v>
+        <v>707606</v>
       </c>
       <c r="R21" t="n">
-        <v>6374976</v>
+        <v>6374961</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3082,11 +3110,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3098,7 +3121,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3116,10 +3139,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578802</v>
+        <v>122578812</v>
       </c>
       <c r="B22" t="n">
-        <v>98333</v>
+        <v>105553</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3128,40 +3151,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3170,10 +3184,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707697</v>
+        <v>707646</v>
       </c>
       <c r="R22" t="n">
-        <v>6374969</v>
+        <v>6374967</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3206,6 +3220,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3237,10 +3256,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578744</v>
+        <v>122578817</v>
       </c>
       <c r="B23" t="n">
-        <v>105553</v>
+        <v>99883</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3253,26 +3272,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3282,7 +3301,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3291,13 +3310,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707626</v>
+        <v>707624</v>
       </c>
       <c r="R23" t="n">
-        <v>6375071</v>
+        <v>6374996</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3331,7 +3350,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3363,7 +3382,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578801</v>
+        <v>122578765</v>
       </c>
       <c r="B24" t="n">
         <v>99883</v>
@@ -3408,13 +3427,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707697</v>
+        <v>707532</v>
       </c>
       <c r="R24" t="n">
-        <v>6374980</v>
+        <v>6375035</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3448,7 +3467,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3480,7 +3499,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578796</v>
+        <v>122578775</v>
       </c>
       <c r="B25" t="n">
         <v>99883</v>
@@ -3513,7 +3532,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3525,13 +3553,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707725</v>
+        <v>707564</v>
       </c>
       <c r="R25" t="n">
-        <v>6374976</v>
+        <v>6375169</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3563,11 +3591,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3579,7 +3602,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3597,7 +3620,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578749</v>
+        <v>122578740</v>
       </c>
       <c r="B26" t="n">
         <v>105553</v>
@@ -3630,34 +3653,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707570</v>
+        <v>707609</v>
       </c>
       <c r="R26" t="n">
-        <v>6374984</v>
+        <v>6375033</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3691,7 +3700,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3723,10 +3732,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578741</v>
+        <v>122578821</v>
       </c>
       <c r="B27" t="n">
-        <v>99883</v>
+        <v>105553</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3739,37 +3748,51 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707609</v>
+        <v>707605</v>
       </c>
       <c r="R27" t="n">
-        <v>6375033</v>
+        <v>6374970</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3803,7 +3826,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3817,7 +3840,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3835,10 +3858,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578774</v>
+        <v>122578758</v>
       </c>
       <c r="B28" t="n">
-        <v>99883</v>
+        <v>105553</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3851,36 +3874,36 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3889,13 +3912,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707528</v>
+        <v>707557</v>
       </c>
       <c r="R28" t="n">
-        <v>6375154</v>
+        <v>6375009</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3927,6 +3950,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3938,7 +3966,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4077,10 +4105,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578748</v>
+        <v>122578771</v>
       </c>
       <c r="B30" t="n">
-        <v>99883</v>
+        <v>98333</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4089,41 +4117,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707590</v>
+        <v>707490</v>
       </c>
       <c r="R30" t="n">
-        <v>6375036</v>
+        <v>6375090</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4157,7 +4199,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4171,7 +4213,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4189,10 +4231,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578763</v>
+        <v>122578786</v>
       </c>
       <c r="B31" t="n">
-        <v>99883</v>
+        <v>98333</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4201,35 +4243,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4243,13 +4285,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707548</v>
+        <v>707652</v>
       </c>
       <c r="R31" t="n">
-        <v>6375014</v>
+        <v>6375083</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4283,7 +4325,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4315,10 +4357,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578814</v>
+        <v>122578769</v>
       </c>
       <c r="B32" t="n">
-        <v>98333</v>
+        <v>99883</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4327,35 +4369,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4369,13 +4411,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707638</v>
+        <v>707513</v>
       </c>
       <c r="R32" t="n">
-        <v>6374988</v>
+        <v>6375053</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4407,6 +4449,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>3 ex.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4418,7 +4465,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4436,7 +4483,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578783</v>
+        <v>122578807</v>
       </c>
       <c r="B33" t="n">
         <v>99883</v>
@@ -4481,13 +4528,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707633</v>
+        <v>707678</v>
       </c>
       <c r="R33" t="n">
-        <v>6375094</v>
+        <v>6374990</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4521,7 +4568,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4553,7 +4600,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578760</v>
+        <v>122578785</v>
       </c>
       <c r="B34" t="n">
         <v>105553</v>
@@ -4586,16 +4633,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4607,10 +4645,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707547</v>
+        <v>707648</v>
       </c>
       <c r="R34" t="n">
-        <v>6375010</v>
+        <v>6375072</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4647,7 +4685,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4679,10 +4717,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578764</v>
+        <v>122578809</v>
       </c>
       <c r="B35" t="n">
-        <v>99883</v>
+        <v>105553</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4695,36 +4733,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4733,13 +4762,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707538</v>
+        <v>707652</v>
       </c>
       <c r="R35" t="n">
-        <v>6375024</v>
+        <v>6374986</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4773,7 +4802,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4805,7 +4834,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578817</v>
+        <v>122578763</v>
       </c>
       <c r="B36" t="n">
         <v>99883</v>
@@ -4840,7 +4869,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4859,13 +4888,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707624</v>
+        <v>707548</v>
       </c>
       <c r="R36" t="n">
-        <v>6374996</v>
+        <v>6375014</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4899,7 +4928,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4931,7 +4960,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578772</v>
+        <v>122578770</v>
       </c>
       <c r="B37" t="n">
         <v>99883</v>
@@ -4966,7 +4995,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4988,7 +5017,7 @@
         <v>707506</v>
       </c>
       <c r="R37" t="n">
-        <v>6375110</v>
+        <v>6375077</v>
       </c>
       <c r="S37" t="n">
         <v>7</v>
@@ -5057,10 +5086,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578776</v>
+        <v>122578742</v>
       </c>
       <c r="B38" t="n">
-        <v>99883</v>
+        <v>105553</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5073,51 +5102,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707584</v>
+        <v>707638</v>
       </c>
       <c r="R38" t="n">
-        <v>6375172</v>
+        <v>6375036</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5149,6 +5164,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5160,7 +5180,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5178,7 +5198,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578807</v>
+        <v>122578801</v>
       </c>
       <c r="B39" t="n">
         <v>99883</v>
@@ -5223,10 +5243,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707678</v>
+        <v>707697</v>
       </c>
       <c r="R39" t="n">
-        <v>6374990</v>
+        <v>6374980</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5263,7 +5283,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5295,7 +5315,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578781</v>
+        <v>122578743</v>
       </c>
       <c r="B40" t="n">
         <v>99883</v>
@@ -5329,24 +5349,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707621</v>
+        <v>707638</v>
       </c>
       <c r="R40" t="n">
-        <v>6375108</v>
+        <v>6375036</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5380,7 +5395,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5412,7 +5427,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578746</v>
+        <v>122578825</v>
       </c>
       <c r="B41" t="n">
         <v>99883</v>
@@ -5445,20 +5460,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707626</v>
+        <v>707611</v>
       </c>
       <c r="R41" t="n">
-        <v>6375071</v>
+        <v>6374954</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5490,11 +5519,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Stensamling, grav? Nära.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5506,7 +5530,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5524,7 +5548,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578752</v>
+        <v>122578779</v>
       </c>
       <c r="B42" t="n">
         <v>99883</v>
@@ -5557,16 +5581,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5578,13 +5593,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707569</v>
+        <v>707597</v>
       </c>
       <c r="R42" t="n">
-        <v>6374979</v>
+        <v>6375142</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5618,7 +5633,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Enstaka strå.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5632,7 +5647,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5650,7 +5665,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578818</v>
+        <v>122578806</v>
       </c>
       <c r="B43" t="n">
         <v>105553</v>
@@ -5683,16 +5698,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5704,10 +5710,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707605</v>
+        <v>707678</v>
       </c>
       <c r="R43" t="n">
-        <v>6374982</v>
+        <v>6374990</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5744,7 +5750,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5758,7 +5764,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5776,7 +5782,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578758</v>
+        <v>122578815</v>
       </c>
       <c r="B44" t="n">
         <v>105553</v>
@@ -5809,16 +5815,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5830,13 +5827,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707557</v>
+        <v>707638</v>
       </c>
       <c r="R44" t="n">
-        <v>6375009</v>
+        <v>6374988</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5870,7 +5867,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5902,7 +5899,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578770</v>
+        <v>122578773</v>
       </c>
       <c r="B45" t="n">
         <v>99883</v>
@@ -5937,7 +5934,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5956,13 +5953,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707506</v>
+        <v>707489</v>
       </c>
       <c r="R45" t="n">
-        <v>6375077</v>
+        <v>6375140</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5994,11 +5991,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2 ex.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6010,7 +6002,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6028,10 +6020,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578800</v>
+        <v>122578782</v>
       </c>
       <c r="B46" t="n">
-        <v>105553</v>
+        <v>98333</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6040,40 +6032,40 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6082,10 +6074,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707697</v>
+        <v>707621</v>
       </c>
       <c r="R46" t="n">
-        <v>6374980</v>
+        <v>6375108</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6118,11 +6110,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6154,10 +6141,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578775</v>
+        <v>122578747</v>
       </c>
       <c r="B47" t="n">
-        <v>99883</v>
+        <v>105553</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6170,51 +6157,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707564</v>
+        <v>707590</v>
       </c>
       <c r="R47" t="n">
-        <v>6375169</v>
+        <v>6375036</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6246,6 +6219,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6257,7 +6235,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6275,10 +6253,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578751</v>
+        <v>122578777</v>
       </c>
       <c r="B48" t="n">
-        <v>98333</v>
+        <v>99883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6287,35 +6265,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6329,13 +6307,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707569</v>
+        <v>707591</v>
       </c>
       <c r="R48" t="n">
-        <v>6374979</v>
+        <v>6375187</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6369,7 +6347,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>30 m S åker i N.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6383,7 +6361,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6401,10 +6379,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578757</v>
+        <v>122578767</v>
       </c>
       <c r="B49" t="n">
-        <v>98333</v>
+        <v>98377</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6417,26 +6395,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6455,13 +6433,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707557</v>
+        <v>707513</v>
       </c>
       <c r="R49" t="n">
-        <v>6375009</v>
+        <v>6375053</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6493,11 +6471,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6509,7 +6482,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6527,10 +6500,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578769</v>
+        <v>122578795</v>
       </c>
       <c r="B50" t="n">
-        <v>99883</v>
+        <v>105553</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6543,36 +6516,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6581,13 +6545,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707513</v>
+        <v>707725</v>
       </c>
       <c r="R50" t="n">
-        <v>6375053</v>
+        <v>6374976</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6621,7 +6585,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6635,7 +6599,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6653,10 +6617,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578813</v>
+        <v>122578797</v>
       </c>
       <c r="B51" t="n">
-        <v>99883</v>
+        <v>98333</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6665,28 +6629,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6698,10 +6671,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707646</v>
+        <v>707725</v>
       </c>
       <c r="R51" t="n">
-        <v>6374967</v>
+        <v>6374976</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6734,11 +6707,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6770,10 +6738,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578742</v>
+        <v>122578808</v>
       </c>
       <c r="B52" t="n">
-        <v>105553</v>
+        <v>98333</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6782,41 +6750,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707638</v>
+        <v>707678</v>
       </c>
       <c r="R52" t="n">
-        <v>6375036</v>
+        <v>6374990</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6846,11 +6828,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6882,7 +6859,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578743</v>
+        <v>122578813</v>
       </c>
       <c r="B53" t="n">
         <v>99883</v>
@@ -6916,19 +6893,24 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707638</v>
+        <v>707646</v>
       </c>
       <c r="R53" t="n">
-        <v>6375036</v>
+        <v>6374967</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6962,7 +6944,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6994,7 +6976,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578816</v>
+        <v>122578772</v>
       </c>
       <c r="B54" t="n">
         <v>99883</v>
@@ -7027,7 +7009,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7039,13 +7030,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707638</v>
+        <v>707506</v>
       </c>
       <c r="R54" t="n">
-        <v>6374988</v>
+        <v>6375110</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7079,7 +7070,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7093,7 +7084,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7111,7 +7102,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578756</v>
+        <v>122578746</v>
       </c>
       <c r="B55" t="n">
         <v>99883</v>
@@ -7144,34 +7135,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707541</v>
+        <v>707626</v>
       </c>
       <c r="R55" t="n">
-        <v>6374993</v>
+        <v>6375071</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7205,7 +7182,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7237,10 +7214,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578747</v>
+        <v>122578814</v>
       </c>
       <c r="B56" t="n">
-        <v>105553</v>
+        <v>98333</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7249,38 +7226,52 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707590</v>
+        <v>707638</v>
       </c>
       <c r="R56" t="n">
-        <v>6375036</v>
+        <v>6374988</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7313,11 +7304,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7349,10 +7335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578805</v>
+        <v>122578750</v>
       </c>
       <c r="B57" t="n">
-        <v>98333</v>
+        <v>98377</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7365,26 +7351,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7403,13 +7389,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707697</v>
+        <v>707569</v>
       </c>
       <c r="R57" t="n">
-        <v>6374980</v>
+        <v>6374979</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7439,6 +7425,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7596,10 +7587,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578755</v>
+        <v>122578774</v>
       </c>
       <c r="B59" t="n">
-        <v>98333</v>
+        <v>99883</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7608,35 +7599,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7650,13 +7641,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707541</v>
+        <v>707528</v>
       </c>
       <c r="R59" t="n">
-        <v>6374993</v>
+        <v>6375154</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7688,11 +7679,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7704,7 +7690,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7722,10 +7708,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578806</v>
+        <v>122578752</v>
       </c>
       <c r="B60" t="n">
-        <v>105553</v>
+        <v>99883</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7738,27 +7724,36 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7767,13 +7762,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707678</v>
+        <v>707569</v>
       </c>
       <c r="R60" t="n">
-        <v>6374990</v>
+        <v>6374979</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7807,7 +7802,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7839,10 +7834,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578785</v>
+        <v>122578778</v>
       </c>
       <c r="B61" t="n">
-        <v>105553</v>
+        <v>99883</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7855,27 +7850,36 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7884,13 +7888,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707648</v>
+        <v>707599</v>
       </c>
       <c r="R61" t="n">
-        <v>6375072</v>
+        <v>6375165</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7924,7 +7928,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7938,7 +7942,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7956,7 +7960,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578825</v>
+        <v>122578748</v>
       </c>
       <c r="B62" t="n">
         <v>99883</v>
@@ -7989,31 +7993,17 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707611</v>
+        <v>707590</v>
       </c>
       <c r="R62" t="n">
-        <v>6374954</v>
+        <v>6375036</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8048,6 +8038,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8059,7 +8054,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8077,10 +8072,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578750</v>
+        <v>122578754</v>
       </c>
       <c r="B63" t="n">
-        <v>98377</v>
+        <v>99883</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8089,35 +8084,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8131,13 +8126,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707569</v>
+        <v>707554</v>
       </c>
       <c r="R63" t="n">
-        <v>6374979</v>
+        <v>6374978</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8203,10 +8198,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578771</v>
+        <v>122578784</v>
       </c>
       <c r="B64" t="n">
-        <v>98333</v>
+        <v>99883</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8215,37 +8210,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8257,13 +8243,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707490</v>
+        <v>707648</v>
       </c>
       <c r="R64" t="n">
-        <v>6375090</v>
+        <v>6375072</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8297,7 +8283,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8311,7 +8297,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8329,10 +8315,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578782</v>
+        <v>122578759</v>
       </c>
       <c r="B65" t="n">
-        <v>98333</v>
+        <v>99883</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8341,35 +8327,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8383,13 +8369,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707621</v>
+        <v>707557</v>
       </c>
       <c r="R65" t="n">
-        <v>6375108</v>
+        <v>6375009</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8419,6 +8405,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8450,10 +8441,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578786</v>
+        <v>122578764</v>
       </c>
       <c r="B66" t="n">
-        <v>98333</v>
+        <v>99883</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8462,35 +8453,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8504,13 +8495,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707652</v>
+        <v>707538</v>
       </c>
       <c r="R66" t="n">
-        <v>6375083</v>
+        <v>6375024</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8544,7 +8535,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8576,10 +8567,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578740</v>
+        <v>122578766</v>
       </c>
       <c r="B67" t="n">
-        <v>105553</v>
+        <v>99883</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8592,37 +8583,51 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707609</v>
+        <v>707548</v>
       </c>
       <c r="R67" t="n">
-        <v>6375033</v>
+        <v>6375091</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8656,7 +8661,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8670,7 +8675,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8688,7 +8693,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578754</v>
+        <v>122578796</v>
       </c>
       <c r="B68" t="n">
         <v>99883</v>
@@ -8721,16 +8726,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8742,10 +8738,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707554</v>
+        <v>707725</v>
       </c>
       <c r="R68" t="n">
-        <v>6374978</v>
+        <v>6374976</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8782,7 +8778,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8814,10 +8810,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578821</v>
+        <v>122578802</v>
       </c>
       <c r="B69" t="n">
-        <v>105553</v>
+        <v>98333</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8826,40 +8822,40 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8868,10 +8864,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707605</v>
+        <v>707697</v>
       </c>
       <c r="R69" t="n">
-        <v>6374970</v>
+        <v>6374969</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8906,11 +8902,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minsta antal + spridd.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8922,7 +8913,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8940,7 +8931,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578810</v>
+        <v>122578780</v>
       </c>
       <c r="B70" t="n">
         <v>99883</v>
@@ -8985,13 +8976,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707652</v>
+        <v>707626</v>
       </c>
       <c r="R70" t="n">
-        <v>6374986</v>
+        <v>6375120</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9025,7 +9016,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9057,10 +9048,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578779</v>
+        <v>122578760</v>
       </c>
       <c r="B71" t="n">
-        <v>99883</v>
+        <v>105553</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9073,27 +9064,36 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9102,13 +9102,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707597</v>
+        <v>707547</v>
       </c>
       <c r="R71" t="n">
-        <v>6375142</v>
+        <v>6375010</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>122578783</v>
       </c>
       <c r="B3" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>122578741</v>
       </c>
       <c r="B4" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578823</v>
+        <v>122578742</v>
       </c>
       <c r="B5" t="n">
-        <v>99883</v>
+        <v>105555</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,51 +1055,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707605</v>
+        <v>707638</v>
       </c>
       <c r="R5" t="n">
-        <v>6374970</v>
+        <v>6375036</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,7 +1119,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,7 +1133,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1165,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578776</v>
+        <v>122578816</v>
       </c>
       <c r="B6" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,16 +1184,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1219,13 +1196,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707584</v>
+        <v>707638</v>
       </c>
       <c r="R6" t="n">
-        <v>6375172</v>
+        <v>6374988</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1257,6 +1234,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridd, ganska rikligt.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1268,7 +1250,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1286,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578755</v>
+        <v>122578754</v>
       </c>
       <c r="B7" t="n">
-        <v>98333</v>
+        <v>99885</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,35 +1280,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1340,13 +1322,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707541</v>
+        <v>707554</v>
       </c>
       <c r="R7" t="n">
-        <v>6374993</v>
+        <v>6374978</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1412,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578749</v>
+        <v>122578807</v>
       </c>
       <c r="B8" t="n">
-        <v>105553</v>
+        <v>99885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,36 +1410,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1466,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707570</v>
+        <v>707678</v>
       </c>
       <c r="R8" t="n">
-        <v>6374984</v>
+        <v>6374990</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1506,7 +1479,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578762</v>
+        <v>122578779</v>
       </c>
       <c r="B9" t="n">
-        <v>105553</v>
+        <v>99885</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,36 +1527,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1592,13 +1556,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707548</v>
+        <v>707597</v>
       </c>
       <c r="R9" t="n">
-        <v>6375014</v>
+        <v>6375142</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1632,7 +1596,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Enstaka strå.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,7 +1610,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1664,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578800</v>
+        <v>122578786</v>
       </c>
       <c r="B10" t="n">
-        <v>105553</v>
+        <v>98335</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,40 +1640,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1718,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707697</v>
+        <v>707652</v>
       </c>
       <c r="R10" t="n">
-        <v>6374980</v>
+        <v>6375083</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1758,7 +1722,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Inget i tallplantager mot S och O.</t>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578810</v>
+        <v>122578767</v>
       </c>
       <c r="B11" t="n">
-        <v>99883</v>
+        <v>98379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1802,28 +1766,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1835,13 +1808,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707652</v>
+        <v>707513</v>
       </c>
       <c r="R11" t="n">
-        <v>6374986</v>
+        <v>6375053</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1873,11 +1846,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1889,7 +1857,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1907,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578756</v>
+        <v>122578824</v>
       </c>
       <c r="B12" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1942,7 +1910,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1961,13 +1929,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707541</v>
+        <v>707606</v>
       </c>
       <c r="R12" t="n">
-        <v>6374993</v>
+        <v>6374961</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1999,11 +1967,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2015,7 +1978,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2033,10 +1996,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578818</v>
+        <v>122578785</v>
       </c>
       <c r="B13" t="n">
-        <v>105553</v>
+        <v>105555</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2066,16 +2029,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2087,10 +2041,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707605</v>
+        <v>707648</v>
       </c>
       <c r="R13" t="n">
-        <v>6374982</v>
+        <v>6375072</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2127,7 +2081,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2141,7 +2095,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2159,10 +2113,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578751</v>
+        <v>122578777</v>
       </c>
       <c r="B14" t="n">
-        <v>98333</v>
+        <v>99885</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,35 +2125,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2213,13 +2167,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707569</v>
+        <v>707591</v>
       </c>
       <c r="R14" t="n">
-        <v>6374979</v>
+        <v>6375187</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2253,7 +2207,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>30 m S åker i N.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2267,7 +2221,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2285,10 +2239,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578819</v>
+        <v>122578759</v>
       </c>
       <c r="B15" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2320,7 +2274,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2339,13 +2293,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707605</v>
+        <v>707557</v>
       </c>
       <c r="R15" t="n">
-        <v>6374982</v>
+        <v>6375009</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2379,7 +2333,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2393,7 +2347,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2411,10 +2365,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578816</v>
+        <v>122578823</v>
       </c>
       <c r="B16" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2444,7 +2398,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2456,10 +2419,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707638</v>
+        <v>707605</v>
       </c>
       <c r="R16" t="n">
-        <v>6374988</v>
+        <v>6374970</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2496,7 +2459,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2510,7 +2473,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2528,10 +2491,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578744</v>
+        <v>122578775</v>
       </c>
       <c r="B17" t="n">
-        <v>105553</v>
+        <v>99885</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2544,26 +2507,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2573,7 +2536,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2582,10 +2545,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707626</v>
+        <v>707564</v>
       </c>
       <c r="R17" t="n">
-        <v>6375071</v>
+        <v>6375169</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2620,11 +2583,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Stensamling, grav? Nära.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2636,7 +2594,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2654,10 +2612,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578781</v>
+        <v>122578818</v>
       </c>
       <c r="B18" t="n">
-        <v>99883</v>
+        <v>105555</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2670,27 +2628,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2699,10 +2666,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707621</v>
+        <v>707605</v>
       </c>
       <c r="R18" t="n">
-        <v>6375108</v>
+        <v>6374982</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2739,7 +2706,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,7 +2720,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2771,10 +2738,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578805</v>
+        <v>122578773</v>
       </c>
       <c r="B19" t="n">
-        <v>98333</v>
+        <v>99885</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2783,35 +2750,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2825,13 +2792,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707697</v>
+        <v>707489</v>
       </c>
       <c r="R19" t="n">
-        <v>6374980</v>
+        <v>6375140</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2874,7 +2841,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2892,10 +2859,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578757</v>
+        <v>122578805</v>
       </c>
       <c r="B20" t="n">
-        <v>98333</v>
+        <v>98335</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2927,7 +2894,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2946,13 +2913,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707557</v>
+        <v>707697</v>
       </c>
       <c r="R20" t="n">
-        <v>6375009</v>
+        <v>6374980</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2982,11 +2949,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3018,10 +2980,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578824</v>
+        <v>122578747</v>
       </c>
       <c r="B21" t="n">
-        <v>99883</v>
+        <v>105555</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3034,48 +2996,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707606</v>
+        <v>707590</v>
       </c>
       <c r="R21" t="n">
-        <v>6374961</v>
+        <v>6375036</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3110,6 +3058,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3121,7 +3074,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3139,10 +3092,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578812</v>
+        <v>122578764</v>
       </c>
       <c r="B22" t="n">
-        <v>105553</v>
+        <v>99885</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3155,27 +3108,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3184,13 +3146,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707646</v>
+        <v>707538</v>
       </c>
       <c r="R22" t="n">
-        <v>6374967</v>
+        <v>6375024</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3224,7 +3186,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3256,10 +3218,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578817</v>
+        <v>122578758</v>
       </c>
       <c r="B23" t="n">
-        <v>99883</v>
+        <v>105555</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3272,36 +3234,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3310,13 +3272,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707624</v>
+        <v>707557</v>
       </c>
       <c r="R23" t="n">
-        <v>6374996</v>
+        <v>6375009</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3350,7 +3312,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3382,10 +3344,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578765</v>
+        <v>122578778</v>
       </c>
       <c r="B24" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3415,7 +3377,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3427,13 +3398,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707532</v>
+        <v>707599</v>
       </c>
       <c r="R24" t="n">
-        <v>6375035</v>
+        <v>6375165</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3467,7 +3438,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3481,7 +3452,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3499,10 +3470,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578775</v>
+        <v>122578770</v>
       </c>
       <c r="B25" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3534,7 +3505,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3553,13 +3524,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707564</v>
+        <v>707506</v>
       </c>
       <c r="R25" t="n">
-        <v>6375169</v>
+        <v>6375077</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3591,6 +3562,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3602,7 +3578,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3620,10 +3596,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578740</v>
+        <v>122578771</v>
       </c>
       <c r="B26" t="n">
-        <v>105553</v>
+        <v>98335</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3632,41 +3608,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707609</v>
+        <v>707490</v>
       </c>
       <c r="R26" t="n">
-        <v>6375033</v>
+        <v>6375090</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3700,7 +3690,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3714,7 +3704,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3732,10 +3722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578821</v>
+        <v>122578814</v>
       </c>
       <c r="B27" t="n">
-        <v>105553</v>
+        <v>98335</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3744,40 +3734,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3786,10 +3776,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707605</v>
+        <v>707638</v>
       </c>
       <c r="R27" t="n">
-        <v>6374970</v>
+        <v>6374988</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3824,11 +3814,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minsta antal + spridd.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3840,7 +3825,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3858,10 +3843,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578758</v>
+        <v>122578755</v>
       </c>
       <c r="B28" t="n">
-        <v>105553</v>
+        <v>98335</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3870,25 +3855,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3898,12 +3883,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3912,10 +3897,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707557</v>
+        <v>707541</v>
       </c>
       <c r="R28" t="n">
-        <v>6375009</v>
+        <v>6374993</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3984,10 +3969,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578811</v>
+        <v>122578812</v>
       </c>
       <c r="B29" t="n">
-        <v>98333</v>
+        <v>105555</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3996,40 +3981,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4038,10 +4014,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707652</v>
+        <v>707646</v>
       </c>
       <c r="R29" t="n">
-        <v>6374986</v>
+        <v>6374967</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4074,6 +4050,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4105,10 +4086,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578771</v>
+        <v>122578743</v>
       </c>
       <c r="B30" t="n">
-        <v>98333</v>
+        <v>99885</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4117,55 +4098,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707490</v>
+        <v>707638</v>
       </c>
       <c r="R30" t="n">
-        <v>6375090</v>
+        <v>6375036</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4199,7 +4166,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4213,7 +4180,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4231,10 +4198,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578786</v>
+        <v>122578762</v>
       </c>
       <c r="B31" t="n">
-        <v>98333</v>
+        <v>105555</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4243,40 +4210,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4285,13 +4252,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707652</v>
+        <v>707548</v>
       </c>
       <c r="R31" t="n">
-        <v>6375083</v>
+        <v>6375014</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4325,7 +4292,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4357,10 +4324,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578769</v>
+        <v>122578795</v>
       </c>
       <c r="B32" t="n">
-        <v>99883</v>
+        <v>105555</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4373,36 +4340,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4411,13 +4369,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707513</v>
+        <v>707725</v>
       </c>
       <c r="R32" t="n">
-        <v>6375053</v>
+        <v>6374976</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4451,7 +4409,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4465,7 +4423,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4483,10 +4441,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578807</v>
+        <v>122578796</v>
       </c>
       <c r="B33" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4528,10 +4486,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707678</v>
+        <v>707725</v>
       </c>
       <c r="R33" t="n">
-        <v>6374990</v>
+        <v>6374976</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4600,10 +4558,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578785</v>
+        <v>122578817</v>
       </c>
       <c r="B34" t="n">
-        <v>105553</v>
+        <v>99885</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4616,27 +4574,36 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4645,10 +4612,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707648</v>
+        <v>707624</v>
       </c>
       <c r="R34" t="n">
-        <v>6375072</v>
+        <v>6374996</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4685,7 +4652,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4717,10 +4684,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578809</v>
+        <v>122578797</v>
       </c>
       <c r="B35" t="n">
-        <v>105553</v>
+        <v>98335</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4729,31 +4696,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4762,10 +4738,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707652</v>
+        <v>707725</v>
       </c>
       <c r="R35" t="n">
-        <v>6374986</v>
+        <v>6374976</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4798,11 +4774,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4834,10 +4805,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578763</v>
+        <v>122578815</v>
       </c>
       <c r="B36" t="n">
-        <v>99883</v>
+        <v>105555</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4850,36 +4821,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4888,13 +4850,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707548</v>
+        <v>707638</v>
       </c>
       <c r="R36" t="n">
-        <v>6375014</v>
+        <v>6374988</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4928,7 +4890,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4960,10 +4922,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578770</v>
+        <v>122578782</v>
       </c>
       <c r="B37" t="n">
-        <v>99883</v>
+        <v>98335</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4972,35 +4934,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5014,13 +4976,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707506</v>
+        <v>707621</v>
       </c>
       <c r="R37" t="n">
-        <v>6375077</v>
+        <v>6375108</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5052,11 +5014,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2 ex.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5068,7 +5025,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5086,10 +5043,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578742</v>
+        <v>122578810</v>
       </c>
       <c r="B38" t="n">
-        <v>105553</v>
+        <v>99885</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5102,37 +5059,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707638</v>
+        <v>707652</v>
       </c>
       <c r="R38" t="n">
-        <v>6375036</v>
+        <v>6374986</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5166,7 +5128,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5198,10 +5160,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578801</v>
+        <v>122578748</v>
       </c>
       <c r="B39" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5232,21 +5194,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707697</v>
+        <v>707590</v>
       </c>
       <c r="R39" t="n">
-        <v>6374980</v>
+        <v>6375036</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5283,7 +5240,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5315,10 +5272,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578743</v>
+        <v>122578749</v>
       </c>
       <c r="B40" t="n">
-        <v>99883</v>
+        <v>105555</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5331,37 +5288,51 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707638</v>
+        <v>707570</v>
       </c>
       <c r="R40" t="n">
-        <v>6375036</v>
+        <v>6374984</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5395,7 +5366,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5427,10 +5398,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578825</v>
+        <v>122578776</v>
       </c>
       <c r="B41" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5462,7 +5433,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5481,13 +5452,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707611</v>
+        <v>707584</v>
       </c>
       <c r="R41" t="n">
-        <v>6374954</v>
+        <v>6375172</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5530,7 +5501,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5548,10 +5519,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578779</v>
+        <v>122578819</v>
       </c>
       <c r="B42" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5581,7 +5552,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5593,13 +5573,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707597</v>
+        <v>707605</v>
       </c>
       <c r="R42" t="n">
-        <v>6375142</v>
+        <v>6374982</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5633,7 +5613,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5647,7 +5627,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5665,10 +5645,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578806</v>
+        <v>122578825</v>
       </c>
       <c r="B43" t="n">
-        <v>105553</v>
+        <v>99885</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5681,27 +5661,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5710,10 +5699,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707678</v>
+        <v>707611</v>
       </c>
       <c r="R43" t="n">
-        <v>6374990</v>
+        <v>6374954</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5748,11 +5737,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5764,7 +5748,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5782,10 +5766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578815</v>
+        <v>122578804</v>
       </c>
       <c r="B44" t="n">
-        <v>105553</v>
+        <v>99885</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5798,27 +5782,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5827,10 +5811,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707638</v>
+        <v>707697</v>
       </c>
       <c r="R44" t="n">
-        <v>6374988</v>
+        <v>6374980</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5867,7 +5851,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5899,10 +5883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578773</v>
+        <v>122578753</v>
       </c>
       <c r="B45" t="n">
-        <v>99883</v>
+        <v>98335</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5911,35 +5895,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5953,13 +5937,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707489</v>
+        <v>707554</v>
       </c>
       <c r="R45" t="n">
-        <v>6375140</v>
+        <v>6374978</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5991,6 +5975,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6002,7 +5991,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6020,10 +6009,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578782</v>
+        <v>122578813</v>
       </c>
       <c r="B46" t="n">
-        <v>98333</v>
+        <v>99885</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6032,37 +6021,28 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6074,10 +6054,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707621</v>
+        <v>707646</v>
       </c>
       <c r="R46" t="n">
-        <v>6375108</v>
+        <v>6374967</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6110,6 +6090,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6141,10 +6126,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578747</v>
+        <v>122578809</v>
       </c>
       <c r="B47" t="n">
-        <v>105553</v>
+        <v>105555</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6175,16 +6160,21 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707590</v>
+        <v>707652</v>
       </c>
       <c r="R47" t="n">
-        <v>6375036</v>
+        <v>6374986</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6221,7 +6211,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6253,10 +6243,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578777</v>
+        <v>122578746</v>
       </c>
       <c r="B48" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6286,34 +6276,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707591</v>
+        <v>707626</v>
       </c>
       <c r="R48" t="n">
-        <v>6375187</v>
+        <v>6375071</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6347,7 +6323,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>30 m S åker i N.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6361,7 +6337,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6379,10 +6355,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578767</v>
+        <v>122578821</v>
       </c>
       <c r="B49" t="n">
-        <v>98377</v>
+        <v>105555</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6391,40 +6367,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219862</v>
+        <v>671</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6433,13 +6409,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707513</v>
+        <v>707605</v>
       </c>
       <c r="R49" t="n">
-        <v>6375053</v>
+        <v>6374970</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6471,6 +6447,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6482,7 +6463,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6500,10 +6481,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578795</v>
+        <v>122578763</v>
       </c>
       <c r="B50" t="n">
-        <v>105553</v>
+        <v>99885</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6516,27 +6497,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6545,13 +6535,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707725</v>
+        <v>707548</v>
       </c>
       <c r="R50" t="n">
-        <v>6374976</v>
+        <v>6375014</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6585,7 +6575,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6617,10 +6607,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578797</v>
+        <v>122578800</v>
       </c>
       <c r="B51" t="n">
-        <v>98333</v>
+        <v>105555</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6629,40 +6619,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6671,10 +6661,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707725</v>
+        <v>707697</v>
       </c>
       <c r="R51" t="n">
-        <v>6374976</v>
+        <v>6374980</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6707,6 +6697,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6738,10 +6733,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578808</v>
+        <v>122578740</v>
       </c>
       <c r="B52" t="n">
-        <v>98333</v>
+        <v>105555</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6750,55 +6745,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707678</v>
+        <v>707609</v>
       </c>
       <c r="R52" t="n">
-        <v>6374990</v>
+        <v>6375033</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6828,6 +6809,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6859,10 +6845,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578813</v>
+        <v>122578774</v>
       </c>
       <c r="B53" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6892,7 +6878,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6904,13 +6899,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707646</v>
+        <v>707528</v>
       </c>
       <c r="R53" t="n">
-        <v>6374967</v>
+        <v>6375154</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6942,11 +6937,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6958,7 +6948,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6979,7 +6969,7 @@
         <v>122578772</v>
       </c>
       <c r="B54" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7102,10 +7092,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578746</v>
+        <v>122578784</v>
       </c>
       <c r="B55" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7136,19 +7126,24 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707626</v>
+        <v>707648</v>
       </c>
       <c r="R55" t="n">
-        <v>6375071</v>
+        <v>6375072</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7182,7 +7177,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7214,10 +7209,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578814</v>
+        <v>122578756</v>
       </c>
       <c r="B56" t="n">
-        <v>98333</v>
+        <v>99885</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7226,35 +7221,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7268,13 +7263,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707638</v>
+        <v>707541</v>
       </c>
       <c r="R56" t="n">
-        <v>6374988</v>
+        <v>6374993</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7304,6 +7299,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7335,10 +7335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578750</v>
+        <v>122578802</v>
       </c>
       <c r="B57" t="n">
-        <v>98377</v>
+        <v>98335</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7351,26 +7351,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7389,13 +7389,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707569</v>
+        <v>707697</v>
       </c>
       <c r="R57" t="n">
-        <v>6374979</v>
+        <v>6374969</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7425,11 +7425,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7461,10 +7456,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578753</v>
+        <v>122578744</v>
       </c>
       <c r="B58" t="n">
-        <v>98333</v>
+        <v>105555</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7473,40 +7468,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7515,13 +7510,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707554</v>
+        <v>707626</v>
       </c>
       <c r="R58" t="n">
-        <v>6374978</v>
+        <v>6375071</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7555,7 +7550,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7587,10 +7582,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578774</v>
+        <v>122578760</v>
       </c>
       <c r="B59" t="n">
-        <v>99883</v>
+        <v>105555</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7603,36 +7598,36 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7641,13 +7636,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707528</v>
+        <v>707547</v>
       </c>
       <c r="R59" t="n">
-        <v>6375154</v>
+        <v>6375010</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7679,6 +7674,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7708,10 +7708,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578752</v>
+        <v>122578765</v>
       </c>
       <c r="B60" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7741,16 +7741,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7762,13 +7753,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707569</v>
+        <v>707532</v>
       </c>
       <c r="R60" t="n">
-        <v>6374979</v>
+        <v>6375035</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7802,7 +7793,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7834,10 +7825,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578778</v>
+        <v>122578811</v>
       </c>
       <c r="B61" t="n">
-        <v>99883</v>
+        <v>98335</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7846,35 +7837,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7888,13 +7879,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707599</v>
+        <v>707652</v>
       </c>
       <c r="R61" t="n">
-        <v>6375165</v>
+        <v>6374986</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7926,11 +7917,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Barrblandskog mot åker i N.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7942,7 +7928,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7960,10 +7946,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578748</v>
+        <v>122578769</v>
       </c>
       <c r="B62" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7993,20 +7979,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707590</v>
+        <v>707513</v>
       </c>
       <c r="R62" t="n">
-        <v>6375036</v>
+        <v>6375053</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8072,10 +8072,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578754</v>
+        <v>122578752</v>
       </c>
       <c r="B63" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8126,13 +8126,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707554</v>
+        <v>707569</v>
       </c>
       <c r="R63" t="n">
-        <v>6374978</v>
+        <v>6374979</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8198,10 +8198,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578784</v>
+        <v>122578766</v>
       </c>
       <c r="B64" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8231,7 +8231,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8243,13 +8252,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707648</v>
+        <v>707548</v>
       </c>
       <c r="R64" t="n">
-        <v>6375072</v>
+        <v>6375091</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8283,7 +8292,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8297,7 +8306,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8315,10 +8324,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578759</v>
+        <v>122578751</v>
       </c>
       <c r="B65" t="n">
-        <v>99883</v>
+        <v>98335</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8327,35 +8336,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8369,10 +8378,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707557</v>
+        <v>707569</v>
       </c>
       <c r="R65" t="n">
-        <v>6375009</v>
+        <v>6374979</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -8441,10 +8450,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578764</v>
+        <v>122578757</v>
       </c>
       <c r="B66" t="n">
-        <v>99883</v>
+        <v>98335</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8453,35 +8462,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8495,13 +8504,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707538</v>
+        <v>707557</v>
       </c>
       <c r="R66" t="n">
-        <v>6375024</v>
+        <v>6375009</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8567,10 +8576,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578766</v>
+        <v>122578808</v>
       </c>
       <c r="B67" t="n">
-        <v>99883</v>
+        <v>98335</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8579,35 +8588,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8621,13 +8630,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707548</v>
+        <v>707678</v>
       </c>
       <c r="R67" t="n">
-        <v>6375091</v>
+        <v>6374990</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8659,11 +8668,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8675,7 +8679,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8693,10 +8697,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578796</v>
+        <v>122578780</v>
       </c>
       <c r="B68" t="n">
-        <v>99883</v>
+        <v>99885</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8738,13 +8742,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707725</v>
+        <v>707626</v>
       </c>
       <c r="R68" t="n">
-        <v>6374976</v>
+        <v>6375120</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8778,7 +8782,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8810,10 +8814,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578802</v>
+        <v>122578781</v>
       </c>
       <c r="B69" t="n">
-        <v>98333</v>
+        <v>99885</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8822,37 +8826,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8864,10 +8859,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707697</v>
+        <v>707621</v>
       </c>
       <c r="R69" t="n">
-        <v>6374969</v>
+        <v>6375108</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8900,6 +8895,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8931,10 +8931,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578780</v>
+        <v>122578806</v>
       </c>
       <c r="B70" t="n">
-        <v>99883</v>
+        <v>105555</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8947,27 +8947,27 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8976,13 +8976,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707626</v>
+        <v>707678</v>
       </c>
       <c r="R70" t="n">
-        <v>6375120</v>
+        <v>6374990</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9048,10 +9048,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578760</v>
+        <v>122578750</v>
       </c>
       <c r="B71" t="n">
-        <v>105553</v>
+        <v>98379</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9060,40 +9060,40 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>671</v>
+        <v>219862</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9102,13 +9102,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707547</v>
+        <v>707569</v>
       </c>
       <c r="R71" t="n">
-        <v>6375010</v>
+        <v>6374979</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -6966,7 +6966,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578772</v>
+        <v>122578756</v>
       </c>
       <c r="B54" t="n">
         <v>99885</v>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7020,13 +7020,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707506</v>
+        <v>707541</v>
       </c>
       <c r="R54" t="n">
-        <v>6375110</v>
+        <v>6374993</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7092,7 +7092,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578784</v>
+        <v>122578772</v>
       </c>
       <c r="B55" t="n">
         <v>99885</v>
@@ -7125,7 +7125,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7137,13 +7146,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707648</v>
+        <v>707506</v>
       </c>
       <c r="R55" t="n">
-        <v>6375072</v>
+        <v>6375110</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7177,7 +7186,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7191,7 +7200,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7209,7 +7218,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578756</v>
+        <v>122578784</v>
       </c>
       <c r="B56" t="n">
         <v>99885</v>
@@ -7242,16 +7251,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7263,13 +7263,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707541</v>
+        <v>707648</v>
       </c>
       <c r="R56" t="n">
-        <v>6374993</v>
+        <v>6375072</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -6966,7 +6966,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578756</v>
+        <v>122578772</v>
       </c>
       <c r="B54" t="n">
         <v>99885</v>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7020,13 +7020,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707541</v>
+        <v>707506</v>
       </c>
       <c r="R54" t="n">
-        <v>6374993</v>
+        <v>6375110</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7092,7 +7092,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578772</v>
+        <v>122578784</v>
       </c>
       <c r="B55" t="n">
         <v>99885</v>
@@ -7125,16 +7125,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7146,13 +7137,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707506</v>
+        <v>707648</v>
       </c>
       <c r="R55" t="n">
-        <v>6375110</v>
+        <v>6375072</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7186,7 +7177,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7200,7 +7191,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7218,7 +7209,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578784</v>
+        <v>122578756</v>
       </c>
       <c r="B56" t="n">
         <v>99885</v>
@@ -7251,7 +7242,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7263,13 +7263,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707648</v>
+        <v>707541</v>
       </c>
       <c r="R56" t="n">
-        <v>6375072</v>
+        <v>6374993</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -5883,10 +5883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578753</v>
+        <v>122578813</v>
       </c>
       <c r="B45" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5895,37 +5895,28 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5937,10 +5928,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707554</v>
+        <v>707646</v>
       </c>
       <c r="R45" t="n">
-        <v>6374978</v>
+        <v>6374967</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5977,7 +5968,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6009,10 +6000,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578813</v>
+        <v>122578809</v>
       </c>
       <c r="B46" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6025,27 +6016,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6054,10 +6045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707646</v>
+        <v>707652</v>
       </c>
       <c r="R46" t="n">
-        <v>6374967</v>
+        <v>6374986</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6094,7 +6085,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6126,10 +6117,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578809</v>
+        <v>122578746</v>
       </c>
       <c r="B47" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6142,42 +6133,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707652</v>
+        <v>707626</v>
       </c>
       <c r="R47" t="n">
-        <v>6374986</v>
+        <v>6375071</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6211,7 +6197,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6243,10 +6229,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578746</v>
+        <v>122578821</v>
       </c>
       <c r="B48" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6259,37 +6245,51 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707626</v>
+        <v>707605</v>
       </c>
       <c r="R48" t="n">
-        <v>6375071</v>
+        <v>6374970</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6355,10 +6355,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578821</v>
+        <v>122578763</v>
       </c>
       <c r="B49" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6371,26 +6371,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6409,13 +6409,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707605</v>
+        <v>707548</v>
       </c>
       <c r="R49" t="n">
-        <v>6374970</v>
+        <v>6375014</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6481,10 +6481,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578763</v>
+        <v>122578753</v>
       </c>
       <c r="B50" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6493,35 +6493,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6535,13 +6535,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707548</v>
+        <v>707554</v>
       </c>
       <c r="R50" t="n">
-        <v>6375014</v>
+        <v>6374978</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578783</v>
+        <v>122578754</v>
       </c>
       <c r="B3" t="n">
         <v>99885</v>
@@ -843,7 +843,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -855,13 +864,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707633</v>
+        <v>707554</v>
       </c>
       <c r="R3" t="n">
-        <v>6375094</v>
+        <v>6374978</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +904,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,7 +936,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578741</v>
+        <v>122578810</v>
       </c>
       <c r="B4" t="n">
         <v>99885</v>
@@ -961,19 +970,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707609</v>
+        <v>707652</v>
       </c>
       <c r="R4" t="n">
-        <v>6375033</v>
+        <v>6374986</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,7 +1021,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1053,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578742</v>
+        <v>122578809</v>
       </c>
       <c r="B5" t="n">
         <v>105555</v>
@@ -1073,19 +1087,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707638</v>
+        <v>707652</v>
       </c>
       <c r="R5" t="n">
-        <v>6375036</v>
+        <v>6374986</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1170,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578816</v>
+        <v>122578777</v>
       </c>
       <c r="B6" t="n">
         <v>99885</v>
@@ -1184,7 +1203,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1196,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707638</v>
+        <v>707591</v>
       </c>
       <c r="R6" t="n">
-        <v>6374988</v>
+        <v>6375187</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,7 +1264,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>30 m S åker i N.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1278,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1268,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578754</v>
+        <v>122578795</v>
       </c>
       <c r="B7" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,36 +1312,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707554</v>
+        <v>707725</v>
       </c>
       <c r="R7" t="n">
-        <v>6374978</v>
+        <v>6374976</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1362,7 +1381,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,7 +1413,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578807</v>
+        <v>122578817</v>
       </c>
       <c r="B8" t="n">
         <v>99885</v>
@@ -1427,7 +1446,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1439,10 +1467,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707678</v>
+        <v>707624</v>
       </c>
       <c r="R8" t="n">
-        <v>6374990</v>
+        <v>6374996</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1479,7 +1507,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,7 +1539,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578779</v>
+        <v>122578804</v>
       </c>
       <c r="B9" t="n">
         <v>99885</v>
@@ -1556,13 +1584,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707597</v>
+        <v>707697</v>
       </c>
       <c r="R9" t="n">
-        <v>6375142</v>
+        <v>6374980</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1596,7 +1624,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,7 +1638,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1628,10 +1656,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578786</v>
+        <v>122578823</v>
       </c>
       <c r="B10" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,35 +1668,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1682,10 +1710,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707652</v>
+        <v>707605</v>
       </c>
       <c r="R10" t="n">
-        <v>6375083</v>
+        <v>6374970</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1722,7 +1750,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,7 +1764,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1754,10 +1782,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578767</v>
+        <v>122578764</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>99885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1766,35 +1794,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1808,13 +1836,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707513</v>
+        <v>707538</v>
       </c>
       <c r="R11" t="n">
-        <v>6375053</v>
+        <v>6375024</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1846,6 +1874,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1857,7 +1890,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1875,7 +1908,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578824</v>
+        <v>122578778</v>
       </c>
       <c r="B12" t="n">
         <v>99885</v>
@@ -1910,7 +1943,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1929,13 +1962,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707606</v>
+        <v>707599</v>
       </c>
       <c r="R12" t="n">
-        <v>6374961</v>
+        <v>6375165</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1967,6 +2000,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Barrblandskog mot åker i N.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1978,7 +2016,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1996,7 +2034,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578785</v>
+        <v>122578812</v>
       </c>
       <c r="B13" t="n">
         <v>105555</v>
@@ -2041,10 +2079,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707648</v>
+        <v>707646</v>
       </c>
       <c r="R13" t="n">
-        <v>6375072</v>
+        <v>6374967</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2081,7 +2119,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2113,10 +2151,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578777</v>
+        <v>122578742</v>
       </c>
       <c r="B14" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2129,51 +2167,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707591</v>
+        <v>707638</v>
       </c>
       <c r="R14" t="n">
-        <v>6375187</v>
+        <v>6375036</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2207,7 +2231,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>30 m S åker i N.</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,7 +2245,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2239,10 +2263,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578759</v>
+        <v>122578797</v>
       </c>
       <c r="B15" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,35 +2275,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2293,13 +2317,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707557</v>
+        <v>707725</v>
       </c>
       <c r="R15" t="n">
-        <v>6375009</v>
+        <v>6374976</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2329,11 +2353,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,7 +2384,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578823</v>
+        <v>122578759</v>
       </c>
       <c r="B16" t="n">
         <v>99885</v>
@@ -2400,7 +2419,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2419,13 +2438,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707605</v>
+        <v>707557</v>
       </c>
       <c r="R16" t="n">
-        <v>6374970</v>
+        <v>6375009</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2459,7 +2478,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2473,7 +2492,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2491,7 +2510,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578775</v>
+        <v>122578766</v>
       </c>
       <c r="B17" t="n">
         <v>99885</v>
@@ -2526,12 +2545,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2545,13 +2564,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707564</v>
+        <v>707548</v>
       </c>
       <c r="R17" t="n">
-        <v>6375169</v>
+        <v>6375091</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2583,6 +2602,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2594,7 +2618,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2612,10 +2636,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578818</v>
+        <v>122578771</v>
       </c>
       <c r="B18" t="n">
-        <v>105555</v>
+        <v>98335</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2624,40 +2648,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2666,13 +2690,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707605</v>
+        <v>707490</v>
       </c>
       <c r="R18" t="n">
-        <v>6374982</v>
+        <v>6375090</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2706,7 +2730,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2720,7 +2744,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2738,10 +2762,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578773</v>
+        <v>122578782</v>
       </c>
       <c r="B19" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2750,35 +2774,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2792,13 +2816,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707489</v>
+        <v>707621</v>
       </c>
       <c r="R19" t="n">
-        <v>6375140</v>
+        <v>6375108</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2841,7 +2865,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2859,10 +2883,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578805</v>
+        <v>122578769</v>
       </c>
       <c r="B20" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2871,35 +2895,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2913,13 +2937,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707697</v>
+        <v>707513</v>
       </c>
       <c r="R20" t="n">
-        <v>6374980</v>
+        <v>6375053</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2951,6 +2975,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3 ex.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2962,7 +2991,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2980,10 +3009,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578747</v>
+        <v>122578825</v>
       </c>
       <c r="B21" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2996,34 +3025,48 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707590</v>
+        <v>707611</v>
       </c>
       <c r="R21" t="n">
-        <v>6375036</v>
+        <v>6374954</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3058,11 +3101,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3074,7 +3112,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3092,10 +3130,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578764</v>
+        <v>122578786</v>
       </c>
       <c r="B22" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3104,35 +3142,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3146,13 +3184,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707538</v>
+        <v>707652</v>
       </c>
       <c r="R22" t="n">
-        <v>6375024</v>
+        <v>6375083</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3186,7 +3224,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3344,10 +3382,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578778</v>
+        <v>122578808</v>
       </c>
       <c r="B24" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3356,35 +3394,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3398,13 +3436,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707599</v>
+        <v>707678</v>
       </c>
       <c r="R24" t="n">
-        <v>6375165</v>
+        <v>6374990</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3436,11 +3474,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Barrblandskog mot åker i N.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3452,7 +3485,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3470,10 +3503,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578770</v>
+        <v>122578762</v>
       </c>
       <c r="B25" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3486,36 +3519,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3524,13 +3557,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707506</v>
+        <v>707548</v>
       </c>
       <c r="R25" t="n">
-        <v>6375077</v>
+        <v>6375014</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3564,7 +3597,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3578,7 +3611,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3596,10 +3629,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578771</v>
+        <v>122578806</v>
       </c>
       <c r="B26" t="n">
-        <v>98335</v>
+        <v>105555</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3608,40 +3641,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3650,13 +3674,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707490</v>
+        <v>707678</v>
       </c>
       <c r="R26" t="n">
-        <v>6375090</v>
+        <v>6374990</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3690,7 +3714,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3704,7 +3728,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3722,10 +3746,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578814</v>
+        <v>122578743</v>
       </c>
       <c r="B27" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3734,42 +3758,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
@@ -3779,10 +3789,10 @@
         <v>707638</v>
       </c>
       <c r="R27" t="n">
-        <v>6374988</v>
+        <v>6375036</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3812,6 +3822,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3843,10 +3858,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578755</v>
+        <v>122578824</v>
       </c>
       <c r="B28" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3855,35 +3870,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3897,13 +3912,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707541</v>
+        <v>707606</v>
       </c>
       <c r="R28" t="n">
-        <v>6374993</v>
+        <v>6374961</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3935,11 +3950,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3951,7 +3961,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3969,7 +3979,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578812</v>
+        <v>122578760</v>
       </c>
       <c r="B29" t="n">
         <v>105555</v>
@@ -4002,7 +4012,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4014,10 +4033,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707646</v>
+        <v>707547</v>
       </c>
       <c r="R29" t="n">
-        <v>6374967</v>
+        <v>6375010</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4054,7 +4073,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4086,10 +4105,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578743</v>
+        <v>122578814</v>
       </c>
       <c r="B30" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4098,28 +4117,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
@@ -4129,10 +4162,10 @@
         <v>707638</v>
       </c>
       <c r="R30" t="n">
-        <v>6375036</v>
+        <v>6374988</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4162,11 +4195,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4198,10 +4226,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578762</v>
+        <v>122578805</v>
       </c>
       <c r="B31" t="n">
-        <v>105555</v>
+        <v>98335</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4210,40 +4238,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4252,13 +4280,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707548</v>
+        <v>707697</v>
       </c>
       <c r="R31" t="n">
-        <v>6375014</v>
+        <v>6374980</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4288,11 +4316,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4324,10 +4347,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578795</v>
+        <v>122578773</v>
       </c>
       <c r="B32" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4340,27 +4363,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4369,13 +4401,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707725</v>
+        <v>707489</v>
       </c>
       <c r="R32" t="n">
-        <v>6374976</v>
+        <v>6375140</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4407,11 +4439,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4423,7 +4450,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4441,10 +4468,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578796</v>
+        <v>122578755</v>
       </c>
       <c r="B33" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4453,28 +4480,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4486,13 +4522,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707725</v>
+        <v>707541</v>
       </c>
       <c r="R33" t="n">
-        <v>6374976</v>
+        <v>6374993</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4526,7 +4562,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4558,10 +4594,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578817</v>
+        <v>122578785</v>
       </c>
       <c r="B34" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4574,36 +4610,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4612,10 +4639,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707624</v>
+        <v>707648</v>
       </c>
       <c r="R34" t="n">
-        <v>6374996</v>
+        <v>6375072</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4652,7 +4679,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4684,10 +4711,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578797</v>
+        <v>122578803</v>
       </c>
       <c r="B35" t="n">
-        <v>98335</v>
+        <v>105555</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4696,40 +4723,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4738,10 +4756,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707725</v>
+        <v>707697</v>
       </c>
       <c r="R35" t="n">
-        <v>6374976</v>
+        <v>6374980</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4774,6 +4792,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4805,10 +4828,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578815</v>
+        <v>122578784</v>
       </c>
       <c r="B36" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4821,27 +4844,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4850,10 +4873,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707638</v>
+        <v>707648</v>
       </c>
       <c r="R36" t="n">
-        <v>6374988</v>
+        <v>6375072</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4890,7 +4913,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4922,10 +4945,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578782</v>
+        <v>122578796</v>
       </c>
       <c r="B37" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4934,37 +4957,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4976,10 +4990,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707621</v>
+        <v>707725</v>
       </c>
       <c r="R37" t="n">
-        <v>6375108</v>
+        <v>6374976</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5012,6 +5026,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5043,10 +5062,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578810</v>
+        <v>122578821</v>
       </c>
       <c r="B38" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5059,27 +5078,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5088,10 +5116,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707652</v>
+        <v>707605</v>
       </c>
       <c r="R38" t="n">
-        <v>6374986</v>
+        <v>6374970</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5128,7 +5156,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5142,7 +5170,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5160,10 +5188,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578748</v>
+        <v>122578747</v>
       </c>
       <c r="B39" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5176,21 +5204,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5240,7 +5268,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5272,10 +5300,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578749</v>
+        <v>122578767</v>
       </c>
       <c r="B40" t="n">
-        <v>105555</v>
+        <v>98379</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5284,40 +5312,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>671</v>
+        <v>219862</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5326,13 +5354,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707570</v>
+        <v>707513</v>
       </c>
       <c r="R40" t="n">
-        <v>6374984</v>
+        <v>6375053</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5364,11 +5392,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5380,7 +5403,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5398,7 +5421,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578776</v>
+        <v>122578748</v>
       </c>
       <c r="B41" t="n">
         <v>99885</v>
@@ -5431,34 +5454,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707584</v>
+        <v>707590</v>
       </c>
       <c r="R41" t="n">
-        <v>6375172</v>
+        <v>6375036</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5490,6 +5499,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5501,7 +5515,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5519,7 +5533,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578819</v>
+        <v>122578783</v>
       </c>
       <c r="B42" t="n">
         <v>99885</v>
@@ -5552,16 +5566,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5573,13 +5578,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707605</v>
+        <v>707633</v>
       </c>
       <c r="R42" t="n">
-        <v>6374982</v>
+        <v>6375094</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5613,7 +5618,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5627,7 +5632,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5645,7 +5650,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578825</v>
+        <v>122578772</v>
       </c>
       <c r="B43" t="n">
         <v>99885</v>
@@ -5680,7 +5685,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5699,13 +5704,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707611</v>
+        <v>707506</v>
       </c>
       <c r="R43" t="n">
-        <v>6374954</v>
+        <v>6375110</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5737,6 +5742,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5748,7 +5758,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5766,10 +5776,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578804</v>
+        <v>122578815</v>
       </c>
       <c r="B44" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5782,27 +5792,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5811,10 +5821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707697</v>
+        <v>707638</v>
       </c>
       <c r="R44" t="n">
-        <v>6374980</v>
+        <v>6374988</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5851,7 +5861,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5883,7 +5893,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578813</v>
+        <v>122578779</v>
       </c>
       <c r="B45" t="n">
         <v>99885</v>
@@ -5928,13 +5938,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707646</v>
+        <v>707597</v>
       </c>
       <c r="R45" t="n">
-        <v>6374967</v>
+        <v>6375142</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5968,7 +5978,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Enstaka strå.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5982,7 +5992,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6000,10 +6010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578809</v>
+        <v>122578770</v>
       </c>
       <c r="B46" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6016,27 +6026,36 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6045,13 +6064,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707652</v>
+        <v>707506</v>
       </c>
       <c r="R46" t="n">
-        <v>6374986</v>
+        <v>6375077</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6085,7 +6104,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6099,7 +6118,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6117,10 +6136,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578746</v>
+        <v>122578757</v>
       </c>
       <c r="B47" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6129,41 +6148,55 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707626</v>
+        <v>707557</v>
       </c>
       <c r="R47" t="n">
-        <v>6375071</v>
+        <v>6375009</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6197,7 +6230,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6229,10 +6262,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578821</v>
+        <v>122578763</v>
       </c>
       <c r="B48" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6245,26 +6278,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6274,7 +6307,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6283,13 +6316,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707605</v>
+        <v>707548</v>
       </c>
       <c r="R48" t="n">
-        <v>6374970</v>
+        <v>6375014</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6323,7 +6356,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6337,7 +6370,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6355,7 +6388,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578763</v>
+        <v>122578752</v>
       </c>
       <c r="B49" t="n">
         <v>99885</v>
@@ -6390,7 +6423,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6409,10 +6442,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707548</v>
+        <v>707569</v>
       </c>
       <c r="R49" t="n">
-        <v>6375014</v>
+        <v>6374979</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6481,7 +6514,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578753</v>
+        <v>122578811</v>
       </c>
       <c r="B50" t="n">
         <v>98335</v>
@@ -6516,7 +6549,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6535,10 +6568,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707554</v>
+        <v>707652</v>
       </c>
       <c r="R50" t="n">
-        <v>6374978</v>
+        <v>6374986</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6571,11 +6604,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6607,10 +6635,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578800</v>
+        <v>122578750</v>
       </c>
       <c r="B51" t="n">
-        <v>105555</v>
+        <v>98379</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6619,40 +6647,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>671</v>
+        <v>219862</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6661,13 +6689,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707697</v>
+        <v>707569</v>
       </c>
       <c r="R51" t="n">
-        <v>6374980</v>
+        <v>6374979</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6701,7 +6729,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Inget i tallplantager mot S och O.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6733,10 +6761,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578740</v>
+        <v>122578802</v>
       </c>
       <c r="B52" t="n">
-        <v>105555</v>
+        <v>98335</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6745,41 +6773,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707609</v>
+        <v>707697</v>
       </c>
       <c r="R52" t="n">
-        <v>6375033</v>
+        <v>6374969</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6809,11 +6851,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6845,7 +6882,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578774</v>
+        <v>122578776</v>
       </c>
       <c r="B53" t="n">
         <v>99885</v>
@@ -6880,7 +6917,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6899,13 +6936,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707528</v>
+        <v>707584</v>
       </c>
       <c r="R53" t="n">
-        <v>6375154</v>
+        <v>6375172</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6948,7 +6985,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6966,10 +7003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578772</v>
+        <v>122578818</v>
       </c>
       <c r="B54" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6982,36 +7019,36 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7020,13 +7057,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707506</v>
+        <v>707605</v>
       </c>
       <c r="R54" t="n">
-        <v>6375110</v>
+        <v>6374982</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7060,7 +7097,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7074,7 +7111,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7092,7 +7129,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578784</v>
+        <v>122578775</v>
       </c>
       <c r="B55" t="n">
         <v>99885</v>
@@ -7125,7 +7162,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7137,13 +7183,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707648</v>
+        <v>707564</v>
       </c>
       <c r="R55" t="n">
-        <v>6375072</v>
+        <v>6375169</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7175,11 +7221,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7191,7 +7232,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7209,10 +7250,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578756</v>
+        <v>122578744</v>
       </c>
       <c r="B56" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7225,26 +7266,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7254,7 +7295,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7263,13 +7304,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707541</v>
+        <v>707626</v>
       </c>
       <c r="R56" t="n">
-        <v>6374993</v>
+        <v>6375071</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7303,7 +7344,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7335,10 +7376,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578802</v>
+        <v>122578756</v>
       </c>
       <c r="B57" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7347,35 +7388,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7389,13 +7430,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707697</v>
+        <v>707541</v>
       </c>
       <c r="R57" t="n">
-        <v>6374969</v>
+        <v>6374993</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7425,6 +7466,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7456,10 +7502,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578744</v>
+        <v>122578746</v>
       </c>
       <c r="B58" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7472,38 +7518,24 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
@@ -7582,10 +7614,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578760</v>
+        <v>122578781</v>
       </c>
       <c r="B59" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7598,36 +7630,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7636,10 +7659,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707547</v>
+        <v>707621</v>
       </c>
       <c r="R59" t="n">
-        <v>6375010</v>
+        <v>6375108</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7676,7 +7699,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7708,7 +7731,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578765</v>
+        <v>122578819</v>
       </c>
       <c r="B60" t="n">
         <v>99885</v>
@@ -7741,7 +7764,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7753,13 +7785,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707532</v>
+        <v>707605</v>
       </c>
       <c r="R60" t="n">
-        <v>6375035</v>
+        <v>6374982</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7793,7 +7825,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7807,7 +7839,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7825,10 +7857,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578811</v>
+        <v>122578780</v>
       </c>
       <c r="B61" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7837,37 +7869,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7879,13 +7902,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707652</v>
+        <v>707626</v>
       </c>
       <c r="R61" t="n">
-        <v>6374986</v>
+        <v>6375120</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7915,6 +7938,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7946,7 +7974,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578769</v>
+        <v>122578765</v>
       </c>
       <c r="B62" t="n">
         <v>99885</v>
@@ -7979,16 +8007,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8000,13 +8019,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707513</v>
+        <v>707532</v>
       </c>
       <c r="R62" t="n">
-        <v>6375053</v>
+        <v>6375035</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8040,7 +8059,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8054,7 +8073,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8072,7 +8091,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578752</v>
+        <v>122578741</v>
       </c>
       <c r="B63" t="n">
         <v>99885</v>
@@ -8105,34 +8124,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707569</v>
+        <v>707609</v>
       </c>
       <c r="R63" t="n">
-        <v>6374979</v>
+        <v>6375033</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8166,7 +8171,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8198,7 +8203,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578766</v>
+        <v>122578816</v>
       </c>
       <c r="B64" t="n">
         <v>99885</v>
@@ -8231,16 +8236,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8252,13 +8248,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707548</v>
+        <v>707638</v>
       </c>
       <c r="R64" t="n">
-        <v>6375091</v>
+        <v>6374988</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8292,7 +8288,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8306,7 +8302,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8450,10 +8446,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578757</v>
+        <v>122578740</v>
       </c>
       <c r="B66" t="n">
-        <v>98335</v>
+        <v>105555</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8462,55 +8458,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707557</v>
+        <v>707609</v>
       </c>
       <c r="R66" t="n">
-        <v>6375009</v>
+        <v>6375033</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8544,7 +8526,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8576,10 +8558,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578808</v>
+        <v>122578807</v>
       </c>
       <c r="B67" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8588,37 +8570,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8666,6 +8639,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8697,10 +8675,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578780</v>
+        <v>122578753</v>
       </c>
       <c r="B68" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8709,28 +8687,37 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8742,13 +8729,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707626</v>
+        <v>707554</v>
       </c>
       <c r="R68" t="n">
-        <v>6375120</v>
+        <v>6374978</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8782,7 +8769,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8814,10 +8801,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578781</v>
+        <v>122578749</v>
       </c>
       <c r="B69" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8830,27 +8817,36 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8859,10 +8855,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707621</v>
+        <v>707570</v>
       </c>
       <c r="R69" t="n">
-        <v>6375108</v>
+        <v>6374984</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8899,7 +8895,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8931,10 +8927,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578806</v>
+        <v>122578774</v>
       </c>
       <c r="B70" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8947,27 +8943,36 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8976,13 +8981,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707678</v>
+        <v>707528</v>
       </c>
       <c r="R70" t="n">
-        <v>6374990</v>
+        <v>6375154</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9014,11 +9019,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9048,10 +9048,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578750</v>
+        <v>122578813</v>
       </c>
       <c r="B71" t="n">
-        <v>98379</v>
+        <v>99885</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9060,37 +9060,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -9102,13 +9093,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707569</v>
+        <v>707646</v>
       </c>
       <c r="R71" t="n">
-        <v>6374979</v>
+        <v>6374967</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9142,7 +9133,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578759</v>
+        <v>122578771</v>
       </c>
       <c r="B16" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,30 +2396,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2438,13 +2438,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707557</v>
+        <v>707490</v>
       </c>
       <c r="R16" t="n">
-        <v>6375009</v>
+        <v>6375090</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2510,10 +2510,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578766</v>
+        <v>122578782</v>
       </c>
       <c r="B17" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2522,35 +2522,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2564,13 +2564,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707548</v>
+        <v>707621</v>
       </c>
       <c r="R17" t="n">
-        <v>6375091</v>
+        <v>6375108</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2602,11 +2602,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2618,7 +2613,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2636,10 +2631,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578771</v>
+        <v>122578759</v>
       </c>
       <c r="B18" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2648,30 +2643,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2690,13 +2685,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707490</v>
+        <v>707557</v>
       </c>
       <c r="R18" t="n">
-        <v>6375090</v>
+        <v>6375009</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2730,7 +2725,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2744,7 +2739,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2762,10 +2757,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578782</v>
+        <v>122578766</v>
       </c>
       <c r="B19" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2774,35 +2769,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2816,13 +2811,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707621</v>
+        <v>707548</v>
       </c>
       <c r="R19" t="n">
-        <v>6375108</v>
+        <v>6375091</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2854,6 +2849,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578758</v>
+        <v>122578808</v>
       </c>
       <c r="B23" t="n">
-        <v>105555</v>
+        <v>98335</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3268,40 +3268,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3310,13 +3310,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707557</v>
+        <v>707678</v>
       </c>
       <c r="R23" t="n">
-        <v>6375009</v>
+        <v>6374990</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3346,11 +3346,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3382,10 +3377,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578808</v>
+        <v>122578758</v>
       </c>
       <c r="B24" t="n">
-        <v>98335</v>
+        <v>105555</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3394,40 +3389,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3436,13 +3431,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707678</v>
+        <v>707557</v>
       </c>
       <c r="R24" t="n">
-        <v>6374990</v>
+        <v>6375009</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3472,6 +3467,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3503,7 +3503,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578762</v>
+        <v>122578806</v>
       </c>
       <c r="B25" t="n">
         <v>105555</v>
@@ -3536,16 +3536,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3557,13 +3548,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707548</v>
+        <v>707678</v>
       </c>
       <c r="R25" t="n">
-        <v>6375014</v>
+        <v>6374990</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3597,7 +3588,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3629,10 +3620,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578806</v>
+        <v>122578743</v>
       </c>
       <c r="B26" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3645,42 +3636,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707678</v>
+        <v>707638</v>
       </c>
       <c r="R26" t="n">
-        <v>6374990</v>
+        <v>6375036</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3714,7 +3700,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3746,10 +3732,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578743</v>
+        <v>122578762</v>
       </c>
       <c r="B27" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3762,37 +3748,51 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707638</v>
+        <v>707548</v>
       </c>
       <c r="R27" t="n">
-        <v>6375036</v>
+        <v>6375014</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3858,10 +3858,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578824</v>
+        <v>122578814</v>
       </c>
       <c r="B28" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3870,35 +3870,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707606</v>
+        <v>707638</v>
       </c>
       <c r="R28" t="n">
-        <v>6374961</v>
+        <v>6374988</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578760</v>
+        <v>122578805</v>
       </c>
       <c r="B29" t="n">
-        <v>105555</v>
+        <v>98335</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3991,40 +3991,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707547</v>
+        <v>707697</v>
       </c>
       <c r="R29" t="n">
-        <v>6375010</v>
+        <v>6374980</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4069,11 +4069,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4105,10 +4100,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578814</v>
+        <v>122578824</v>
       </c>
       <c r="B30" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4117,35 +4112,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4159,10 +4154,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707638</v>
+        <v>707606</v>
       </c>
       <c r="R30" t="n">
-        <v>6374988</v>
+        <v>6374961</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4208,7 +4203,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4226,10 +4221,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578805</v>
+        <v>122578760</v>
       </c>
       <c r="B31" t="n">
-        <v>98335</v>
+        <v>105555</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4238,40 +4233,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4280,10 +4275,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707697</v>
+        <v>707547</v>
       </c>
       <c r="R31" t="n">
-        <v>6374980</v>
+        <v>6375010</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4316,6 +4311,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4347,10 +4347,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578773</v>
+        <v>122578755</v>
       </c>
       <c r="B32" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4359,35 +4359,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707489</v>
+        <v>707541</v>
       </c>
       <c r="R32" t="n">
-        <v>6375140</v>
+        <v>6374993</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4439,6 +4439,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4450,7 +4455,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4468,10 +4473,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578755</v>
+        <v>122578773</v>
       </c>
       <c r="B33" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4480,35 +4485,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4522,10 +4527,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707541</v>
+        <v>707489</v>
       </c>
       <c r="R33" t="n">
-        <v>6374993</v>
+        <v>6375140</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4560,11 +4565,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -3503,7 +3503,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578806</v>
+        <v>122578762</v>
       </c>
       <c r="B25" t="n">
         <v>105555</v>
@@ -3536,7 +3536,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3548,13 +3557,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707678</v>
+        <v>707548</v>
       </c>
       <c r="R25" t="n">
-        <v>6374990</v>
+        <v>6375014</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3588,7 +3597,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3620,10 +3629,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578743</v>
+        <v>122578806</v>
       </c>
       <c r="B26" t="n">
-        <v>99885</v>
+        <v>105555</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3636,37 +3645,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707638</v>
+        <v>707678</v>
       </c>
       <c r="R26" t="n">
-        <v>6375036</v>
+        <v>6374990</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3700,7 +3714,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3732,10 +3746,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578762</v>
+        <v>122578743</v>
       </c>
       <c r="B27" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3748,51 +3762,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707548</v>
+        <v>707638</v>
       </c>
       <c r="R27" t="n">
-        <v>6375014</v>
+        <v>6375036</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3858,10 +3858,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578814</v>
+        <v>122578824</v>
       </c>
       <c r="B28" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3870,35 +3870,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707638</v>
+        <v>707606</v>
       </c>
       <c r="R28" t="n">
-        <v>6374988</v>
+        <v>6374961</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578805</v>
+        <v>122578760</v>
       </c>
       <c r="B29" t="n">
-        <v>98335</v>
+        <v>105555</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3991,40 +3991,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707697</v>
+        <v>707547</v>
       </c>
       <c r="R29" t="n">
-        <v>6374980</v>
+        <v>6375010</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4069,6 +4069,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4100,10 +4105,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578824</v>
+        <v>122578814</v>
       </c>
       <c r="B30" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4112,35 +4117,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4154,10 +4159,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707606</v>
+        <v>707638</v>
       </c>
       <c r="R30" t="n">
-        <v>6374961</v>
+        <v>6374988</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4203,7 +4208,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4221,10 +4226,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578760</v>
+        <v>122578805</v>
       </c>
       <c r="B31" t="n">
-        <v>105555</v>
+        <v>98335</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4233,40 +4238,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4275,10 +4280,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707547</v>
+        <v>707697</v>
       </c>
       <c r="R31" t="n">
-        <v>6375010</v>
+        <v>6374980</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4311,11 +4316,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -6635,10 +6635,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578750</v>
+        <v>122578744</v>
       </c>
       <c r="B51" t="n">
-        <v>98379</v>
+        <v>105555</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6647,40 +6647,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219862</v>
+        <v>671</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6689,13 +6689,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707569</v>
+        <v>707626</v>
       </c>
       <c r="R51" t="n">
-        <v>6374979</v>
+        <v>6375071</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6761,10 +6761,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578802</v>
+        <v>122578746</v>
       </c>
       <c r="B52" t="n">
-        <v>98335</v>
+        <v>99885</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6773,55 +6773,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707697</v>
+        <v>707626</v>
       </c>
       <c r="R52" t="n">
-        <v>6374969</v>
+        <v>6375071</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6851,6 +6837,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7250,10 +7241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578744</v>
+        <v>122578756</v>
       </c>
       <c r="B56" t="n">
-        <v>105555</v>
+        <v>99885</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7266,26 +7257,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7295,7 +7286,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7304,13 +7295,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707626</v>
+        <v>707541</v>
       </c>
       <c r="R56" t="n">
-        <v>6375071</v>
+        <v>6374993</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7344,7 +7335,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7376,10 +7367,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578756</v>
+        <v>122578750</v>
       </c>
       <c r="B57" t="n">
-        <v>99885</v>
+        <v>98379</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7388,35 +7379,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7430,10 +7421,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707541</v>
+        <v>707569</v>
       </c>
       <c r="R57" t="n">
-        <v>6374993</v>
+        <v>6374979</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -7502,10 +7493,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578746</v>
+        <v>122578802</v>
       </c>
       <c r="B58" t="n">
-        <v>99885</v>
+        <v>98335</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7514,41 +7505,55 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707626</v>
+        <v>707697</v>
       </c>
       <c r="R58" t="n">
-        <v>6375071</v>
+        <v>6374969</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7578,11 +7583,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578754</v>
+        <v>122578804</v>
       </c>
       <c r="B3" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -843,16 +843,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -864,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707554</v>
+        <v>707697</v>
       </c>
       <c r="R3" t="n">
-        <v>6374978</v>
+        <v>6374980</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -904,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578810</v>
+        <v>122578802</v>
       </c>
       <c r="B4" t="n">
-        <v>99885</v>
+        <v>98343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,28 +939,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707652</v>
+        <v>707697</v>
       </c>
       <c r="R4" t="n">
-        <v>6374986</v>
+        <v>6374969</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1017,11 +1017,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578809</v>
+        <v>122578805</v>
       </c>
       <c r="B5" t="n">
-        <v>105555</v>
+        <v>98343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,31 +1060,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1098,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707652</v>
+        <v>707697</v>
       </c>
       <c r="R5" t="n">
-        <v>6374986</v>
+        <v>6374980</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1134,11 +1138,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578777</v>
+        <v>122578741</v>
       </c>
       <c r="B6" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,34 +1202,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707591</v>
+        <v>707609</v>
       </c>
       <c r="R6" t="n">
-        <v>6375187</v>
+        <v>6375033</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,7 +1249,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>30 m S åker i N.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,7 +1263,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578795</v>
+        <v>122578814</v>
       </c>
       <c r="B7" t="n">
-        <v>105555</v>
+        <v>98343</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1308,31 +1293,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1341,10 +1335,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707725</v>
+        <v>707638</v>
       </c>
       <c r="R7" t="n">
-        <v>6374976</v>
+        <v>6374988</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1377,11 +1371,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578817</v>
+        <v>122578797</v>
       </c>
       <c r="B8" t="n">
-        <v>99885</v>
+        <v>98343</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,35 +1414,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1467,10 +1456,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707624</v>
+        <v>707725</v>
       </c>
       <c r="R8" t="n">
-        <v>6374996</v>
+        <v>6374976</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1503,11 +1492,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578804</v>
+        <v>122578750</v>
       </c>
       <c r="B9" t="n">
-        <v>99885</v>
+        <v>98387</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,28 +1535,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1584,13 +1577,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707697</v>
+        <v>707569</v>
       </c>
       <c r="R9" t="n">
-        <v>6374980</v>
+        <v>6374979</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1624,7 +1617,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578823</v>
+        <v>122578784</v>
       </c>
       <c r="B10" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,16 +1682,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1710,10 +1694,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707605</v>
+        <v>707648</v>
       </c>
       <c r="R10" t="n">
-        <v>6374970</v>
+        <v>6375072</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1750,7 +1734,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,7 +1748,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1782,10 +1766,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578764</v>
+        <v>122578821</v>
       </c>
       <c r="B11" t="n">
-        <v>99885</v>
+        <v>105563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,26 +1782,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1827,7 +1811,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1836,13 +1820,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707538</v>
+        <v>707605</v>
       </c>
       <c r="R11" t="n">
-        <v>6375024</v>
+        <v>6374970</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1876,7 +1860,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,7 +1874,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1908,10 +1892,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578778</v>
+        <v>122578815</v>
       </c>
       <c r="B12" t="n">
-        <v>99885</v>
+        <v>105563</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1924,36 +1908,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1962,13 +1937,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707599</v>
+        <v>707638</v>
       </c>
       <c r="R12" t="n">
-        <v>6375165</v>
+        <v>6374988</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2002,7 +1977,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Barrblandskog mot åker i N.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,7 +1991,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2034,10 +2009,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578812</v>
+        <v>122578825</v>
       </c>
       <c r="B13" t="n">
-        <v>105555</v>
+        <v>99893</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2050,27 +2025,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2079,10 +2063,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707646</v>
+        <v>707611</v>
       </c>
       <c r="R13" t="n">
-        <v>6374967</v>
+        <v>6374954</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2117,11 +2101,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2133,7 +2112,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2151,10 +2130,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578742</v>
+        <v>122578809</v>
       </c>
       <c r="B14" t="n">
-        <v>105555</v>
+        <v>105563</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2185,19 +2164,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707638</v>
+        <v>707652</v>
       </c>
       <c r="R14" t="n">
-        <v>6375036</v>
+        <v>6374986</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2231,7 +2215,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578797</v>
+        <v>122578816</v>
       </c>
       <c r="B15" t="n">
-        <v>98335</v>
+        <v>99893</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2275,37 +2259,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2317,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707725</v>
+        <v>707638</v>
       </c>
       <c r="R15" t="n">
-        <v>6374976</v>
+        <v>6374988</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2353,6 +2328,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2384,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578771</v>
+        <v>122578808</v>
       </c>
       <c r="B16" t="n">
-        <v>98335</v>
+        <v>98343</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2419,12 +2399,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2438,13 +2418,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707490</v>
+        <v>707678</v>
       </c>
       <c r="R16" t="n">
-        <v>6375090</v>
+        <v>6374990</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2476,11 +2456,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>I långsträckt stensamlig, grav?</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2492,7 +2467,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2510,10 +2485,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578782</v>
+        <v>122578740</v>
       </c>
       <c r="B17" t="n">
-        <v>98335</v>
+        <v>105563</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2522,55 +2497,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707621</v>
+        <v>707609</v>
       </c>
       <c r="R17" t="n">
-        <v>6375108</v>
+        <v>6375033</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2600,6 +2561,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2631,10 +2597,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578759</v>
+        <v>122578744</v>
       </c>
       <c r="B18" t="n">
-        <v>99885</v>
+        <v>105563</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2647,26 +2613,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2676,7 +2642,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2685,13 +2651,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707557</v>
+        <v>707626</v>
       </c>
       <c r="R18" t="n">
-        <v>6375009</v>
+        <v>6375071</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2725,7 +2691,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2757,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578766</v>
+        <v>122578759</v>
       </c>
       <c r="B19" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2792,12 +2758,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2811,13 +2777,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707548</v>
+        <v>707557</v>
       </c>
       <c r="R19" t="n">
-        <v>6375091</v>
+        <v>6375009</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2851,7 +2817,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2865,7 +2831,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2883,10 +2849,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578769</v>
+        <v>122578760</v>
       </c>
       <c r="B20" t="n">
-        <v>99885</v>
+        <v>105563</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2899,36 +2865,36 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2937,13 +2903,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707513</v>
+        <v>707547</v>
       </c>
       <c r="R20" t="n">
-        <v>6375053</v>
+        <v>6375010</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2977,7 +2943,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2991,7 +2957,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3009,10 +2975,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578825</v>
+        <v>122578818</v>
       </c>
       <c r="B21" t="n">
-        <v>99885</v>
+        <v>105563</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3025,36 +2991,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3063,10 +3029,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707611</v>
+        <v>707605</v>
       </c>
       <c r="R21" t="n">
-        <v>6374954</v>
+        <v>6374982</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3101,6 +3067,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3112,7 +3083,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3130,10 +3101,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578786</v>
+        <v>122578777</v>
       </c>
       <c r="B22" t="n">
-        <v>98335</v>
+        <v>99893</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3142,35 +3113,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3184,13 +3155,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707652</v>
+        <v>707591</v>
       </c>
       <c r="R22" t="n">
-        <v>6375083</v>
+        <v>6375187</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3224,7 +3195,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>30 m S åker i N.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3238,7 +3209,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3256,10 +3227,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578808</v>
+        <v>122578779</v>
       </c>
       <c r="B23" t="n">
-        <v>98335</v>
+        <v>99893</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3268,37 +3239,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3310,13 +3272,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707678</v>
+        <v>707597</v>
       </c>
       <c r="R23" t="n">
-        <v>6374990</v>
+        <v>6375142</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3348,6 +3310,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka strå.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3359,7 +3326,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3377,10 +3344,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578758</v>
+        <v>122578770</v>
       </c>
       <c r="B24" t="n">
-        <v>105555</v>
+        <v>99893</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3393,36 +3360,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3431,13 +3398,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707557</v>
+        <v>707506</v>
       </c>
       <c r="R24" t="n">
-        <v>6375009</v>
+        <v>6375077</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3471,7 +3438,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3485,7 +3452,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3503,10 +3470,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578762</v>
+        <v>122578757</v>
       </c>
       <c r="B25" t="n">
-        <v>105555</v>
+        <v>98343</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3515,40 +3482,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3557,10 +3524,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707548</v>
+        <v>707557</v>
       </c>
       <c r="R25" t="n">
-        <v>6375014</v>
+        <v>6375009</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3629,10 +3596,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578806</v>
+        <v>122578800</v>
       </c>
       <c r="B26" t="n">
-        <v>105555</v>
+        <v>105563</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3662,7 +3629,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3674,10 +3650,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707678</v>
+        <v>707697</v>
       </c>
       <c r="R26" t="n">
-        <v>6374990</v>
+        <v>6374980</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3714,7 +3690,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Inget i tallplantager mot S och O.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3746,10 +3722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578743</v>
+        <v>122578742</v>
       </c>
       <c r="B27" t="n">
-        <v>99885</v>
+        <v>105563</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3762,21 +3738,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3826,7 +3802,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3858,10 +3834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578824</v>
+        <v>122578819</v>
       </c>
       <c r="B28" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3893,7 +3869,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3912,10 +3888,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707606</v>
+        <v>707605</v>
       </c>
       <c r="R28" t="n">
-        <v>6374961</v>
+        <v>6374982</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3950,6 +3926,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3961,7 +3942,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3979,10 +3960,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578760</v>
+        <v>122578751</v>
       </c>
       <c r="B29" t="n">
-        <v>105555</v>
+        <v>98343</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3991,40 +3972,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4033,13 +4014,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707547</v>
+        <v>707569</v>
       </c>
       <c r="R29" t="n">
-        <v>6375010</v>
+        <v>6374979</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4105,10 +4086,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578814</v>
+        <v>122578755</v>
       </c>
       <c r="B30" t="n">
-        <v>98335</v>
+        <v>98343</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4159,13 +4140,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707638</v>
+        <v>707541</v>
       </c>
       <c r="R30" t="n">
-        <v>6374988</v>
+        <v>6374993</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4195,6 +4176,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4226,10 +4212,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578805</v>
+        <v>122578765</v>
       </c>
       <c r="B31" t="n">
-        <v>98335</v>
+        <v>99893</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4238,37 +4224,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4280,13 +4257,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707697</v>
+        <v>707532</v>
       </c>
       <c r="R31" t="n">
-        <v>6374980</v>
+        <v>6375035</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4316,6 +4293,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4347,10 +4329,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578755</v>
+        <v>122578806</v>
       </c>
       <c r="B32" t="n">
-        <v>98335</v>
+        <v>105563</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4359,40 +4341,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4401,13 +4374,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707541</v>
+        <v>707678</v>
       </c>
       <c r="R32" t="n">
-        <v>6374993</v>
+        <v>6374990</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4441,7 +4414,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4473,10 +4446,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578773</v>
+        <v>122578796</v>
       </c>
       <c r="B33" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4506,16 +4479,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4527,13 +4491,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707489</v>
+        <v>707725</v>
       </c>
       <c r="R33" t="n">
-        <v>6375140</v>
+        <v>6374976</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4565,6 +4529,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4576,7 +4545,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4594,10 +4563,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578785</v>
+        <v>122578769</v>
       </c>
       <c r="B34" t="n">
-        <v>105555</v>
+        <v>99893</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4610,27 +4579,36 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4639,13 +4617,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707648</v>
+        <v>707513</v>
       </c>
       <c r="R34" t="n">
-        <v>6375072</v>
+        <v>6375053</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4679,7 +4657,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4693,7 +4671,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4711,10 +4689,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578803</v>
+        <v>122578754</v>
       </c>
       <c r="B35" t="n">
-        <v>105555</v>
+        <v>99893</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4727,27 +4705,36 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4756,10 +4743,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707697</v>
+        <v>707554</v>
       </c>
       <c r="R35" t="n">
-        <v>6374980</v>
+        <v>6374978</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4796,7 +4783,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4828,10 +4815,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578784</v>
+        <v>122578753</v>
       </c>
       <c r="B36" t="n">
-        <v>99885</v>
+        <v>98343</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4840,28 +4827,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4873,10 +4869,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707648</v>
+        <v>707554</v>
       </c>
       <c r="R36" t="n">
-        <v>6375072</v>
+        <v>6374978</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4913,7 +4909,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4945,10 +4941,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578796</v>
+        <v>122578786</v>
       </c>
       <c r="B37" t="n">
-        <v>99885</v>
+        <v>98343</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4957,28 +4953,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4990,10 +4995,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707725</v>
+        <v>707652</v>
       </c>
       <c r="R37" t="n">
-        <v>6374976</v>
+        <v>6375083</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5030,7 +5035,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5062,10 +5067,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578821</v>
+        <v>122578749</v>
       </c>
       <c r="B38" t="n">
-        <v>105555</v>
+        <v>105563</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5097,12 +5102,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5116,10 +5121,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707605</v>
+        <v>707570</v>
       </c>
       <c r="R38" t="n">
-        <v>6374970</v>
+        <v>6374984</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5156,7 +5161,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5170,7 +5175,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5188,10 +5193,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578747</v>
+        <v>122578774</v>
       </c>
       <c r="B39" t="n">
-        <v>105555</v>
+        <v>99893</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5204,37 +5209,51 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707590</v>
+        <v>707528</v>
       </c>
       <c r="R39" t="n">
-        <v>6375036</v>
+        <v>6375154</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5266,11 +5285,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5282,7 +5296,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5300,10 +5314,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578767</v>
+        <v>122578746</v>
       </c>
       <c r="B40" t="n">
-        <v>98379</v>
+        <v>99893</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5312,55 +5326,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707513</v>
+        <v>707626</v>
       </c>
       <c r="R40" t="n">
-        <v>6375053</v>
+        <v>6375071</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5392,6 +5392,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Stensamling, grav? Nära.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5403,7 +5408,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5421,10 +5426,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578748</v>
+        <v>122578795</v>
       </c>
       <c r="B41" t="n">
-        <v>99885</v>
+        <v>105563</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5437,34 +5442,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707590</v>
+        <v>707725</v>
       </c>
       <c r="R41" t="n">
-        <v>6375036</v>
+        <v>6374976</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5533,10 +5543,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578783</v>
+        <v>122578747</v>
       </c>
       <c r="B42" t="n">
-        <v>99885</v>
+        <v>105563</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5549,42 +5559,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707633</v>
+        <v>707590</v>
       </c>
       <c r="R42" t="n">
-        <v>6375094</v>
+        <v>6375036</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5618,7 +5623,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5653,7 +5658,7 @@
         <v>122578772</v>
       </c>
       <c r="B43" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5776,10 +5781,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578815</v>
+        <v>122578783</v>
       </c>
       <c r="B44" t="n">
-        <v>105555</v>
+        <v>99893</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5792,27 +5797,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5821,13 +5826,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707638</v>
+        <v>707633</v>
       </c>
       <c r="R44" t="n">
-        <v>6374988</v>
+        <v>6375094</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5861,7 +5866,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5893,10 +5898,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578779</v>
+        <v>122578748</v>
       </c>
       <c r="B45" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5927,24 +5932,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707597</v>
+        <v>707590</v>
       </c>
       <c r="R45" t="n">
-        <v>6375142</v>
+        <v>6375036</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578770</v>
+        <v>122578824</v>
       </c>
       <c r="B46" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6064,13 +6064,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707506</v>
+        <v>707606</v>
       </c>
       <c r="R46" t="n">
-        <v>6375077</v>
+        <v>6374961</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6102,11 +6102,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2 ex.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6118,7 +6113,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6136,10 +6131,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578757</v>
+        <v>122578764</v>
       </c>
       <c r="B47" t="n">
-        <v>98335</v>
+        <v>99893</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6148,35 +6143,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6190,13 +6185,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707557</v>
+        <v>707538</v>
       </c>
       <c r="R47" t="n">
-        <v>6375009</v>
+        <v>6375024</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6262,10 +6257,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578763</v>
+        <v>122578812</v>
       </c>
       <c r="B48" t="n">
-        <v>99885</v>
+        <v>105563</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6278,36 +6273,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6316,13 +6302,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707548</v>
+        <v>707646</v>
       </c>
       <c r="R48" t="n">
-        <v>6375014</v>
+        <v>6374967</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6356,7 +6342,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6388,10 +6374,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578752</v>
+        <v>122578743</v>
       </c>
       <c r="B49" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6421,34 +6407,20 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707569</v>
+        <v>707638</v>
       </c>
       <c r="R49" t="n">
-        <v>6374979</v>
+        <v>6375036</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6482,7 +6454,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6514,10 +6486,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578811</v>
+        <v>122578773</v>
       </c>
       <c r="B50" t="n">
-        <v>98335</v>
+        <v>99893</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6526,35 +6498,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6568,13 +6540,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707652</v>
+        <v>707489</v>
       </c>
       <c r="R50" t="n">
-        <v>6374986</v>
+        <v>6375140</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6617,7 +6589,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6635,10 +6607,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578744</v>
+        <v>122578771</v>
       </c>
       <c r="B51" t="n">
-        <v>105555</v>
+        <v>98343</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6647,30 +6619,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6680,7 +6652,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6689,13 +6661,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707626</v>
+        <v>707490</v>
       </c>
       <c r="R51" t="n">
-        <v>6375071</v>
+        <v>6375090</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6729,7 +6701,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6743,7 +6715,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6761,10 +6733,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578746</v>
+        <v>122578758</v>
       </c>
       <c r="B52" t="n">
-        <v>99885</v>
+        <v>105563</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6777,37 +6749,51 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707626</v>
+        <v>707557</v>
       </c>
       <c r="R52" t="n">
-        <v>6375071</v>
+        <v>6375009</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6841,7 +6827,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6873,10 +6859,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578776</v>
+        <v>122578823</v>
       </c>
       <c r="B53" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6908,7 +6894,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6927,13 +6913,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707584</v>
+        <v>707605</v>
       </c>
       <c r="R53" t="n">
-        <v>6375172</v>
+        <v>6374970</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6965,6 +6951,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Minsta antal + spridd.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6976,7 +6967,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6994,10 +6985,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578818</v>
+        <v>122578781</v>
       </c>
       <c r="B54" t="n">
-        <v>105555</v>
+        <v>99893</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7010,36 +7001,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7048,10 +7030,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707605</v>
+        <v>707621</v>
       </c>
       <c r="R54" t="n">
-        <v>6374982</v>
+        <v>6375108</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7088,7 +7070,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7102,7 +7084,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7120,10 +7102,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578775</v>
+        <v>122578780</v>
       </c>
       <c r="B55" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7153,16 +7135,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7174,13 +7147,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707564</v>
+        <v>707626</v>
       </c>
       <c r="R55" t="n">
-        <v>6375169</v>
+        <v>6375120</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7212,6 +7185,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7223,7 +7201,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7241,10 +7219,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578756</v>
+        <v>122578813</v>
       </c>
       <c r="B56" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7274,16 +7252,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7295,13 +7264,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707541</v>
+        <v>707646</v>
       </c>
       <c r="R56" t="n">
-        <v>6374993</v>
+        <v>6374967</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7335,7 +7304,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7367,10 +7336,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578750</v>
+        <v>122578776</v>
       </c>
       <c r="B57" t="n">
-        <v>98379</v>
+        <v>99893</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7379,35 +7348,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7421,13 +7390,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707569</v>
+        <v>707584</v>
       </c>
       <c r="R57" t="n">
-        <v>6374979</v>
+        <v>6375172</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7459,11 +7428,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7475,7 +7439,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7493,10 +7457,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578802</v>
+        <v>122578785</v>
       </c>
       <c r="B58" t="n">
-        <v>98335</v>
+        <v>105563</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7505,40 +7469,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7547,10 +7502,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707697</v>
+        <v>707648</v>
       </c>
       <c r="R58" t="n">
-        <v>6374969</v>
+        <v>6375072</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7583,6 +7538,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Glest spridd, men saknas mot O-NO..</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7614,10 +7574,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578781</v>
+        <v>122578767</v>
       </c>
       <c r="B59" t="n">
-        <v>99885</v>
+        <v>98387</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7626,28 +7586,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>783</v>
+        <v>219862</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7659,13 +7628,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707621</v>
+        <v>707513</v>
       </c>
       <c r="R59" t="n">
-        <v>6375108</v>
+        <v>6375053</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7697,11 +7666,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Glest spridd.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7713,7 +7677,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7731,10 +7695,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578819</v>
+        <v>122578810</v>
       </c>
       <c r="B60" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7764,16 +7728,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7785,10 +7740,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707605</v>
+        <v>707652</v>
       </c>
       <c r="R60" t="n">
-        <v>6374982</v>
+        <v>6374986</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7825,7 +7780,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7839,7 +7794,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7857,10 +7812,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578780</v>
+        <v>122578782</v>
       </c>
       <c r="B61" t="n">
-        <v>99885</v>
+        <v>98343</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7869,28 +7824,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7902,13 +7866,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707626</v>
+        <v>707621</v>
       </c>
       <c r="R61" t="n">
-        <v>6375120</v>
+        <v>6375108</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7938,11 +7902,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7974,10 +7933,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122578765</v>
+        <v>122578817</v>
       </c>
       <c r="B62" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8007,7 +7966,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8019,13 +7987,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707532</v>
+        <v>707624</v>
       </c>
       <c r="R62" t="n">
-        <v>6375035</v>
+        <v>6374996</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8059,7 +8027,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8091,10 +8059,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578741</v>
+        <v>122578807</v>
       </c>
       <c r="B63" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8125,19 +8093,24 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707609</v>
+        <v>707678</v>
       </c>
       <c r="R63" t="n">
-        <v>6375033</v>
+        <v>6374990</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8171,7 +8144,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8203,10 +8176,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578816</v>
+        <v>122578762</v>
       </c>
       <c r="B64" t="n">
-        <v>99885</v>
+        <v>105563</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8219,27 +8192,36 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8248,13 +8230,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707638</v>
+        <v>707548</v>
       </c>
       <c r="R64" t="n">
-        <v>6374988</v>
+        <v>6375014</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8288,7 +8270,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8320,10 +8302,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578751</v>
+        <v>122578775</v>
       </c>
       <c r="B65" t="n">
-        <v>98335</v>
+        <v>99893</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8332,35 +8314,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8374,13 +8356,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707569</v>
+        <v>707564</v>
       </c>
       <c r="R65" t="n">
-        <v>6374979</v>
+        <v>6375169</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8412,11 +8394,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8428,7 +8405,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8446,10 +8423,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578740</v>
+        <v>122578756</v>
       </c>
       <c r="B66" t="n">
-        <v>105555</v>
+        <v>99893</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8462,37 +8439,51 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707609</v>
+        <v>707541</v>
       </c>
       <c r="R66" t="n">
-        <v>6375033</v>
+        <v>6374993</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8526,7 +8517,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8558,10 +8549,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578807</v>
+        <v>122578766</v>
       </c>
       <c r="B67" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8591,7 +8582,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8603,13 +8603,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707678</v>
+        <v>707548</v>
       </c>
       <c r="R67" t="n">
-        <v>6374990</v>
+        <v>6375091</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8675,10 +8675,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578753</v>
+        <v>122578778</v>
       </c>
       <c r="B68" t="n">
-        <v>98335</v>
+        <v>99893</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8687,35 +8687,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8729,13 +8729,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707554</v>
+        <v>707599</v>
       </c>
       <c r="R68" t="n">
-        <v>6374978</v>
+        <v>6375165</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8801,10 +8801,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578749</v>
+        <v>122578752</v>
       </c>
       <c r="B69" t="n">
-        <v>105555</v>
+        <v>99893</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8817,36 +8817,36 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8855,13 +8855,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707570</v>
+        <v>707569</v>
       </c>
       <c r="R69" t="n">
-        <v>6374984</v>
+        <v>6374979</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8927,10 +8927,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578774</v>
+        <v>122578763</v>
       </c>
       <c r="B70" t="n">
-        <v>99885</v>
+        <v>99893</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8981,13 +8981,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707528</v>
+        <v>707548</v>
       </c>
       <c r="R70" t="n">
-        <v>6375154</v>
+        <v>6375014</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9019,6 +9019,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9030,7 +9035,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9048,10 +9053,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578813</v>
+        <v>122578811</v>
       </c>
       <c r="B71" t="n">
-        <v>99885</v>
+        <v>98343</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9060,28 +9065,37 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -9093,10 +9107,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707646</v>
+        <v>707652</v>
       </c>
       <c r="R71" t="n">
-        <v>6374967</v>
+        <v>6374986</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9129,11 +9143,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>97822</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>707652.2700944055</v>
+        <v>707652</v>
       </c>
       <c r="R2" t="n">
-        <v>6375039.953590461</v>
+        <v>6375040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>100109</v>
+        <v>100115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>100115</v>
+        <v>100119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>100119</v>
+        <v>100125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>100125</v>
+        <v>100126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>100126</v>
+        <v>100153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>100153</v>
+        <v>100159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>100159</v>
+        <v>100166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>100166</v>
+        <v>100170</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>100170</v>
+        <v>100177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>100180</v>
+        <v>100185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074257</v>
       </c>
       <c r="B2" t="n">
-        <v>100185</v>
+        <v>100193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9157,6 +9157,249 @@
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>134263109</v>
+      </c>
+      <c r="B72" t="n">
+        <v>106405</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>671</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>707561</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6374999</v>
+      </c>
+      <c r="S72" t="n">
+        <v>39</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>I-Got-4284</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Körväg V. 3 kvm.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134263110</v>
+      </c>
+      <c r="B73" t="n">
+        <v>106405</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>671</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>707658</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6375003</v>
+      </c>
+      <c r="S73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>I-Got-4285</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Spridd, riklig.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -9162,7 +9162,7 @@
         <v>134263109</v>
       </c>
       <c r="B72" t="n">
-        <v>106405</v>
+        <v>106406</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>134263110</v>
       </c>
       <c r="B73" t="n">
-        <v>106405</v>
+        <v>106406</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -9162,7 +9162,7 @@
         <v>134263109</v>
       </c>
       <c r="B72" t="n">
-        <v>106407</v>
+        <v>106414</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>134263110</v>
       </c>
       <c r="B73" t="n">
-        <v>106407</v>
+        <v>106414</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105074257</v>
+        <v>122578740</v>
       </c>
       <c r="B2" t="n">
-        <v>100193</v>
+        <v>106341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sigsarve 1:6, 550 m N, Gtl</t>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>707652</v>
+        <v>707609</v>
       </c>
       <c r="R2" t="n">
-        <v>6375040</v>
+        <v>6375033</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1986-01-01</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>(50 x 50 m)</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,23 +778,14 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122578804</v>
+        <v>122578742</v>
       </c>
       <c r="B3" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707697</v>
+        <v>707638</v>
       </c>
       <c r="R3" t="n">
-        <v>6374980</v>
+        <v>6375036</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,52 +889,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122578802</v>
+        <v>122578744</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707697</v>
+        <v>707626</v>
       </c>
       <c r="R4" t="n">
-        <v>6374969</v>
+        <v>6375071</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,6 +974,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,64 +1010,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122578805</v>
+        <v>122578747</v>
       </c>
       <c r="B5" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707697</v>
+        <v>707590</v>
       </c>
       <c r="R5" t="n">
-        <v>6374980</v>
+        <v>6375036</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,6 +1081,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,15 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122578741</v>
+        <v>122578749</v>
       </c>
       <c r="B6" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,37 +1128,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707609</v>
+        <v>707570</v>
       </c>
       <c r="R6" t="n">
-        <v>6375033</v>
+        <v>6374984</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1206,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,37 +1238,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122578814</v>
+        <v>122578758</v>
       </c>
       <c r="B7" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1306,12 +1273,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,13 +1287,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707638</v>
+        <v>707557</v>
       </c>
       <c r="R7" t="n">
-        <v>6374988</v>
+        <v>6375009</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,6 +1323,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,52 +1359,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122578797</v>
+        <v>122578760</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1441,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707725</v>
+        <v>707547</v>
       </c>
       <c r="R8" t="n">
-        <v>6374976</v>
+        <v>6375010</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1477,6 +1444,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,52 +1480,47 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122578750</v>
+        <v>122578762</v>
       </c>
       <c r="B9" t="n">
-        <v>98387</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1562,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707569</v>
+        <v>707548</v>
       </c>
       <c r="R9" t="n">
-        <v>6374979</v>
+        <v>6375014</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1634,15 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122578784</v>
+        <v>122578785</v>
       </c>
       <c r="B10" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,27 +1612,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1751,15 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122578821</v>
+        <v>122578788</v>
       </c>
       <c r="B11" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1784,16 +1741,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1805,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707605</v>
+        <v>707697</v>
       </c>
       <c r="R11" t="n">
-        <v>6374970</v>
+        <v>6375043</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1845,7 +1793,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,7 +1807,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1877,15 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122578815</v>
+        <v>122578795</v>
       </c>
       <c r="B12" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707638</v>
+        <v>707725</v>
       </c>
       <c r="R12" t="n">
-        <v>6374988</v>
+        <v>6374976</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1962,7 +1905,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,15 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122578825</v>
+        <v>122578800</v>
       </c>
       <c r="B13" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,36 +1948,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2048,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707611</v>
+        <v>707697</v>
       </c>
       <c r="R13" t="n">
-        <v>6374954</v>
+        <v>6374980</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2086,6 +2024,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Inget i tallplantager mot S och O.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2097,7 +2040,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2115,15 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122578809</v>
+        <v>122578806</v>
       </c>
       <c r="B14" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707652</v>
+        <v>707678</v>
       </c>
       <c r="R14" t="n">
-        <v>6374986</v>
+        <v>6374990</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2232,15 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122578816</v>
+        <v>122578809</v>
       </c>
       <c r="B15" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,27 +2181,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2277,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707638</v>
+        <v>707652</v>
       </c>
       <c r="R15" t="n">
-        <v>6374988</v>
+        <v>6374986</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2317,7 +2250,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spridd, ganska rikligt.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2349,52 +2282,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122578808</v>
+        <v>122578812</v>
       </c>
       <c r="B16" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2403,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>707678</v>
+        <v>707646</v>
       </c>
       <c r="R16" t="n">
-        <v>6374990</v>
+        <v>6374967</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2439,6 +2358,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,15 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122578740</v>
+        <v>122578815</v>
       </c>
       <c r="B17" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,19 +2423,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707609</v>
+        <v>707638</v>
       </c>
       <c r="R17" t="n">
-        <v>6375033</v>
+        <v>6374988</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2550,7 +2474,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spridd, riklig. Strensamling, grav?</t>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2582,15 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122578744</v>
+        <v>122578818</v>
       </c>
       <c r="B18" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,12 +2536,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2636,13 +2555,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707626</v>
+        <v>707605</v>
       </c>
       <c r="R18" t="n">
-        <v>6375071</v>
+        <v>6374982</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2676,7 +2595,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Stensamling, grav? Nära.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,7 +2609,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2708,15 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122578759</v>
+        <v>122578821</v>
       </c>
       <c r="B19" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,26 +2638,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2753,7 +2667,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2762,13 +2676,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707557</v>
+        <v>707605</v>
       </c>
       <c r="R19" t="n">
-        <v>6375009</v>
+        <v>6374970</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2802,7 +2716,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,7 +2730,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2834,15 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122578760</v>
+        <v>122578826</v>
       </c>
       <c r="B20" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2869,12 +2778,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2888,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707547</v>
+        <v>707617</v>
       </c>
       <c r="R20" t="n">
-        <v>6375010</v>
+        <v>6374931</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2926,11 +2835,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2942,7 +2846,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge, f.d. grus-/sandtag?</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2960,15 +2864,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122578818</v>
+        <v>134263109</v>
       </c>
       <c r="B21" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106421</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2993,34 +2892,27 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+          <t>Viklau Sigsarve 1:2, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707605</v>
+        <v>707561</v>
       </c>
       <c r="R21" t="n">
-        <v>6374982</v>
+        <v>6374999</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3042,6 +2934,11 @@
           <t>Viklau</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>I-Got-4284</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr">
         <is>
           <t>2025-02-11</t>
@@ -3054,7 +2951,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Körväg V. 3 kvm.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3063,18 +2960,19 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3082,19 +2980,18 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122578777</v>
+        <v>134263110</v>
       </c>
       <c r="B22" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106421</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3102,51 +2999,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+          <t>Viklau Sigsarve 1:2, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707591</v>
+        <v>707658</v>
       </c>
       <c r="R22" t="n">
-        <v>6375187</v>
+        <v>6375003</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3168,6 +3053,11 @@
           <t>Viklau</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>I-Got-4285</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr">
         <is>
           <t>2025-02-11</t>
@@ -3180,7 +3070,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>30 m S åker i N.</t>
+          <t>Spridd, riklig.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3189,18 +3079,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3208,19 +3099,18 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122578779</v>
+        <v>105074257</v>
       </c>
       <c r="B23" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,25 +3135,29 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+          <t>Sigsarve 1:6, 550 m N, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707597</v>
+        <v>707652</v>
       </c>
       <c r="R23" t="n">
-        <v>6375142</v>
+        <v>6375040</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3287,17 +3181,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>1986-01-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>1990-12-31</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Enstaka strå.</t>
+          <t>(50 x 50 m)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3311,7 +3205,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3325,19 +3219,18 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122578770</v>
+        <v>105074295</v>
       </c>
       <c r="B24" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,32 +3257,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+          <t>Kyrkan 570 m NO, Sigsarve 1:2, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707506</v>
+        <v>707654</v>
       </c>
       <c r="R24" t="n">
-        <v>6375077</v>
+        <v>6374950</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3413,17 +3301,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>1988-12-31</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Sigsarve 1:2</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3437,7 +3325,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3451,71 +3339,56 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122578757</v>
+        <v>122578741</v>
       </c>
       <c r="B25" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707557</v>
+        <v>707609</v>
       </c>
       <c r="R25" t="n">
-        <v>6375009</v>
+        <v>6375033</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3549,7 +3422,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd, riklig. Strensamling, grav?</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3581,15 +3454,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122578800</v>
+        <v>122578743</v>
       </c>
       <c r="B26" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,51 +3465,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707697</v>
+        <v>707638</v>
       </c>
       <c r="R26" t="n">
-        <v>6374980</v>
+        <v>6375036</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3675,7 +3529,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Inget i tallplantager mot S och O.</t>
+          <t>Spridd, rikligt söderut.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3707,15 +3561,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122578742</v>
+        <v>122578746</v>
       </c>
       <c r="B27" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3723,21 +3572,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3747,10 +3596,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707638</v>
+        <v>707626</v>
       </c>
       <c r="R27" t="n">
-        <v>6375036</v>
+        <v>6375071</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3787,7 +3636,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt spridd 100 S till där tallplantage börjar söderut.</t>
+          <t>Stensamling, grav? Nära.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3819,15 +3668,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122578819</v>
+        <v>122578748</v>
       </c>
       <c r="B28" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3852,31 +3696,17 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707605</v>
+        <v>707590</v>
       </c>
       <c r="R28" t="n">
-        <v>6374982</v>
+        <v>6375036</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3913,7 +3743,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3927,7 +3757,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3945,47 +3775,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122578751</v>
+        <v>122578752</v>
       </c>
       <c r="B29" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4071,47 +3896,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122578755</v>
+        <v>122578754</v>
       </c>
       <c r="B30" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4125,13 +3945,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707541</v>
+        <v>707554</v>
       </c>
       <c r="R30" t="n">
-        <v>6374993</v>
+        <v>6374978</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4197,15 +4017,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122578765</v>
+        <v>122578756</v>
       </c>
       <c r="B31" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4230,7 +4045,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4242,13 +4066,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707532</v>
+        <v>707541</v>
       </c>
       <c r="R31" t="n">
-        <v>6375035</v>
+        <v>6374993</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4282,7 +4106,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Spridd glest mot O-N.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4314,15 +4138,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122578806</v>
+        <v>122578759</v>
       </c>
       <c r="B32" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4330,27 +4149,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4359,13 +4187,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707678</v>
+        <v>707557</v>
       </c>
       <c r="R32" t="n">
-        <v>6374990</v>
+        <v>6375009</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4399,7 +4227,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4431,15 +4259,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122578796</v>
+        <v>122578763</v>
       </c>
       <c r="B33" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4464,7 +4287,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4476,13 +4308,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707725</v>
+        <v>707548</v>
       </c>
       <c r="R33" t="n">
-        <v>6374976</v>
+        <v>6375014</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4516,7 +4348,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4548,15 +4380,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122578769</v>
+        <v>122578764</v>
       </c>
       <c r="B34" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4583,7 +4410,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4602,13 +4429,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707513</v>
+        <v>707538</v>
       </c>
       <c r="R34" t="n">
-        <v>6375053</v>
+        <v>6375024</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4642,7 +4469,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4656,7 +4483,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4674,15 +4501,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122578754</v>
+        <v>122578765</v>
       </c>
       <c r="B35" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4707,16 +4529,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -4728,13 +4541,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707554</v>
+        <v>707532</v>
       </c>
       <c r="R35" t="n">
-        <v>6374978</v>
+        <v>6375035</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4768,7 +4581,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Spridd glest mot O-N.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4800,47 +4613,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122578753</v>
+        <v>122578766</v>
       </c>
       <c r="B36" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4854,13 +4662,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707554</v>
+        <v>707548</v>
       </c>
       <c r="R36" t="n">
-        <v>6374978</v>
+        <v>6375091</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4894,7 +4702,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4908,7 +4716,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4926,47 +4734,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122578786</v>
+        <v>122578769</v>
       </c>
       <c r="B37" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4980,13 +4783,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707652</v>
+        <v>707513</v>
       </c>
       <c r="R37" t="n">
-        <v>6375083</v>
+        <v>6375053</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5020,7 +4823,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5034,7 +4837,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5052,15 +4855,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122578749</v>
+        <v>122578770</v>
       </c>
       <c r="B38" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5068,36 +4866,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5106,13 +4904,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707570</v>
+        <v>707506</v>
       </c>
       <c r="R38" t="n">
-        <v>6374984</v>
+        <v>6375077</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5146,7 +4944,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5160,7 +4958,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5178,15 +4976,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122578774</v>
+        <v>122578772</v>
       </c>
       <c r="B39" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5213,7 +5006,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5232,13 +5025,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707528</v>
+        <v>707506</v>
       </c>
       <c r="R39" t="n">
-        <v>6375154</v>
+        <v>6375110</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5270,6 +5063,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5281,7 +5079,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5299,15 +5097,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122578746</v>
+        <v>122578773</v>
       </c>
       <c r="B40" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5332,20 +5125,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707626</v>
+        <v>707489</v>
       </c>
       <c r="R40" t="n">
-        <v>6375071</v>
+        <v>6375140</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5377,11 +5184,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Stensamling, grav? Nära.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5393,7 +5195,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5411,15 +5213,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122578795</v>
+        <v>122578774</v>
       </c>
       <c r="B41" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5427,27 +5224,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5456,13 +5262,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707725</v>
+        <v>707528</v>
       </c>
       <c r="R41" t="n">
-        <v>6374976</v>
+        <v>6375154</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5494,11 +5300,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5510,7 +5311,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5528,15 +5329,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122578747</v>
+        <v>122578775</v>
       </c>
       <c r="B42" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5544,37 +5340,51 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707590</v>
+        <v>707564</v>
       </c>
       <c r="R42" t="n">
-        <v>6375036</v>
+        <v>6375169</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5606,11 +5416,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5622,7 +5427,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5640,15 +5445,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122578772</v>
+        <v>122578776</v>
       </c>
       <c r="B43" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5694,10 +5494,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707506</v>
+        <v>707584</v>
       </c>
       <c r="R43" t="n">
-        <v>6375110</v>
+        <v>6375172</v>
       </c>
       <c r="S43" t="n">
         <v>7</v>
@@ -5732,11 +5532,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2 ex.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5748,7 +5543,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5766,15 +5561,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122578783</v>
+        <v>122578777</v>
       </c>
       <c r="B44" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5799,7 +5589,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -5811,13 +5610,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707633</v>
+        <v>707591</v>
       </c>
       <c r="R44" t="n">
-        <v>6375094</v>
+        <v>6375187</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5851,7 +5650,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>30 m S åker i N.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5865,7 +5664,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5883,15 +5682,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122578748</v>
+        <v>122578778</v>
       </c>
       <c r="B45" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5916,20 +5710,34 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707590</v>
+        <v>707599</v>
       </c>
       <c r="R45" t="n">
-        <v>6375036</v>
+        <v>6375165</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5963,7 +5771,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Barrblandskog mot åker i N.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5977,7 +5785,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5995,15 +5803,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122578824</v>
+        <v>122578779</v>
       </c>
       <c r="B46" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6028,16 +5831,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6049,13 +5843,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707606</v>
+        <v>707597</v>
       </c>
       <c r="R46" t="n">
-        <v>6374961</v>
+        <v>6375142</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6087,6 +5881,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Enstaka strå.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6098,7 +5897,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Grandunge.</t>
+          <t>Granplantering halvgammal med enstaka tall.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6116,15 +5915,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122578764</v>
+        <v>122578780</v>
       </c>
       <c r="B47" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6149,16 +5943,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6170,13 +5955,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707538</v>
+        <v>707626</v>
       </c>
       <c r="R47" t="n">
-        <v>6375024</v>
+        <v>6375120</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6210,7 +5995,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6242,15 +6027,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122578812</v>
+        <v>122578781</v>
       </c>
       <c r="B48" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6258,27 +6038,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6287,10 +6067,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707646</v>
+        <v>707621</v>
       </c>
       <c r="R48" t="n">
-        <v>6374967</v>
+        <v>6375108</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6327,7 +6107,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6359,15 +6139,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122578743</v>
+        <v>122578783</v>
       </c>
       <c r="B49" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6393,19 +6168,24 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707638</v>
+        <v>707633</v>
       </c>
       <c r="R49" t="n">
-        <v>6375036</v>
+        <v>6375094</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6439,7 +6219,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Spridd, rikligt söderut.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6471,15 +6251,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122578773</v>
+        <v>122578784</v>
       </c>
       <c r="B50" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6504,16 +6279,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6525,13 +6291,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707489</v>
+        <v>707648</v>
       </c>
       <c r="R50" t="n">
-        <v>6375140</v>
+        <v>6375072</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6563,6 +6329,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Glest spridd, men saknas mot O-NO..</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6574,7 +6345,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6592,49 +6363,35 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122578771</v>
+        <v>122578787</v>
       </c>
       <c r="B51" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -6646,13 +6403,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707490</v>
+        <v>707689</v>
       </c>
       <c r="R51" t="n">
-        <v>6375090</v>
+        <v>6375067</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6686,7 +6443,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>I långsträckt stensamlig, grav?</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6700,7 +6457,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6718,15 +6475,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122578758</v>
+        <v>122578790</v>
       </c>
       <c r="B52" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6734,36 +6486,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6772,13 +6515,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707557</v>
+        <v>707707</v>
       </c>
       <c r="R52" t="n">
-        <v>6375009</v>
+        <v>6375037</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6812,7 +6555,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Glest spridd.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6844,15 +6587,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122578823</v>
+        <v>122578792</v>
       </c>
       <c r="B53" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6879,7 +6617,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6898,13 +6636,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707605</v>
+        <v>707727</v>
       </c>
       <c r="R53" t="n">
-        <v>6374970</v>
+        <v>6375039</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6938,7 +6676,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minsta antal + spridd.</t>
+          <t>O avverkningsväg vid gammal granstubbe + en del yngre gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6952,7 +6690,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Granplantering äldre, enstaka tall.</t>
+          <t>Tallplantering, vid granstubbe samt några yngre granar.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6970,15 +6708,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122578781</v>
+        <v>122578794</v>
       </c>
       <c r="B54" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7015,13 +6748,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707621</v>
+        <v>707746</v>
       </c>
       <c r="R54" t="n">
-        <v>6375108</v>
+        <v>6375008</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7055,7 +6788,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Glest spridd.</t>
+          <t>Glest spridd till avverkningsväg i O. Öster om avverkningsvägen bara enstaka strån vid spridda granar i Tallplanteringen.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7087,15 +6820,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122578780</v>
+        <v>122578796</v>
       </c>
       <c r="B55" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7132,13 +6860,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707626</v>
+        <v>707725</v>
       </c>
       <c r="R55" t="n">
-        <v>6375120</v>
+        <v>6374976</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7172,7 +6900,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Glest spridd. Avverkningsväg i O mot NO och just i N (större). Granplantering, något yngre i N. Tall + gran mot O (ingen skogskorn ses här).</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7204,15 +6932,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122578813</v>
+        <v>122578799</v>
       </c>
       <c r="B56" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7237,7 +6960,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7249,10 +6981,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707646</v>
+        <v>707722</v>
       </c>
       <c r="R56" t="n">
-        <v>6374967</v>
+        <v>6374931</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7289,7 +7021,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
+          <t>Enda sedda i tallplanteringen mot S.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7303,7 +7035,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Tallplantering halvgammal, men yngre än granplantering i N.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7321,15 +7053,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122578776</v>
+        <v>122578801</v>
       </c>
       <c r="B57" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7354,16 +7081,7 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7375,13 +7093,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707584</v>
+        <v>707697</v>
       </c>
       <c r="R57" t="n">
-        <v>6375172</v>
+        <v>6374980</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7413,6 +7131,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spridd. Förutom m3 strå inget i tallplantager mot S och O.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7424,7 +7147,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7442,15 +7165,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122578785</v>
+        <v>122578807</v>
       </c>
       <c r="B58" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,27 +7176,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7487,10 +7205,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707648</v>
+        <v>707678</v>
       </c>
       <c r="R58" t="n">
-        <v>6375072</v>
+        <v>6374990</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7527,7 +7245,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Glest spridd, men saknas mot O-NO..</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7559,49 +7277,35 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122578767</v>
+        <v>122578810</v>
       </c>
       <c r="B59" t="n">
-        <v>98387</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219862</v>
+        <v>783</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7613,13 +7317,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707513</v>
+        <v>707652</v>
       </c>
       <c r="R59" t="n">
-        <v>6375053</v>
+        <v>6374986</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7651,6 +7355,11 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7662,7 +7371,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Granplantering äldre.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7680,15 +7389,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122578810</v>
+        <v>122578813</v>
       </c>
       <c r="B60" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7725,10 +7429,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707652</v>
+        <v>707646</v>
       </c>
       <c r="R60" t="n">
-        <v>6374986</v>
+        <v>6374967</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7765,7 +7469,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt i sydkant av äldre granplantering; inga plantor ses i yngre tallplantering mot S.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7797,49 +7501,35 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122578782</v>
+        <v>122578816</v>
       </c>
       <c r="B61" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -7851,10 +7541,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707621</v>
+        <v>707638</v>
       </c>
       <c r="R61" t="n">
-        <v>6375108</v>
+        <v>6374988</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7887,6 +7577,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Spridd, ganska rikligt.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7921,12 +7616,7 @@
         <v>122578817</v>
       </c>
       <c r="B62" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8044,15 +7734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122578807</v>
+        <v>122578819</v>
       </c>
       <c r="B63" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8077,7 +7762,16 @@
           <t>(L.) Harz</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -8089,10 +7783,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707678</v>
+        <v>707605</v>
       </c>
       <c r="R63" t="n">
-        <v>6374990</v>
+        <v>6374982</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8129,7 +7823,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8143,7 +7837,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8161,15 +7855,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122578762</v>
+        <v>122578823</v>
       </c>
       <c r="B64" t="n">
-        <v>105563</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8177,36 +7866,36 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>671</v>
+        <v>783</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8215,13 +7904,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707548</v>
+        <v>707605</v>
       </c>
       <c r="R64" t="n">
-        <v>6375014</v>
+        <v>6374970</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8255,7 +7944,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Körväg V.</t>
+          <t>Minsta antal + spridd.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8269,7 +7958,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering äldre, enstaka tall.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8287,15 +7976,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122578775</v>
+        <v>122578824</v>
       </c>
       <c r="B65" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8322,7 +8006,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8341,13 +8025,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707564</v>
+        <v>707606</v>
       </c>
       <c r="R65" t="n">
-        <v>6375169</v>
+        <v>6374961</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8390,7 +8074,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8408,15 +8092,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122578756</v>
+        <v>122578825</v>
       </c>
       <c r="B66" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8443,7 +8122,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8462,13 +8141,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707541</v>
+        <v>707611</v>
       </c>
       <c r="R66" t="n">
-        <v>6374993</v>
+        <v>6374954</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8500,11 +8179,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Körväg V.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8516,7 +8190,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Grandunge.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8534,15 +8208,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122578766</v>
+        <v>122578827</v>
       </c>
       <c r="B67" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8569,12 +8238,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8588,13 +8257,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707548</v>
+        <v>707613</v>
       </c>
       <c r="R67" t="n">
-        <v>6375091</v>
+        <v>6374932</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8626,11 +8295,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt inom 30 m mot O, N och V från kröken av skogsvägen. Även riklig SO vägkrök.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8642,7 +8306,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal.</t>
+          <t>Grandunge, f.d. grus-/sandtag?</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8660,15 +8324,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122578778</v>
+        <v>122578828</v>
       </c>
       <c r="B68" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8695,7 +8354,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8714,13 +8373,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707599</v>
+        <v>707605</v>
       </c>
       <c r="R68" t="n">
-        <v>6375165</v>
+        <v>6374936</v>
       </c>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8752,11 +8411,6 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Barrblandskog mot åker i N.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8768,7 +8422,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Granplantering halvgammal med enstaka tall. Vid äldre myrstack.</t>
+          <t>Grandunge, f.d. grus-/sandtag?</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8786,47 +8440,42 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122578752</v>
+        <v>122578751</v>
       </c>
       <c r="B69" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8912,47 +8561,42 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122578763</v>
+        <v>122578753</v>
       </c>
       <c r="B70" t="n">
-        <v>99893</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -8966,13 +8610,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707548</v>
+        <v>707554</v>
       </c>
       <c r="R70" t="n">
-        <v>6375014</v>
+        <v>6374978</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9038,15 +8682,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122578811</v>
+        <v>122578755</v>
       </c>
       <c r="B71" t="n">
-        <v>98343</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9073,7 +8712,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9092,13 +8731,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707652</v>
+        <v>707541</v>
       </c>
       <c r="R71" t="n">
-        <v>6374986</v>
+        <v>6374993</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9128,6 +8767,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9159,55 +8803,62 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134263109</v>
+        <v>122578757</v>
       </c>
       <c r="B72" t="n">
-        <v>106414</v>
+        <v>99096</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Viklau Sigsarve 1:2, Gtl</t>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>707561</v>
+        <v>707557</v>
       </c>
       <c r="R72" t="n">
-        <v>6374999</v>
+        <v>6375009</v>
       </c>
       <c r="S72" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9229,11 +8880,6 @@
           <t>Viklau</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>I-Got-4284</t>
-        </is>
-      </c>
       <c r="Y72" t="inlineStr">
         <is>
           <t>2025-02-11</t>
@@ -9246,7 +8892,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Körväg V. 3 kvm.</t>
+          <t>Körväg V.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9255,7 +8901,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9267,7 +8912,7 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -9275,58 +8920,66 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134263110</v>
+        <v>122578771</v>
       </c>
       <c r="B73" t="n">
-        <v>106414</v>
+        <v>99096</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Viklau Sigsarve 1:2, Gtl</t>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707658</v>
+        <v>707490</v>
       </c>
       <c r="R73" t="n">
-        <v>6375003</v>
+        <v>6375090</v>
       </c>
       <c r="S73" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9348,11 +9001,6 @@
           <t>Viklau</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>I-Got-4285</t>
-        </is>
-      </c>
       <c r="Y73" t="inlineStr">
         <is>
           <t>2025-02-11</t>
@@ -9365,7 +9013,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Spridd, riklig.</t>
+          <t>I långsträckt stensamlig, grav?</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9374,19 +9022,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Granplantering äldre.</t>
+          <t>Granplantering halvgammal.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -9394,11 +9041,1409 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>122578782</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>707621</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6375108</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>122578786</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>707652</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6375083</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Både skogskorn och gotlandsmåra saknas just här.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>122578789</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>707697</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6375043</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>122578791</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>707707</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6375037</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>122578797</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>707725</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6374976</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>122578802</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>707697</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6374969</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>122578805</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>707697</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6374980</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>122578808</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>707678</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6374990</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>122578811</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>707652</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6374986</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>122578814</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>707638</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6374988</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>122578750</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>707569</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6374979</v>
+      </c>
+      <c r="S84" t="n">
+        <v>3</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Körväg V.</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Granplantering äldre.</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>122578767</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Viklau Sigsarve 1:2 (3) NV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>707513</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6375053</v>
+      </c>
+      <c r="S85" t="n">
+        <v>7</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Viklau</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Granplantering halvgammal.</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2485-2025 artfynd.xlsx
+++ b/artfynd/A 2485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AZ85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578740</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578742</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578744</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578747</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578749</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578758</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,6 +1512,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578760</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578762</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1710,6 +1755,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578785</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1822,6 +1872,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578788</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1934,6 +1989,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578795</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2055,6 +2115,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578800</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2167,6 +2232,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578806</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2279,6 +2349,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578809</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2391,6 +2466,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578812</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2503,6 +2583,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578815</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2624,6 +2709,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578818</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2745,6 +2835,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578821</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2861,6 +2956,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578826</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2985,6 +3085,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263109</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3104,6 +3209,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263110</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3224,6 +3334,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074257</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3344,6 +3459,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074295</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3451,6 +3571,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578741</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3558,6 +3683,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578743</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3665,6 +3795,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578746</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3772,6 +3907,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578748</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3893,6 +4033,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578752</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4014,6 +4159,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578754</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4135,6 +4285,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578756</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4256,6 +4411,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578759</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4377,6 +4537,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578763</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4498,6 +4663,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578764</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4610,6 +4780,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578765</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4731,6 +4906,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578766</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4852,6 +5032,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578769</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4973,6 +5158,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578770</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5094,6 +5284,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578772</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5210,6 +5405,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578773</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5326,6 +5526,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578774</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5442,6 +5647,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578775</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5558,6 +5768,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578776</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5679,6 +5894,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578777</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5800,6 +6020,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578778</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5912,6 +6137,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578779</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6024,6 +6254,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578780</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6136,6 +6371,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578781</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6248,6 +6488,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578783</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6360,6 +6605,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578784</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6472,6 +6722,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578787</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6584,6 +6839,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578790</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6705,6 +6965,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578792</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6817,6 +7082,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578794</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6929,6 +7199,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578796</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7050,6 +7325,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578799</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7162,6 +7442,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578801</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7274,6 +7559,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578807</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7386,6 +7676,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578810</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7498,6 +7793,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578813</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7610,6 +7910,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578816</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7731,6 +8036,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578817</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7852,6 +8162,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578819</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7973,6 +8288,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578823</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8089,6 +8409,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578824</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8205,6 +8530,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578825</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8321,6 +8651,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578827</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8437,6 +8772,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578828</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8558,6 +8898,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578751</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8679,6 +9024,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578753</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8800,6 +9150,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578755</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8921,6 +9276,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578757</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9042,6 +9402,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578771</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9158,6 +9523,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578782</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9279,6 +9649,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578786</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9395,6 +9770,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578789</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9511,6 +9891,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578791</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9627,6 +10012,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578797</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9743,6 +10133,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578802</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9859,6 +10254,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578805</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9975,6 +10375,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578808</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10091,6 +10496,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578811</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10207,6 +10617,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578814</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10328,6 +10743,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578750</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10444,8 +10864,99 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578767</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>